--- a/Audit/JJ_PD_IP_M06_통합테스트결과서_계획서_v1.2_이노팸.xlsx
+++ b/Audit/JJ_PD_IP_M06_통합테스트결과서_계획서_v1.2_이노팸.xlsx
@@ -932,15 +932,15 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="10">
     <numFmt numFmtId="164" formatCode="yyyy\.mm\.dd"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\$#,##0.00_);&quot;₩&quot;&quot;₩&quot;\(&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\$#,##0.00&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\)"/>
-    <numFmt numFmtId="167" formatCode="&quot;₩&quot;#,##0.00;[Red]&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="&quot;₩&quot;#,##0;[Red]&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;#,##0"/>
-    <numFmt numFmtId="169" formatCode="_-&quot;₩&quot;* #,##0_-;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_-* #,##0.00_-;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="172" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="173" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\$#,##0.00_);&quot;₩&quot;&quot;₩&quot;\(&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\$#,##0.00&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\)"/>
+    <numFmt numFmtId="168" formatCode="&quot;₩&quot;#,##0.00;[Red]&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;#,##0.00"/>
+    <numFmt numFmtId="169" formatCode="&quot;₩&quot;#,##0;[Red]&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;#,##0"/>
+    <numFmt numFmtId="170" formatCode="_-&quot;₩&quot;* #,##0_-;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="171" formatCode="_-* #,##0.00_-;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="172" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="173" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="65">
     <font>
@@ -2191,14 +2191,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="168" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="169" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="7" fillId="2" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2212,7 +2212,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="10" fontId="7" fillId="2" borderId="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5"/>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
@@ -4817,14 +4817,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="172" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="173" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="172" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4963,7 +4963,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5192,7 +5192,10 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1643"/>
-    <xf numFmtId="173" fontId="56" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1643">
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1643">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1643">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -8660,7 +8663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A2:I30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.375" defaultRowHeight="17.1"/>
   <cols>
     <col width="8.125" customWidth="1" style="54" min="1" max="1"/>
@@ -8675,7 +8678,6 @@
     <col width="11.375" customWidth="1" style="54" min="14" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="27.6" customHeight="1" s="48">
       <c r="E2" s="11" t="n"/>
       <c r="F2" s="56" t="inlineStr">
@@ -8706,11 +8708,6 @@
       </c>
       <c r="I3" s="65" t="n"/>
     </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
     <row r="9" ht="26.25" customHeight="1" s="48">
       <c r="A9" s="63" t="inlineStr">
         <is>
@@ -8765,19 +8762,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
     <row r="28" ht="43.5" customHeight="1" s="48">
       <c r="B28" s="55" t="n"/>
       <c r="E28" s="55" t="n"/>
@@ -8918,7 +8902,7 @@
       <c r="E6" s="17" t="n"/>
     </row>
     <row r="7" ht="24.75" customHeight="1" s="48">
-      <c r="A7" s="85" t="n">
+      <c r="A7" s="86" t="n">
         <v>46323</v>
       </c>
       <c r="B7" s="17" t="inlineStr">
@@ -9123,7 +9107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M61"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.5" customWidth="1" style="48" min="1" max="1"/>
@@ -9140,6 +9124,7 @@
     <col width="13" customWidth="1" style="48" min="13" max="13"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="41.25" customHeight="1" s="48">
       <c r="A2" s="72" t="inlineStr">
         <is>
@@ -9147,6 +9132,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15.95" customHeight="1" s="48">
       <c r="A4" s="70" t="inlineStr">
         <is>
@@ -9332,8 +9318,8 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>- 대시보드 진입, 최종 업데이트 시각·KPI·추이 차트·집중구역/읍면동 순위 확인
-- [오늘/주간/월간]·상세 필터 전환</t>
+          <t>- 대시보드 진입, 최근 갱신 일시·KPI·추이 차트·집중구역/읍면동 순위 확인
+- [어제/주간/월간]·상세 필터 전환</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -9366,7 +9352,7 @@
       </c>
       <c r="F8" s="35" t="inlineStr">
         <is>
-          <t>[화면] 대시보드(Home)</t>
+          <t>[화면] 대시보드</t>
         </is>
       </c>
       <c r="G8" s="36" t="inlineStr">
@@ -9387,11 +9373,11 @@
       </c>
       <c r="J8" s="38" t="inlineStr">
         <is>
-          <t>- Header(메뉴명/최종 업데이트 일시)
-- 조회 필터 바(오늘/주간/월간 탭·상세 필터)
-- KPI 카드(총 민원건수/불법주차 발생/위험단계 발생)
+          <t>- Header(메뉴명/최근 갱신 일시)
+- 조회 필터 바(어제/주간/월간 탭·상세 필터)
+- KPI 카드(총 민원 건수/공영주차장 현황/위험단계알림 건수)
 - 민원 발생 추이 라인차트(유형별 색상)
-- 민원 집중구역 순위 Top5
+- 불법주차 집중구역 순위 Top5
 - 읍면동 민원순위 카드(건수/증감율/유형)
 - 분석·보고서·AI 최근목록 바로가기</t>
         </is>
@@ -9403,7 +9389,7 @@
       </c>
       <c r="L8" s="38" t="inlineStr">
         <is>
-          <t>- 대시보드(Home) 화면의 설계 기능이 모두 정상 표출·동작</t>
+          <t>- 대시보드 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
       <c r="M8" s="35" t="inlineStr">
@@ -9446,7 +9432,7 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>- 대시보드 [GIS 보기] 이동(조회조건 승계)
+          <t>- 대시보드 [자세히 보기] 이동(조회조건 승계)
 - 민원 다발/단속 집중/수요 부족 레이어 전환
 - 민원 다발·단속 집중 레이어 읍면동(폴리곤) ↔ 히트맵(밀도) 표현 전환
 - 공영주차장·행정동 경계 토글</t>
@@ -9588,7 +9574,7 @@
       </c>
       <c r="F12" s="35" t="inlineStr">
         <is>
-          <t>[화면] 민원현황(GIS)</t>
+          <t>[화면] 민원현황</t>
         </is>
       </c>
       <c r="G12" s="36" t="inlineStr">
@@ -9624,7 +9610,7 @@
       </c>
       <c r="L12" s="38" t="inlineStr">
         <is>
-          <t>- 민원현황(GIS) 화면의 설계 기능이 모두 정상 표출·동작</t>
+          <t>- 민원현황 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
       <c r="M12" s="35" t="inlineStr">
@@ -9862,7 +9848,7 @@
       </c>
       <c r="C17" s="67" t="inlineStr">
         <is>
-          <t>집중구역 진단 → 정책 시뮬레이션 → 보고서</t>
+          <t>집중구역 진단 → 정책 효과 시뮬레이션 → 보고서</t>
         </is>
       </c>
       <c r="D17" s="67" t="inlineStr">
@@ -9984,7 +9970,7 @@
       </c>
       <c r="F19" s="35" t="inlineStr">
         <is>
-          <t>[화면] 집중구역분석</t>
+          <t>[화면] 불법 주차 불법 주차 집중 구역 분석</t>
         </is>
       </c>
       <c r="G19" s="36" t="inlineStr">
@@ -10017,7 +10003,7 @@
       </c>
       <c r="L19" s="38" t="inlineStr">
         <is>
-          <t>- 집중구역분석 화면의 설계 기능이 모두 정상 표출·동작</t>
+          <t>- 불법 주차 불법 주차 집중 구역 분석 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
       <c r="M19" s="35" t="inlineStr">
@@ -10146,7 +10132,7 @@
       </c>
       <c r="F22" s="35" t="inlineStr">
         <is>
-          <t>[화면] 정책 시뮬레이션</t>
+          <t>[화면] 정책 효과 시뮬레이션</t>
         </is>
       </c>
       <c r="G22" s="36" t="inlineStr">
@@ -10180,7 +10166,7 @@
       </c>
       <c r="L22" s="38" t="inlineStr">
         <is>
-          <t>- 정책 시뮬레이션 화면의 설계 기능이 모두 정상 표출·동작</t>
+          <t>- 정책 효과 시뮬레이션 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
       <c r="M22" s="35" t="inlineStr">
@@ -10203,7 +10189,7 @@
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>[화면] 정책 시뮬레이션(상세)</t>
+          <t>[화면] 정책 효과 시뮬레이션(상세)</t>
         </is>
       </c>
       <c r="G23" s="36" t="n"/>
@@ -10485,7 +10471,7 @@
       </c>
       <c r="F28" s="35" t="inlineStr">
         <is>
-          <t>[화면] 구역 추천</t>
+          <t>[화면] 구역추천</t>
         </is>
       </c>
       <c r="G28" s="36" t="inlineStr">
@@ -10518,7 +10504,7 @@
       </c>
       <c r="L28" s="38" t="inlineStr">
         <is>
-          <t>- 구역 추천 화면의 설계 기능이 모두 정상 표출·동작</t>
+          <t>- 구역추천 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
       <c r="M28" s="35" t="inlineStr">
@@ -12426,7 +12412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:S44"/>
+  <dimension ref="A1:S44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="5.125" customWidth="1" style="2" min="1" max="1"/>
@@ -12447,6 +12433,7 @@
     <col width="9" customWidth="1" style="4" min="19" max="16384"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="41.25" customFormat="1" customHeight="1" s="83">
       <c r="A2" s="72" t="inlineStr">
         <is>
@@ -12609,7 +12596,7 @@
         <is>
           <t>- 로그인 화면 접속
 - [통합 인증으로 로그인] 클릭(D-Hub 통합 인증)
-- 대시보드(Home) 진입 확인</t>
+- 대시보드 진입 확인</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -12662,7 +12649,7 @@
       <c r="H7" s="1" t="inlineStr">
         <is>
           <t>- 대시보드 진입
-- 최종 업데이트 시각, KPI 카드, 추이 차트, 집중구역 순위, 읍·면·동 순위, 하단 위젯 확인</t>
+- 최근 갱신 일시, KPI 카드, 추이 차트, 집중구역 순위, 읍·면·동 순위, 하단 위젯 확인</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -12715,7 +12702,7 @@
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>- 상단 [오늘/주간/월간] 탭 전환
+          <t>- 상단 [어제/주간/월간] 탭 전환
 - [상세 필터]로 조회 기간 지정</t>
         </is>
       </c>
@@ -12933,7 +12920,7 @@
       <c r="H12" s="1" t="inlineStr">
         <is>
           <t>- 배치 완료 후 대시보드 재진입
-- 최종 업데이트 시각 및 KPI 수치 확인</t>
+- 최근 갱신 일시 및 KPI 수치 확인</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -12943,7 +12930,7 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>- 최종 업데이트 시각이 갱신되고 KPI 수치가 수집 결과와 일치</t>
+          <t>- 최근 갱신 일시이 갱신되고 KPI 수치가 수집 결과와 일치</t>
         </is>
       </c>
       <c r="K12" s="3" t="n"/>
@@ -12985,7 +12972,7 @@
       </c>
       <c r="F13" s="73" t="inlineStr">
         <is>
-          <t>GIS 보기 화면 이동 및 조회조건 승계</t>
+          <t>자세히 보기 이동 및 조회조건 승계</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
@@ -12993,7 +12980,7 @@
       </c>
       <c r="H13" s="1" t="inlineStr">
         <is>
-          <t>- 대시보드 '민원 집중구역 순위' 영역의 [GIS 보기] 클릭
+          <t>- 대시보드 '불법주차 집중구역 순위' 영역의 [자세히 보기] 클릭
 - 민원현황 화면 진입 확인</t>
         </is>
       </c>
@@ -13004,7 +12991,7 @@
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>- 민원현황(GIS) 화면으로 이동하고 직전 조회 단위·기간 조건이 승계</t>
+          <t>- 민원현황 화면으로 이동하고 직전 조회 단위·기간 조건이 승계</t>
         </is>
       </c>
       <c r="K13" s="3" t="n"/>
@@ -13151,7 +13138,7 @@
       <c r="H16" s="1" t="inlineStr">
         <is>
           <t>- 조회 필터(행정구역/민원유형/위험단계) 변경
-- 우측 지역별 민원현황 및 민원 집중구역 순위 확인</t>
+- 우측 지역별 민원현황 및 불법주차 집중구역 순위 확인</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -13210,7 +13197,7 @@
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
-          <t>- 분석·시뮬레이션 &gt; 집중구역분석 진입
+          <t>- 분석·시뮬레이션 &gt; 불법 주차 불법 주차 집중 구역 분석 진입
 - 분석 지역(제주시), 분석 기간(최근3개월) 설정
 - [분석 실행] 클릭</t>
         </is>
@@ -14782,13 +14769,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:O897"/>
+  <dimension ref="A1:O897"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="17.1"/>
   <cols>
     <col width="10" customWidth="1" style="48" min="1" max="3"/>
     <col width="12" customWidth="1" style="48" min="4" max="15"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="24" customHeight="1" s="48">
       <c r="A2" s="43" t="inlineStr">
         <is>
@@ -14991,6 +14979,7 @@
       <c r="N23" s="51" t="n"/>
       <c r="O23" s="52" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25" ht="24" customHeight="1" s="48">
       <c r="A25" s="43" t="inlineStr">
         <is>
@@ -15193,6 +15182,7 @@
       <c r="N46" s="51" t="n"/>
       <c r="O46" s="52" t="n"/>
     </row>
+    <row r="47"/>
     <row r="48" ht="24" customHeight="1" s="48">
       <c r="A48" s="43" t="inlineStr">
         <is>
@@ -15395,6 +15385,7 @@
       <c r="N69" s="51" t="n"/>
       <c r="O69" s="52" t="n"/>
     </row>
+    <row r="70"/>
     <row r="71" ht="24" customHeight="1" s="48">
       <c r="A71" s="43" t="inlineStr">
         <is>
@@ -15597,6 +15588,7 @@
       <c r="N92" s="51" t="n"/>
       <c r="O92" s="52" t="n"/>
     </row>
+    <row r="93"/>
     <row r="94" ht="24" customHeight="1" s="48">
       <c r="A94" s="43" t="inlineStr">
         <is>
@@ -15799,6 +15791,7 @@
       <c r="N115" s="51" t="n"/>
       <c r="O115" s="52" t="n"/>
     </row>
+    <row r="116"/>
     <row r="117" ht="24" customHeight="1" s="48">
       <c r="A117" s="43" t="inlineStr">
         <is>
@@ -16001,6 +15994,7 @@
       <c r="N138" s="51" t="n"/>
       <c r="O138" s="52" t="n"/>
     </row>
+    <row r="139"/>
     <row r="140" ht="24" customHeight="1" s="48">
       <c r="A140" s="43" t="inlineStr">
         <is>
@@ -16203,6 +16197,7 @@
       <c r="N161" s="51" t="n"/>
       <c r="O161" s="52" t="n"/>
     </row>
+    <row r="162"/>
     <row r="163" ht="24" customHeight="1" s="48">
       <c r="A163" s="43" t="inlineStr">
         <is>
@@ -16288,7 +16283,7 @@
       <c r="C166" s="42" t="n"/>
       <c r="D166" s="40" t="inlineStr">
         <is>
-          <t>GIS 보기 화면 이동 및 조회조건 승계</t>
+          <t>자세히 보기 이동 및 조회조건 승계</t>
         </is>
       </c>
       <c r="E166" s="41" t="n"/>
@@ -16405,6 +16400,7 @@
       <c r="N184" s="51" t="n"/>
       <c r="O184" s="52" t="n"/>
     </row>
+    <row r="185"/>
     <row r="186" ht="24" customHeight="1" s="48">
       <c r="A186" s="43" t="inlineStr">
         <is>
@@ -16607,6 +16603,7 @@
       <c r="N207" s="51" t="n"/>
       <c r="O207" s="52" t="n"/>
     </row>
+    <row r="208"/>
     <row r="209" ht="24" customHeight="1" s="48">
       <c r="A209" s="43" t="inlineStr">
         <is>
@@ -16809,6 +16806,7 @@
       <c r="N230" s="51" t="n"/>
       <c r="O230" s="52" t="n"/>
     </row>
+    <row r="231"/>
     <row r="232" ht="24" customHeight="1" s="48">
       <c r="A232" s="43" t="inlineStr">
         <is>
@@ -17011,6 +17009,7 @@
       <c r="N253" s="51" t="n"/>
       <c r="O253" s="52" t="n"/>
     </row>
+    <row r="254"/>
     <row r="255" ht="24" customHeight="1" s="48">
       <c r="A255" s="43" t="inlineStr">
         <is>
@@ -17213,6 +17212,7 @@
       <c r="N276" s="51" t="n"/>
       <c r="O276" s="52" t="n"/>
     </row>
+    <row r="277"/>
     <row r="278" ht="24" customHeight="1" s="48">
       <c r="A278" s="43" t="inlineStr">
         <is>
@@ -17415,6 +17415,7 @@
       <c r="N299" s="51" t="n"/>
       <c r="O299" s="52" t="n"/>
     </row>
+    <row r="300"/>
     <row r="301" ht="24" customHeight="1" s="48">
       <c r="A301" s="43" t="inlineStr">
         <is>
@@ -17617,6 +17618,7 @@
       <c r="N322" s="51" t="n"/>
       <c r="O322" s="52" t="n"/>
     </row>
+    <row r="323"/>
     <row r="324" ht="24" customHeight="1" s="48">
       <c r="A324" s="43" t="inlineStr">
         <is>
@@ -17819,6 +17821,7 @@
       <c r="N345" s="51" t="n"/>
       <c r="O345" s="52" t="n"/>
     </row>
+    <row r="346"/>
     <row r="347" ht="24" customHeight="1" s="48">
       <c r="A347" s="43" t="inlineStr">
         <is>
@@ -18021,6 +18024,7 @@
       <c r="N368" s="51" t="n"/>
       <c r="O368" s="52" t="n"/>
     </row>
+    <row r="369"/>
     <row r="370" ht="24" customHeight="1" s="48">
       <c r="A370" s="43" t="inlineStr">
         <is>
@@ -18223,6 +18227,7 @@
       <c r="N391" s="51" t="n"/>
       <c r="O391" s="52" t="n"/>
     </row>
+    <row r="392"/>
     <row r="393" ht="24" customHeight="1" s="48">
       <c r="A393" s="43" t="inlineStr">
         <is>
@@ -18425,6 +18430,7 @@
       <c r="N414" s="51" t="n"/>
       <c r="O414" s="52" t="n"/>
     </row>
+    <row r="415"/>
     <row r="416" ht="24" customHeight="1" s="48">
       <c r="A416" s="43" t="inlineStr">
         <is>
@@ -18627,6 +18633,7 @@
       <c r="N437" s="51" t="n"/>
       <c r="O437" s="52" t="n"/>
     </row>
+    <row r="438"/>
     <row r="439" ht="24" customHeight="1" s="48">
       <c r="A439" s="43" t="inlineStr">
         <is>
@@ -18829,6 +18836,7 @@
       <c r="N460" s="51" t="n"/>
       <c r="O460" s="52" t="n"/>
     </row>
+    <row r="461"/>
     <row r="462" ht="24" customHeight="1" s="48">
       <c r="A462" s="43" t="inlineStr">
         <is>
@@ -19031,6 +19039,7 @@
       <c r="N483" s="51" t="n"/>
       <c r="O483" s="52" t="n"/>
     </row>
+    <row r="484"/>
     <row r="485" ht="24" customHeight="1" s="48">
       <c r="A485" s="43" t="inlineStr">
         <is>
@@ -19233,6 +19242,7 @@
       <c r="N506" s="51" t="n"/>
       <c r="O506" s="52" t="n"/>
     </row>
+    <row r="507"/>
     <row r="508" ht="24" customHeight="1" s="48">
       <c r="A508" s="43" t="inlineStr">
         <is>
@@ -19435,6 +19445,7 @@
       <c r="N529" s="51" t="n"/>
       <c r="O529" s="52" t="n"/>
     </row>
+    <row r="530"/>
     <row r="531" ht="24" customHeight="1" s="48">
       <c r="A531" s="43" t="inlineStr">
         <is>
@@ -19637,6 +19648,7 @@
       <c r="N552" s="51" t="n"/>
       <c r="O552" s="52" t="n"/>
     </row>
+    <row r="553"/>
     <row r="554" ht="24" customHeight="1" s="48">
       <c r="A554" s="43" t="inlineStr">
         <is>
@@ -19839,6 +19851,7 @@
       <c r="N575" s="51" t="n"/>
       <c r="O575" s="52" t="n"/>
     </row>
+    <row r="576"/>
     <row r="577" ht="24" customHeight="1" s="48">
       <c r="A577" s="43" t="inlineStr">
         <is>
@@ -20041,6 +20054,7 @@
       <c r="N598" s="51" t="n"/>
       <c r="O598" s="52" t="n"/>
     </row>
+    <row r="599"/>
     <row r="600" ht="24" customHeight="1" s="48">
       <c r="A600" s="43" t="inlineStr">
         <is>
@@ -20243,6 +20257,7 @@
       <c r="N621" s="51" t="n"/>
       <c r="O621" s="52" t="n"/>
     </row>
+    <row r="622"/>
     <row r="623" ht="24" customHeight="1" s="48">
       <c r="A623" s="43" t="inlineStr">
         <is>
@@ -20445,6 +20460,7 @@
       <c r="N644" s="51" t="n"/>
       <c r="O644" s="52" t="n"/>
     </row>
+    <row r="645"/>
     <row r="646" ht="24" customHeight="1" s="48">
       <c r="A646" s="43" t="inlineStr">
         <is>
@@ -20647,6 +20663,7 @@
       <c r="N667" s="51" t="n"/>
       <c r="O667" s="52" t="n"/>
     </row>
+    <row r="668"/>
     <row r="669" ht="24" customHeight="1" s="48">
       <c r="A669" s="43" t="inlineStr">
         <is>
@@ -20849,6 +20866,7 @@
       <c r="N690" s="51" t="n"/>
       <c r="O690" s="52" t="n"/>
     </row>
+    <row r="691"/>
     <row r="692" ht="24" customHeight="1" s="48">
       <c r="A692" s="43" t="inlineStr">
         <is>
@@ -21051,6 +21069,7 @@
       <c r="N713" s="51" t="n"/>
       <c r="O713" s="52" t="n"/>
     </row>
+    <row r="714"/>
     <row r="715" ht="24" customHeight="1" s="48">
       <c r="A715" s="43" t="inlineStr">
         <is>
@@ -21253,6 +21272,7 @@
       <c r="N736" s="51" t="n"/>
       <c r="O736" s="52" t="n"/>
     </row>
+    <row r="737"/>
     <row r="738" ht="24" customHeight="1" s="48">
       <c r="A738" s="43" t="inlineStr">
         <is>
@@ -21455,6 +21475,7 @@
       <c r="N759" s="51" t="n"/>
       <c r="O759" s="52" t="n"/>
     </row>
+    <row r="760"/>
     <row r="761" ht="24" customHeight="1" s="48">
       <c r="A761" s="43" t="inlineStr">
         <is>
@@ -21657,6 +21678,7 @@
       <c r="N782" s="51" t="n"/>
       <c r="O782" s="52" t="n"/>
     </row>
+    <row r="783"/>
     <row r="784" ht="24" customHeight="1" s="48">
       <c r="A784" s="43" t="inlineStr">
         <is>
@@ -21859,6 +21881,7 @@
       <c r="N805" s="51" t="n"/>
       <c r="O805" s="52" t="n"/>
     </row>
+    <row r="806"/>
     <row r="807" ht="24" customHeight="1" s="48">
       <c r="A807" s="43" t="inlineStr">
         <is>
@@ -22061,6 +22084,7 @@
       <c r="N828" s="51" t="n"/>
       <c r="O828" s="52" t="n"/>
     </row>
+    <row r="829"/>
     <row r="830" ht="24" customHeight="1" s="48">
       <c r="A830" s="43" t="inlineStr">
         <is>
@@ -22263,6 +22287,7 @@
       <c r="N851" s="51" t="n"/>
       <c r="O851" s="52" t="n"/>
     </row>
+    <row r="852"/>
     <row r="853" ht="24" customHeight="1" s="48">
       <c r="A853" s="43" t="inlineStr">
         <is>
@@ -22465,6 +22490,7 @@
       <c r="N874" s="51" t="n"/>
       <c r="O874" s="52" t="n"/>
     </row>
+    <row r="875"/>
     <row r="876" ht="24" customHeight="1" s="48">
       <c r="A876" s="43" t="inlineStr">
         <is>
@@ -23050,6 +23076,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="28" t="inlineStr">
         <is>

--- a/Audit/JJ_PD_IP_M06_통합테스트결과서_계획서_v1.2_이노팸.xlsx
+++ b/Audit/JJ_PD_IP_M06_통합테스트결과서_계획서_v1.2_이노팸.xlsx
@@ -13912,7 +13912,7 @@
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
-          <t>- 안전위험도 35%·민원빈도 25%·이용패턴 20%·사고이력 20% 가중치로 종합점수가 자동 산정</t>
+          <t>- 안전위험도 25%·민원빈도 25%·이용패턴 25%·사고이력 25% 가중치로 종합점수가 자동 산정</t>
         </is>
       </c>
       <c r="K30" s="3" t="n"/>

--- a/Audit/JJ_PD_IP_M06_통합테스트결과서_계획서_v1.2_이노팸.xlsx
+++ b/Audit/JJ_PD_IP_M06_통합테스트결과서_계획서_v1.2_이노팸.xlsx
@@ -9894,7 +9894,7 @@
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
-          <t>- 종합점수(민원60%·단속40%) 기준 집중구역 자동 도출, 지도·순위 갱신</t>
+          <t>- 종합점수 기준 집중구역 자동 도출, 지도·순위 갱신</t>
         </is>
       </c>
       <c r="M17" s="67" t="inlineStr">
@@ -9993,7 +9993,7 @@
         <is>
           <t>- 분석 설정(지역 드롭다운·기간 탭/날짜 피커·분석 실행)
 - 지도 시각화(집중구역 마커/순위·클릭 팝업)
-- 종합점수 기준(민원60%·단속40%) 구역 순위(구역명/민원/단속 건수)</t>
+- 종합점수 기준(민원·단속 건수 가중합) 구역 순위(구역명/민원/단속 건수)</t>
         </is>
       </c>
       <c r="K19" s="39" t="inlineStr">
@@ -10670,7 +10670,7 @@
         <is>
           <t>- 요약 카드(대상 주차장 수/높음 개소/최근3개월 사고)
 - 지도 P핀 마커(우선순위 컬러·순위)·클릭 4지표 팝업
-- 종합점수(안전35%·민원25%·이용20%·사고20%) 순위 배지</t>
+- 종합점수(안전위험도·민원빈도·이용패턴·사고이력) 순위 배지</t>
         </is>
       </c>
       <c r="K31" s="39" t="inlineStr">
@@ -13209,7 +13209,7 @@
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
-          <t>- 종합점수(민원 60%·단속 40%) 기준으로 집중구역이 자동 도출되어 지도·순위가 갱신</t>
+          <t>- 종합점수 기준으로 집중구역이 자동 도출되어 지도·순위가 갱신</t>
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
@@ -13853,7 +13853,7 @@
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
-          <t>- 종합점수(민원 40%·증가율 30%·단속 20%·공급부족 10%) 기준으로 상위 구역 순위가 표출</t>
+          <t>- 민원 증가 추세를 반영한 순위 기준으로 상위 구역이 표출</t>
         </is>
       </c>
       <c r="K29" s="3" t="n"/>
@@ -13912,7 +13912,7 @@
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
-          <t>- 안전위험도 25%·민원빈도 25%·이용패턴 25%·사고이력 25% 가중치로 종합점수가 자동 산정</t>
+          <t>- 설정된 가중치(안전위험도·민원빈도·이용패턴·사고이력)로 종합점수가 자동 산정</t>
         </is>
       </c>
       <c r="K30" s="3" t="n"/>

--- a/Audit/JJ_PD_IP_M06_통합테스트결과서_계획서_v1.2_이노팸.xlsx
+++ b/Audit/JJ_PD_IP_M06_통합테스트결과서_계획서_v1.2_이노팸.xlsx
@@ -11896,7 +11896,7 @@
       </c>
       <c r="J53" s="38" t="inlineStr">
         <is>
-          <t>- 분석유형별 탭 가중치 조절(합계 100% 미만 시 저장 불가)
+          <t>- 분석유형별 탭 가중치 조절
 - 가중치 변경 이력 표시
 - 설정 저장(변경 내용 이력 기록)
 - 기본값 초기화(롤백)</t>

--- a/Audit/JJ_PD_IP_M06_통합테스트결과서_계획서_v1.2_이노팸.xlsx
+++ b/Audit/JJ_PD_IP_M06_통합테스트결과서_계획서_v1.2_이노팸.xlsx
@@ -20749,7 +20749,7 @@
       <c r="C672" s="42" t="n"/>
       <c r="D672" s="40" t="inlineStr">
         <is>
-          <t>임계값 초과 시 알림 자동 발생</t>
+          <t>기준 충족 시 알림 자동 발생</t>
         </is>
       </c>
       <c r="E672" s="41" t="n"/>

--- a/Audit/JJ_PD_IP_M06_통합테스트결과서_계획서_v1.2_이노팸.xlsx
+++ b/Audit/JJ_PD_IP_M06_통합테스트결과서_계획서_v1.2_이노팸.xlsx
@@ -9107,7 +9107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A2:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.5" customWidth="1" style="48" min="1" max="1"/>
@@ -9124,7 +9124,6 @@
     <col width="13" customWidth="1" style="48" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="41.25" customHeight="1" s="48">
       <c r="A2" s="72" t="inlineStr">
         <is>
@@ -9132,7 +9131,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15.95" customHeight="1" s="48">
       <c r="A4" s="70" t="inlineStr">
         <is>
@@ -10746,21 +10744,6 @@
       <c r="A33" s="67" t="n">
         <v>28</v>
       </c>
-      <c r="B33" s="67" t="inlineStr">
-        <is>
-          <t>ITS-PAR-05</t>
-        </is>
-      </c>
-      <c r="C33" s="67" t="inlineStr">
-        <is>
-          <t>행정문서 수집·정형화 → AI 어시스턴트 행정 지원</t>
-        </is>
-      </c>
-      <c r="D33" s="67" t="inlineStr">
-        <is>
-          <t>시스템관리자</t>
-        </is>
-      </c>
       <c r="E33" s="67" t="inlineStr">
         <is>
           <t>TT-PAR-05-01</t>
@@ -10768,12 +10751,12 @@
       </c>
       <c r="F33" s="67" t="inlineStr">
         <is>
-          <t>첨부문서 업로드</t>
+          <t>AI 대화 세션 관리</t>
         </is>
       </c>
       <c r="G33" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-010-03</t>
+          <t>PR-PAR-010-01</t>
         </is>
       </c>
       <c r="H33" s="67" t="inlineStr">
@@ -10783,23 +10766,23 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>비정형 행정문서 업로드·정형화</t>
+          <t>자연어 질의(sLLM+RAG)</t>
         </is>
       </c>
       <c r="J33" s="1" t="inlineStr">
         <is>
-          <t>- PDF/DOCX 등 비정형 문서 업로드
-- 텍스트 추출·정형화 적재 및 RAG 연계 확인</t>
+          <t>- 자연어 질의 입력
+- sLLM 응답 및 세션 이력 확인</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>시스템관리자 권한 계정</t>
+          <t>교통행정과 담당자 권한 계정</t>
         </is>
       </c>
       <c r="L33" s="1" t="inlineStr">
         <is>
-          <t>- 비정형 문서가 정형화 적재되고 RAG 검색 대상에 포함</t>
+          <t>- sLLM 자연어 응답이 정상 표출되고 대화 세션·메시지가 관리됨</t>
         </is>
       </c>
       <c r="M33" s="67" t="inlineStr">
@@ -10812,9 +10795,6 @@
       <c r="A34" s="67" t="n">
         <v>29</v>
       </c>
-      <c r="B34" s="68" t="n"/>
-      <c r="C34" s="68" t="n"/>
-      <c r="D34" s="68" t="n"/>
       <c r="E34" s="67" t="inlineStr">
         <is>
           <t>TT-PAR-05-02</t>
@@ -10822,12 +10802,12 @@
       </c>
       <c r="F34" s="67" t="inlineStr">
         <is>
-          <t>AI 대화 세션 관리</t>
+          <t>조례 인용·문서 조회</t>
         </is>
       </c>
       <c r="G34" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-010-01</t>
+          <t>PR-PAR-010-02</t>
         </is>
       </c>
       <c r="H34" s="67" t="inlineStr">
@@ -10837,402 +10817,401 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>자연어 질의(sLLM+RAG)</t>
+          <t>RAG 조례 인용 카드</t>
         </is>
       </c>
       <c r="J34" s="1" t="inlineStr">
-        <is>
-          <t>- 자연어 질의 입력
-- sLLM 응답 및 세션 이력 확인</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>교통행정과 담당자 권한 계정</t>
-        </is>
-      </c>
-      <c r="L34" s="1" t="inlineStr">
-        <is>
-          <t>- sLLM 자연어 응답이 정상 표출되고 대화 세션·메시지가 관리됨</t>
-        </is>
-      </c>
-      <c r="M34" s="67" t="inlineStr">
-        <is>
-          <t>정정</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="78" customHeight="1" s="48">
-      <c r="A35" s="67" t="n">
-        <v>30</v>
-      </c>
-      <c r="B35" s="68" t="n"/>
-      <c r="C35" s="68" t="n"/>
-      <c r="D35" s="68" t="n"/>
-      <c r="E35" s="67" t="inlineStr">
-        <is>
-          <t>TT-PAR-05-03</t>
-        </is>
-      </c>
-      <c r="F35" s="67" t="inlineStr">
-        <is>
-          <t>조례 인용·문서 조회</t>
-        </is>
-      </c>
-      <c r="G35" s="22" t="inlineStr">
-        <is>
-          <t>PR-PAR-010-02</t>
-        </is>
-      </c>
-      <c r="H35" s="67" t="inlineStr">
-        <is>
-          <t>UI-PAR-005-01</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>RAG 조례 인용 카드</t>
-        </is>
-      </c>
-      <c r="J35" s="1" t="inlineStr">
         <is>
           <t>- 조례 관련 질의
 - 조례명·관련 조문 발췌 응답 확인</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>교통행정과 담당자 권한 계정</t>
         </is>
       </c>
-      <c r="L35" s="1" t="inlineStr">
+      <c r="L34" s="1" t="inlineStr">
         <is>
           <t>- 관련 조례가 조례명·조문 발췌로 표출되고 답변에 반영</t>
         </is>
       </c>
-      <c r="M35" s="67" t="inlineStr">
+      <c r="M34" s="67" t="inlineStr">
         <is>
           <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="78" customHeight="1" s="48">
-      <c r="A36" s="35" t="n">
-        <v>31</v>
-      </c>
-      <c r="B36" s="68" t="n"/>
-      <c r="C36" s="68" t="n"/>
-      <c r="D36" s="68" t="n"/>
-      <c r="E36" s="35" t="inlineStr">
-        <is>
-          <t>TT-PAR-05-04</t>
-        </is>
-      </c>
-      <c r="F36" s="35" t="inlineStr">
+    <row r="35" ht="78" customHeight="1" s="48">
+      <c r="A35" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="E35" s="35" t="inlineStr">
+        <is>
+          <t>TT-PAR-05-03</t>
+        </is>
+      </c>
+      <c r="F35" s="35" t="inlineStr">
         <is>
           <t>[화면] AI 어시스턴트(행정조례검색)</t>
         </is>
       </c>
-      <c r="G36" s="36" t="inlineStr">
+      <c r="G35" s="36" t="inlineStr">
         <is>
           <t>PR-PAR-010-01~04</t>
         </is>
       </c>
-      <c r="H36" s="35" t="inlineStr">
+      <c r="H35" s="35" t="inlineStr">
         <is>
           <t>UI-PAR-005-01</t>
         </is>
       </c>
-      <c r="I36" s="37" t="inlineStr">
+      <c r="I35" s="37" t="inlineStr">
         <is>
           <t>sLLM+RAG 기반 대화형 행정 정보 검색
 (화면설계 점검)</t>
         </is>
       </c>
-      <c r="J36" s="38" t="inlineStr">
+      <c r="J35" s="38" t="inlineStr">
         <is>
           <t>- 채팅 영역(조례 인용: 조례명+관련 조문 발췌)
-- sLLM·RAG 정책문서·조례 검색·리포트 생성
-- 질문 입력·파일 첨부(PDF/DOCX)
-- 최근 대화·최근 리포트·자주하는질문</t>
-        </is>
-      </c>
-      <c r="K36" s="39" t="inlineStr">
+- sLLM·RAG 정책문서·조례 검색
+- 질문 입력
+- 최근 대화·최근 리포트</t>
+        </is>
+      </c>
+      <c r="K35" s="39" t="inlineStr">
         <is>
           <t>일반사용자 권한 계정</t>
         </is>
       </c>
-      <c r="L36" s="38" t="inlineStr">
+      <c r="L35" s="38" t="inlineStr">
         <is>
           <t>- AI 어시스턴트(행정조례검색) 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
-      <c r="M36" s="35" t="inlineStr">
+      <c r="M35" s="35" t="inlineStr">
         <is>
           <t>화면설계</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="78" customHeight="1" s="48">
-      <c r="A37" s="67" t="n">
-        <v>32</v>
-      </c>
-      <c r="B37" s="68" t="n"/>
-      <c r="C37" s="68" t="n"/>
-      <c r="D37" s="68" t="n"/>
-      <c r="E37" s="67" t="inlineStr">
-        <is>
-          <t>TT-PAR-05-05</t>
-        </is>
-      </c>
-      <c r="F37" s="67" t="inlineStr">
+    <row r="36" ht="78" customHeight="1" s="48">
+      <c r="A36" s="67" t="n">
+        <v>31</v>
+      </c>
+      <c r="E36" s="67" t="inlineStr">
+        <is>
+          <t>TT-PAR-05-04</t>
+        </is>
+      </c>
+      <c r="F36" s="67" t="inlineStr">
         <is>
           <t>대량 민원 자동 요약</t>
         </is>
       </c>
-      <c r="G37" s="22" t="inlineStr">
+      <c r="G36" s="22" t="inlineStr">
         <is>
           <t>PR-PAR-010-01</t>
         </is>
       </c>
-      <c r="H37" s="67" t="inlineStr">
+      <c r="H36" s="67" t="inlineStr">
         <is>
           <t>UI-PAR-005-02</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
+      <c r="I36" s="3" t="inlineStr">
         <is>
           <t>AI 대량 민원 내용 요약</t>
         </is>
       </c>
-      <c r="J37" s="1" t="inlineStr">
+      <c r="J36" s="1" t="inlineStr">
         <is>
           <t>- 대량 민원 대상 자연어 질의
 - AI 응답의 요약 결과 및 [리포트 생성] 확인</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>교통행정과 담당자 권한 계정</t>
         </is>
       </c>
-      <c r="L37" s="1" t="inlineStr">
+      <c r="L36" s="1" t="inlineStr">
         <is>
           <t>- 대량 민원 내용이 요약되어 표출되고 리포트 생성 버튼 제공</t>
         </is>
       </c>
-      <c r="M37" s="67" t="inlineStr">
+      <c r="M36" s="67" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="78" customHeight="1" s="48">
-      <c r="A38" s="35" t="n">
-        <v>33</v>
-      </c>
-      <c r="B38" s="68" t="n"/>
-      <c r="C38" s="68" t="n"/>
-      <c r="D38" s="68" t="n"/>
-      <c r="E38" s="35" t="inlineStr">
-        <is>
-          <t>TT-PAR-05-06</t>
-        </is>
-      </c>
-      <c r="F38" s="35" t="inlineStr">
+    <row r="37" ht="78" customHeight="1" s="48">
+      <c r="A37" s="35" t="n">
+        <v>32</v>
+      </c>
+      <c r="E37" s="35" t="inlineStr">
+        <is>
+          <t>TT-PAR-05-05</t>
+        </is>
+      </c>
+      <c r="F37" s="35" t="inlineStr">
         <is>
           <t>[화면] AI 어시스턴트(대량 민원 자동 요약)</t>
         </is>
       </c>
-      <c r="G38" s="36" t="n"/>
-      <c r="H38" s="35" t="inlineStr">
+      <c r="G37" s="36" t="n"/>
+      <c r="H37" s="35" t="inlineStr">
         <is>
           <t>UI-PAR-005-02</t>
         </is>
       </c>
-      <c r="I38" s="37" t="inlineStr">
+      <c r="I37" s="37" t="inlineStr">
         <is>
           <t>sLLM+RAG 기반 대량 민원 내용 자동 요약
 (화면설계 점검)</t>
         </is>
       </c>
-      <c r="J38" s="38" t="inlineStr">
+      <c r="J37" s="38" t="inlineStr">
         <is>
           <t>- 채팅 영역
 - AI 응답 시 대량 민원 내용 요약(리포트 생성 버튼 제공)</t>
         </is>
       </c>
-      <c r="K38" s="39" t="inlineStr">
+      <c r="K37" s="39" t="inlineStr">
         <is>
           <t>일반사용자 권한 계정</t>
         </is>
       </c>
-      <c r="L38" s="38" t="inlineStr">
+      <c r="L37" s="38" t="inlineStr">
         <is>
           <t>- AI 어시스턴트(대량 민원 자동 요약) 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
-      <c r="M38" s="35" t="inlineStr">
+      <c r="M37" s="35" t="inlineStr">
         <is>
           <t>화면설계</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="78" customHeight="1" s="48">
-      <c r="A39" s="67" t="n">
-        <v>34</v>
-      </c>
-      <c r="B39" s="68" t="n"/>
-      <c r="C39" s="68" t="n"/>
-      <c r="D39" s="68" t="n"/>
-      <c r="E39" s="67" t="inlineStr">
-        <is>
-          <t>TT-PAR-05-07</t>
-        </is>
-      </c>
-      <c r="F39" s="67" t="inlineStr">
+    <row r="38" ht="78" customHeight="1" s="48">
+      <c r="A38" s="67" t="n">
+        <v>33</v>
+      </c>
+      <c r="E38" s="67" t="inlineStr">
+        <is>
+          <t>TT-PAR-05-06</t>
+        </is>
+      </c>
+      <c r="F38" s="67" t="inlineStr">
         <is>
           <t>요약 보고서 미리보기·다운로드</t>
         </is>
       </c>
-      <c r="G39" s="22" t="inlineStr">
+      <c r="G38" s="22" t="inlineStr">
         <is>
           <t>PR-PAR-010-01</t>
         </is>
       </c>
-      <c r="H39" s="67" t="inlineStr">
+      <c r="H38" s="67" t="inlineStr">
         <is>
           <t>UI-PAR-005-03</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
+      <c r="I38" s="3" t="inlineStr">
         <is>
           <t>민원요약 보고서 출력</t>
         </is>
       </c>
-      <c r="J39" s="1" t="inlineStr">
+      <c r="J38" s="1" t="inlineStr">
         <is>
           <t>- [리포트 생성] 후 미리보기
 - PDF/DOCX 다운로드</t>
         </is>
       </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>교통행정과 담당자 권한 계정</t>
         </is>
       </c>
-      <c r="L39" s="1" t="inlineStr">
+      <c r="L38" s="1" t="inlineStr">
         <is>
           <t>- 민원요약 보고서 미리보기 표출 및 PDF·DOCX 다운로드</t>
         </is>
       </c>
-      <c r="M39" s="67" t="inlineStr">
+      <c r="M38" s="67" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="78" customHeight="1" s="48">
-      <c r="A40" s="35" t="n">
-        <v>35</v>
-      </c>
-      <c r="B40" s="68" t="n"/>
-      <c r="C40" s="68" t="n"/>
-      <c r="D40" s="68" t="n"/>
-      <c r="E40" s="35" t="inlineStr">
-        <is>
-          <t>TT-PAR-05-08</t>
-        </is>
-      </c>
-      <c r="F40" s="35" t="inlineStr">
+    <row r="39" ht="78" customHeight="1" s="48">
+      <c r="A39" s="35" t="n">
+        <v>34</v>
+      </c>
+      <c r="E39" s="35" t="inlineStr">
+        <is>
+          <t>TT-PAR-05-07</t>
+        </is>
+      </c>
+      <c r="F39" s="35" t="inlineStr">
         <is>
           <t>[화면] AI 어시스턴트(보고서 미리보기·다운로드)</t>
         </is>
       </c>
-      <c r="G40" s="36" t="n"/>
-      <c r="H40" s="35" t="inlineStr">
+      <c r="G39" s="36" t="n"/>
+      <c r="H39" s="35" t="inlineStr">
         <is>
           <t>UI-PAR-005-03</t>
         </is>
       </c>
-      <c r="I40" s="37" t="inlineStr">
+      <c r="I39" s="37" t="inlineStr">
         <is>
           <t>민원요약 보고서 미리보기·다운로드
 (화면설계 점검)</t>
         </is>
       </c>
-      <c r="J40" s="38" t="inlineStr">
+      <c r="J39" s="38" t="inlineStr">
         <is>
           <t>- 민원요약 보고서 미리보기
 - 보고서 다운로드(PDF, DOCX)</t>
         </is>
       </c>
-      <c r="K40" s="39" t="inlineStr">
+      <c r="K39" s="39" t="inlineStr">
         <is>
           <t>일반사용자 권한 계정</t>
         </is>
       </c>
-      <c r="L40" s="38" t="inlineStr">
+      <c r="L39" s="38" t="inlineStr">
         <is>
           <t>- AI 어시스턴트(보고서 미리보기·다운로드) 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
-      <c r="M40" s="35" t="inlineStr">
+      <c r="M39" s="35" t="inlineStr">
         <is>
           <t>화면설계</t>
         </is>
       </c>
     </row>
+    <row r="40" ht="78" customHeight="1" s="48">
+      <c r="A40" s="67" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="67" t="inlineStr">
+        <is>
+          <t>ITS-PAR-06</t>
+        </is>
+      </c>
+      <c r="C40" s="67" t="inlineStr">
+        <is>
+          <t>정기 보고서 자동 생성 설정 → 열람</t>
+        </is>
+      </c>
+      <c r="D40" s="67" t="inlineStr">
+        <is>
+          <t>서비스관리자,
+일반사용자</t>
+        </is>
+      </c>
+      <c r="E40" s="67" t="inlineStr">
+        <is>
+          <t>TT-PAR-06-01</t>
+        </is>
+      </c>
+      <c r="F40" s="67" t="inlineStr">
+        <is>
+          <t>보고서 자동생성 설정</t>
+        </is>
+      </c>
+      <c r="G40" s="22" t="inlineStr">
+        <is>
+          <t>PR-PAR-008-02</t>
+        </is>
+      </c>
+      <c r="H40" s="67" t="inlineStr">
+        <is>
+          <t>UI-PAR-004-02</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>배포주기·배포일자 설정</t>
+        </is>
+      </c>
+      <c r="J40" s="1" t="inlineStr">
+        <is>
+          <t>- 배포 주기/일자 선택 후 [보고서 자동 생성]</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>서비스관리자 권한 계정</t>
+        </is>
+      </c>
+      <c r="L40" s="1" t="inlineStr">
+        <is>
+          <t>- 자동 생성 설정 저장 및 자동 생성 목록에 항목 추가</t>
+        </is>
+      </c>
+      <c r="M40" s="67" t="inlineStr">
+        <is>
+          <t>정정</t>
+        </is>
+      </c>
+    </row>
     <row r="41" ht="78" customHeight="1" s="48">
-      <c r="A41" s="67" t="n">
+      <c r="A41" s="35" t="n">
         <v>36</v>
       </c>
-      <c r="B41" s="69" t="n"/>
-      <c r="C41" s="69" t="n"/>
-      <c r="D41" s="69" t="n"/>
-      <c r="E41" s="67" t="inlineStr">
-        <is>
-          <t>TT-PAR-05-09</t>
-        </is>
-      </c>
-      <c r="F41" s="67" t="inlineStr">
-        <is>
-          <t>자주하는질문 관리</t>
-        </is>
-      </c>
-      <c r="G41" s="22" t="inlineStr">
-        <is>
-          <t>PR-PAR-010-04</t>
-        </is>
-      </c>
-      <c r="H41" s="67" t="inlineStr">
-        <is>
-          <t>UI-PAR-005-01</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>AI 추천 질의</t>
-        </is>
-      </c>
-      <c r="J41" s="1" t="inlineStr">
-        <is>
-          <t>- 자주하는질문 등록/노출 확인</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>시스템관리자 권한 계정</t>
-        </is>
-      </c>
-      <c r="L41" s="1" t="inlineStr">
-        <is>
-          <t>- 자주하는질문이 관리되고 AI 추천 질의로 노출</t>
-        </is>
-      </c>
-      <c r="M41" s="67" t="inlineStr">
-        <is>
-          <t>신규</t>
+      <c r="B41" s="68" t="n"/>
+      <c r="C41" s="68" t="n"/>
+      <c r="D41" s="68" t="n"/>
+      <c r="E41" s="35" t="inlineStr">
+        <is>
+          <t>TT-PAR-06-02</t>
+        </is>
+      </c>
+      <c r="F41" s="35" t="inlineStr">
+        <is>
+          <t>[화면] 보고서 관리</t>
+        </is>
+      </c>
+      <c r="G41" s="36" t="inlineStr">
+        <is>
+          <t>PR-PAR-008-02</t>
+        </is>
+      </c>
+      <c r="H41" s="35" t="inlineStr">
+        <is>
+          <t>UI-PAR-004-02</t>
+        </is>
+      </c>
+      <c r="I41" s="37" t="inlineStr">
+        <is>
+          <t>민원 분석 결과 보고서 자동 생성 관리(관리자 전용)
+(화면설계 점검)</t>
+        </is>
+      </c>
+      <c r="J41" s="38" t="inlineStr">
+        <is>
+          <t>- 자동 생성 설정(배포부서/배포주기/배포일자 드롭다운·자동생성 버튼)
+- 자동 생성 설정 목록(조회·수정·삭제)</t>
+        </is>
+      </c>
+      <c r="K41" s="39" t="inlineStr">
+        <is>
+          <t>서비스관리자 권한 계정</t>
+        </is>
+      </c>
+      <c r="L41" s="38" t="inlineStr">
+        <is>
+          <t>- 보고서 관리 화면의 설계 기능이 모두 정상 표출·동작</t>
+        </is>
+      </c>
+      <c r="M41" s="35" t="inlineStr">
+        <is>
+          <t>화면설계</t>
         </is>
       </c>
     </row>
@@ -11240,60 +11219,47 @@
       <c r="A42" s="67" t="n">
         <v>37</v>
       </c>
-      <c r="B42" s="67" t="inlineStr">
-        <is>
-          <t>ITS-PAR-06</t>
-        </is>
-      </c>
-      <c r="C42" s="67" t="inlineStr">
-        <is>
-          <t>정기 보고서 자동 생성 설정 → 열람</t>
-        </is>
-      </c>
-      <c r="D42" s="67" t="inlineStr">
-        <is>
-          <t>서비스관리자,
-일반사용자</t>
-        </is>
-      </c>
+      <c r="B42" s="68" t="n"/>
+      <c r="C42" s="68" t="n"/>
+      <c r="D42" s="68" t="n"/>
       <c r="E42" s="67" t="inlineStr">
         <is>
-          <t>TT-PAR-06-01</t>
+          <t>TT-PAR-06-03</t>
         </is>
       </c>
       <c r="F42" s="67" t="inlineStr">
         <is>
-          <t>보고서 자동생성 설정</t>
+          <t>보고서 목록 조회·열람</t>
         </is>
       </c>
       <c r="G42" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-008-02</t>
+          <t>PR-PAR-008-01</t>
         </is>
       </c>
       <c r="H42" s="67" t="inlineStr">
         <is>
-          <t>UI-PAR-004-02</t>
+          <t>UI-PAR-004-01</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>배포주기·배포일자 설정</t>
+          <t>미리보기·다운로드·열람</t>
         </is>
       </c>
       <c r="J42" s="1" t="inlineStr">
         <is>
-          <t>- 배포 주기/일자 선택 후 [보고서 자동 생성]</t>
+          <t>- [미리보기] 후 [PDF] 다운로드</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>서비스관리자 권한 계정</t>
+          <t>교통행정과 담당자 권한 계정</t>
         </is>
       </c>
       <c r="L42" s="1" t="inlineStr">
         <is>
-          <t>- 자동 생성 설정 저장 및 자동 생성 목록에 항목 추가</t>
+          <t>- 미리보기 팝업 표출 및 PDF 다운로드</t>
         </is>
       </c>
       <c r="M42" s="67" t="inlineStr">
@@ -11306,49 +11272,49 @@
       <c r="A43" s="35" t="n">
         <v>38</v>
       </c>
-      <c r="B43" s="68" t="n"/>
-      <c r="C43" s="68" t="n"/>
-      <c r="D43" s="68" t="n"/>
+      <c r="B43" s="69" t="n"/>
+      <c r="C43" s="69" t="n"/>
+      <c r="D43" s="69" t="n"/>
       <c r="E43" s="35" t="inlineStr">
         <is>
-          <t>TT-PAR-06-02</t>
+          <t>TT-PAR-06-04</t>
         </is>
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>[화면] 보고서 관리</t>
+          <t>[화면] 보고서 목록</t>
         </is>
       </c>
       <c r="G43" s="36" t="inlineStr">
         <is>
-          <t>PR-PAR-008-02</t>
+          <t>PR-PAR-008-01</t>
         </is>
       </c>
       <c r="H43" s="35" t="inlineStr">
         <is>
-          <t>UI-PAR-004-02</t>
+          <t>UI-PAR-004-01</t>
         </is>
       </c>
       <c r="I43" s="37" t="inlineStr">
         <is>
-          <t>민원 분석 결과 보고서 자동 생성 관리(관리자 전용)
+          <t>민원 분석 결과 보고서 목록 조회
 (화면설계 점검)</t>
         </is>
       </c>
       <c r="J43" s="38" t="inlineStr">
         <is>
-          <t>- 자동 생성 설정(배포부서/배포주기/배포일자 드롭다운·자동생성 버튼)
-- 자동 생성 설정 목록(조회·수정·삭제)</t>
+          <t>- 자동생성 보고서 목록(보고서명/배포주기/생성자/부서/생성일/상태·미리보기·PDF·DOCX)
+- 직접생성 보고서 목록(내보내기 출처/분석기간/생성자/부서·미리보기·다운로드)</t>
         </is>
       </c>
       <c r="K43" s="39" t="inlineStr">
         <is>
-          <t>서비스관리자 권한 계정</t>
+          <t>일반사용자 권한 계정</t>
         </is>
       </c>
       <c r="L43" s="38" t="inlineStr">
         <is>
-          <t>- 보고서 관리 화면의 설계 기능이 모두 정상 표출·동작</t>
+          <t>- 보고서 목록 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
       <c r="M43" s="35" t="inlineStr">
@@ -11361,47 +11327,61 @@
       <c r="A44" s="67" t="n">
         <v>39</v>
       </c>
-      <c r="B44" s="68" t="n"/>
-      <c r="C44" s="68" t="n"/>
-      <c r="D44" s="68" t="n"/>
+      <c r="B44" s="67" t="inlineStr">
+        <is>
+          <t>ITS-PAR-07</t>
+        </is>
+      </c>
+      <c r="C44" s="67" t="inlineStr">
+        <is>
+          <t>감시 솔루션 데이터 융합(AI 어시스턴트 질의) → 통합분석 → 보고서</t>
+        </is>
+      </c>
+      <c r="D44" s="67" t="inlineStr">
+        <is>
+          <t>서비스관리자,
+일반사용자</t>
+        </is>
+      </c>
       <c r="E44" s="67" t="inlineStr">
         <is>
-          <t>TT-PAR-06-03</t>
+          <t>TT-PAR-07-01</t>
         </is>
       </c>
       <c r="F44" s="67" t="inlineStr">
         <is>
-          <t>보고서 목록 조회·열람</t>
+          <t>AI 대화 세션 관리(융합 질의)</t>
         </is>
       </c>
       <c r="G44" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-008-01</t>
+          <t>PR-PAR-010-01</t>
         </is>
       </c>
       <c r="H44" s="67" t="inlineStr">
         <is>
-          <t>UI-PAR-004-01</t>
+          <t>UI-PAR-005-04</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>미리보기·다운로드·열람</t>
+          <t>데이터 융합 질의·통합분석</t>
         </is>
       </c>
       <c r="J44" s="1" t="inlineStr">
         <is>
-          <t>- [미리보기] 후 [PDF] 다운로드</t>
+          <t>- AI 어시스턴트로 두 솔루션(주차민원+공영주차장 안전) 융합 질의
+- 상관관계·종합 인사이트 도출</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>교통행정과 담당자 권한 계정</t>
+          <t>시스템관리자 권한 계정</t>
         </is>
       </c>
       <c r="L44" s="1" t="inlineStr">
         <is>
-          <t>- 미리보기 팝업 표출 및 PDF 다운로드</t>
+          <t>- 두 솔루션 데이터가 결합되어 상관관계·종합 인사이트가 시각화</t>
         </is>
       </c>
       <c r="M44" s="67" t="inlineStr">
@@ -11414,49 +11394,46 @@
       <c r="A45" s="35" t="n">
         <v>40</v>
       </c>
-      <c r="B45" s="69" t="n"/>
-      <c r="C45" s="69" t="n"/>
-      <c r="D45" s="69" t="n"/>
+      <c r="B45" s="68" t="n"/>
+      <c r="C45" s="68" t="n"/>
+      <c r="D45" s="68" t="n"/>
       <c r="E45" s="35" t="inlineStr">
         <is>
-          <t>TT-PAR-06-04</t>
+          <t>TT-PAR-07-02</t>
         </is>
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>[화면] 보고서 목록</t>
-        </is>
-      </c>
-      <c r="G45" s="36" t="inlineStr">
-        <is>
-          <t>PR-PAR-008-01</t>
-        </is>
-      </c>
+          <t>[화면] AI 어시스턴트(통합분석)</t>
+        </is>
+      </c>
+      <c r="G45" s="36" t="n"/>
       <c r="H45" s="35" t="inlineStr">
         <is>
-          <t>UI-PAR-004-01</t>
+          <t>UI-PAR-005-04</t>
         </is>
       </c>
       <c r="I45" s="37" t="inlineStr">
         <is>
-          <t>민원 분석 결과 보고서 목록 조회
+          <t>민원데이터와 감시(화재·안전) 데이터를 결합한 통합분석
 (화면설계 점검)</t>
         </is>
       </c>
       <c r="J45" s="38" t="inlineStr">
         <is>
-          <t>- 자동생성 보고서 목록(보고서명/배포주기/생성자/부서/생성일/상태·미리보기·PDF·DOCX)
-- 직접생성 보고서 목록(내보내기 출처/분석기간/생성자/부서·미리보기·다운로드)</t>
+          <t>- 채팅 영역
+- 결합이 필요한 질문에 AI 에이전트 호출·융합 데이터에서 종합 인사이트 도출
+- 결과를 AI 어시스턴트 답변으로 표시(리포트 생성 버튼 제공)</t>
         </is>
       </c>
       <c r="K45" s="39" t="inlineStr">
         <is>
-          <t>일반사용자 권한 계정</t>
+          <t>시스템관리자 권한 계정</t>
         </is>
       </c>
       <c r="L45" s="38" t="inlineStr">
         <is>
-          <t>- 보고서 목록 화면의 설계 기능이 모두 정상 표출·동작</t>
+          <t>- AI 어시스턴트(통합분석) 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
       <c r="M45" s="35" t="inlineStr">
@@ -11469,51 +11446,37 @@
       <c r="A46" s="67" t="n">
         <v>41</v>
       </c>
-      <c r="B46" s="67" t="inlineStr">
-        <is>
-          <t>ITS-PAR-07</t>
-        </is>
-      </c>
-      <c r="C46" s="67" t="inlineStr">
-        <is>
-          <t>감시 솔루션 데이터 융합(AI 어시스턴트 질의) → 통합분석 → 보고서</t>
-        </is>
-      </c>
-      <c r="D46" s="67" t="inlineStr">
-        <is>
-          <t>서비스관리자,
-일반사용자</t>
-        </is>
-      </c>
+      <c r="B46" s="69" t="n"/>
+      <c r="C46" s="69" t="n"/>
+      <c r="D46" s="69" t="n"/>
       <c r="E46" s="67" t="inlineStr">
         <is>
-          <t>TT-PAR-07-01</t>
+          <t>TT-PAR-07-03</t>
         </is>
       </c>
       <c r="F46" s="67" t="inlineStr">
         <is>
-          <t>AI 대화 세션 관리(융합 질의)</t>
+          <t>보고서 목록 조회(반영)</t>
         </is>
       </c>
       <c r="G46" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-010-01</t>
+          <t>PR-PAR-008-01</t>
         </is>
       </c>
       <c r="H46" s="67" t="inlineStr">
         <is>
-          <t>UI-PAR-005-04</t>
+          <t>UI-PAR-004-01</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>데이터 융합 질의·통합분석</t>
+          <t>융합 분석 보고서 반영</t>
         </is>
       </c>
       <c r="J46" s="1" t="inlineStr">
         <is>
-          <t>- AI 어시스턴트로 두 솔루션(주차민원+공영주차장 안전) 융합 질의
-- 상관관계·종합 인사이트 도출</t>
+          <t>- 융합 분석 결과 보고서 내보내기·확인</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
@@ -11523,7 +11486,7 @@
       </c>
       <c r="L46" s="1" t="inlineStr">
         <is>
-          <t>- 두 솔루션 데이터가 결합되어 상관관계·종합 인사이트가 시각화</t>
+          <t>- 융합 분석 인사이트가 보고서에 반영·다운로드</t>
         </is>
       </c>
       <c r="M46" s="67" t="inlineStr">
@@ -11533,54 +11496,67 @@
       </c>
     </row>
     <row r="47" ht="78" customHeight="1" s="48">
-      <c r="A47" s="35" t="n">
+      <c r="A47" s="67" t="n">
         <v>42</v>
       </c>
-      <c r="B47" s="68" t="n"/>
-      <c r="C47" s="68" t="n"/>
-      <c r="D47" s="68" t="n"/>
-      <c r="E47" s="35" t="inlineStr">
-        <is>
-          <t>TT-PAR-07-02</t>
-        </is>
-      </c>
-      <c r="F47" s="35" t="inlineStr">
-        <is>
-          <t>[화면] AI 어시스턴트(통합분석)</t>
-        </is>
-      </c>
-      <c r="G47" s="36" t="n"/>
-      <c r="H47" s="35" t="inlineStr">
-        <is>
-          <t>UI-PAR-005-04</t>
-        </is>
-      </c>
-      <c r="I47" s="37" t="inlineStr">
-        <is>
-          <t>민원데이터와 감시(화재·안전) 데이터를 결합한 통합분석
-(화면설계 점검)</t>
-        </is>
-      </c>
-      <c r="J47" s="38" t="inlineStr">
-        <is>
-          <t>- 채팅 영역
-- 결합이 필요한 질문에 AI 에이전트 호출·융합 데이터에서 종합 인사이트 도출
-- 결과를 AI 어시스턴트 답변으로 표시(리포트 생성 버튼 제공)</t>
-        </is>
-      </c>
-      <c r="K47" s="39" t="inlineStr">
+      <c r="B47" s="67" t="inlineStr">
+        <is>
+          <t>ITS-PAR-08</t>
+        </is>
+      </c>
+      <c r="C47" s="67" t="inlineStr">
+        <is>
+          <t>분석지표 가중치·설정 전환 → 기능 재검증</t>
+        </is>
+      </c>
+      <c r="D47" s="67" t="inlineStr">
+        <is>
+          <t>시스템관리자</t>
+        </is>
+      </c>
+      <c r="E47" s="67" t="inlineStr">
+        <is>
+          <t>TT-PAR-08-01</t>
+        </is>
+      </c>
+      <c r="F47" s="67" t="inlineStr">
+        <is>
+          <t>분석지표 가중치 조회</t>
+        </is>
+      </c>
+      <c r="G47" s="22" t="inlineStr">
+        <is>
+          <t>PR-PAR-011-01</t>
+        </is>
+      </c>
+      <c r="H47" s="67" t="inlineStr">
+        <is>
+          <t>UI-PAR-006-03</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>분석모델별 지표·가중치 조회</t>
+        </is>
+      </c>
+      <c r="J47" s="1" t="inlineStr">
+        <is>
+          <t>- 분석지표 가중치 화면 진입, 분석모델별 지표·가중치 목록 확인</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
       </c>
-      <c r="L47" s="38" t="inlineStr">
-        <is>
-          <t>- AI 어시스턴트(통합분석) 화면의 설계 기능이 모두 정상 표출·동작</t>
-        </is>
-      </c>
-      <c r="M47" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="L47" s="1" t="inlineStr">
+        <is>
+          <t>- 분석모델별 지표·가중치가 정상 조회</t>
+        </is>
+      </c>
+      <c r="M47" s="67" t="inlineStr">
+        <is>
+          <t>신규</t>
         </is>
       </c>
     </row>
@@ -11588,37 +11564,37 @@
       <c r="A48" s="67" t="n">
         <v>43</v>
       </c>
-      <c r="B48" s="69" t="n"/>
-      <c r="C48" s="69" t="n"/>
-      <c r="D48" s="69" t="n"/>
+      <c r="B48" s="68" t="n"/>
+      <c r="C48" s="68" t="n"/>
+      <c r="D48" s="68" t="n"/>
       <c r="E48" s="67" t="inlineStr">
         <is>
-          <t>TT-PAR-07-03</t>
+          <t>TT-PAR-08-02</t>
         </is>
       </c>
       <c r="F48" s="67" t="inlineStr">
         <is>
-          <t>보고서 목록 조회(반영)</t>
+          <t>분석지표 가중치 저장</t>
         </is>
       </c>
       <c r="G48" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-008-01</t>
+          <t>PR-PAR-011-02</t>
         </is>
       </c>
       <c r="H48" s="67" t="inlineStr">
         <is>
-          <t>UI-PAR-004-01</t>
+          <t>UI-PAR-006-03</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>융합 분석 보고서 반영</t>
+          <t>타 지자체 기준 가중치 변경·저장(확산)</t>
         </is>
       </c>
       <c r="J48" s="1" t="inlineStr">
         <is>
-          <t>- 융합 분석 결과 보고서 내보내기·확인</t>
+          <t>- 대상 지역 여건에 맞는 지표·가중치로 변경 후 저장</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
@@ -11628,12 +11604,12 @@
       </c>
       <c r="L48" s="1" t="inlineStr">
         <is>
-          <t>- 융합 분석 인사이트가 보고서에 반영·다운로드</t>
+          <t>- 변경 가중치가 저장되고 변경이력이 함께 기록</t>
         </is>
       </c>
       <c r="M48" s="67" t="inlineStr">
         <is>
-          <t>정정</t>
+          <t>신규</t>
         </is>
       </c>
     </row>
@@ -11641,34 +11617,22 @@
       <c r="A49" s="67" t="n">
         <v>44</v>
       </c>
-      <c r="B49" s="67" t="inlineStr">
-        <is>
-          <t>ITS-PAR-08</t>
-        </is>
-      </c>
-      <c r="C49" s="67" t="inlineStr">
-        <is>
-          <t>분석지표 가중치·설정 전환 → 기능 재검증</t>
-        </is>
-      </c>
-      <c r="D49" s="67" t="inlineStr">
-        <is>
-          <t>시스템관리자</t>
-        </is>
-      </c>
+      <c r="B49" s="68" t="n"/>
+      <c r="C49" s="68" t="n"/>
+      <c r="D49" s="68" t="n"/>
       <c r="E49" s="67" t="inlineStr">
         <is>
-          <t>TT-PAR-08-01</t>
+          <t>TT-PAR-08-03</t>
         </is>
       </c>
       <c r="F49" s="67" t="inlineStr">
         <is>
-          <t>분석지표 가중치 조회</t>
+          <t>가중치 변경이력 조회</t>
         </is>
       </c>
       <c r="G49" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-011-01</t>
+          <t>PR-PAR-011-03</t>
         </is>
       </c>
       <c r="H49" s="67" t="inlineStr">
@@ -11678,12 +11642,12 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>분석모델별 지표·가중치 조회</t>
+          <t>변경이력 조회</t>
         </is>
       </c>
       <c r="J49" s="1" t="inlineStr">
         <is>
-          <t>- 분석지표 가중치 화면 진입, 분석모델별 지표·가중치 목록 확인</t>
+          <t>- 변경항목·내용·사유·변경자 확인</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
@@ -11693,7 +11657,7 @@
       </c>
       <c r="L49" s="1" t="inlineStr">
         <is>
-          <t>- 분석모델별 지표·가중치가 정상 조회</t>
+          <t>- 가중치 변경이력이 항목·사유·변경자와 함께 표출</t>
         </is>
       </c>
       <c r="M49" s="67" t="inlineStr">
@@ -11711,17 +11675,17 @@
       <c r="D50" s="68" t="n"/>
       <c r="E50" s="67" t="inlineStr">
         <is>
-          <t>TT-PAR-08-02</t>
+          <t>TT-PAR-08-04</t>
         </is>
       </c>
       <c r="F50" s="67" t="inlineStr">
         <is>
-          <t>분석지표 가중치 저장</t>
+          <t>가중치 설정 롤백</t>
         </is>
       </c>
       <c r="G50" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-011-02</t>
+          <t>PR-PAR-011-04</t>
         </is>
       </c>
       <c r="H50" s="67" t="inlineStr">
@@ -11731,12 +11695,12 @@
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>타 지자체 기준 가중치 변경·저장(확산)</t>
+          <t>이전 설정 롤백</t>
         </is>
       </c>
       <c r="J50" s="1" t="inlineStr">
         <is>
-          <t>- 대상 지역 여건에 맞는 지표·가중치로 변경 후 저장</t>
+          <t>- 특정 변경이력 선택 후 롤백</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
@@ -11746,7 +11710,7 @@
       </c>
       <c r="L50" s="1" t="inlineStr">
         <is>
-          <t>- 변경 가중치가 저장되고 변경이력이 함께 기록</t>
+          <t>- 이전 가중치 설정으로 정상 복원</t>
         </is>
       </c>
       <c r="M50" s="67" t="inlineStr">
@@ -11756,55 +11720,59 @@
       </c>
     </row>
     <row r="51" ht="78" customHeight="1" s="48">
-      <c r="A51" s="67" t="n">
+      <c r="A51" s="35" t="n">
         <v>46</v>
       </c>
       <c r="B51" s="68" t="n"/>
       <c r="C51" s="68" t="n"/>
       <c r="D51" s="68" t="n"/>
-      <c r="E51" s="67" t="inlineStr">
-        <is>
-          <t>TT-PAR-08-03</t>
-        </is>
-      </c>
-      <c r="F51" s="67" t="inlineStr">
-        <is>
-          <t>가중치 변경이력 조회</t>
-        </is>
-      </c>
-      <c r="G51" s="22" t="inlineStr">
-        <is>
-          <t>PR-PAR-011-03</t>
-        </is>
-      </c>
-      <c r="H51" s="67" t="inlineStr">
+      <c r="E51" s="35" t="inlineStr">
+        <is>
+          <t>TT-PAR-08-05</t>
+        </is>
+      </c>
+      <c r="F51" s="35" t="inlineStr">
+        <is>
+          <t>[화면] 설정_분석지표 가중치설정</t>
+        </is>
+      </c>
+      <c r="G51" s="36" t="inlineStr">
+        <is>
+          <t>PR-PAR-011-01~04</t>
+        </is>
+      </c>
+      <c r="H51" s="35" t="inlineStr">
         <is>
           <t>UI-PAR-006-03</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>변경이력 조회</t>
-        </is>
-      </c>
-      <c r="J51" s="1" t="inlineStr">
-        <is>
-          <t>- 변경항목·내용·사유·변경자 확인</t>
-        </is>
-      </c>
-      <c r="K51" s="5" t="inlineStr">
+      <c r="I51" s="37" t="inlineStr">
+        <is>
+          <t>분석지표 가중치를 지역 여건에 맞게 조정·이력 관리
+(화면설계 점검)</t>
+        </is>
+      </c>
+      <c r="J51" s="38" t="inlineStr">
+        <is>
+          <t>- 분석유형별 탭 가중치 조절
+- 가중치 변경 이력 표시
+- 설정 저장(변경 내용 이력 기록)
+- 기본값 초기화(롤백)</t>
+        </is>
+      </c>
+      <c r="K51" s="39" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
       </c>
-      <c r="L51" s="1" t="inlineStr">
-        <is>
-          <t>- 가중치 변경이력이 항목·사유·변경자와 함께 표출</t>
-        </is>
-      </c>
-      <c r="M51" s="67" t="inlineStr">
-        <is>
-          <t>신규</t>
+      <c r="L51" s="38" t="inlineStr">
+        <is>
+          <t>- 설정_분석지표 가중치설정 화면의 설계 기능이 모두 정상 표출·동작</t>
+        </is>
+      </c>
+      <c r="M51" s="35" t="inlineStr">
+        <is>
+          <t>화면설계</t>
         </is>
       </c>
     </row>
@@ -11817,32 +11785,32 @@
       <c r="D52" s="68" t="n"/>
       <c r="E52" s="67" t="inlineStr">
         <is>
-          <t>TT-PAR-08-04</t>
+          <t>TT-PAR-08-06</t>
         </is>
       </c>
       <c r="F52" s="67" t="inlineStr">
         <is>
-          <t>가중치 설정 롤백</t>
+          <t>메뉴별 권한 조회</t>
         </is>
       </c>
       <c r="G52" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-011-04</t>
+          <t>PR-CMM-003-01</t>
         </is>
       </c>
       <c r="H52" s="67" t="inlineStr">
         <is>
-          <t>UI-PAR-006-03</t>
+          <t>UI-PAR-006-02</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>이전 설정 롤백</t>
+          <t>권한별 메뉴 권한 조회</t>
         </is>
       </c>
       <c r="J52" s="1" t="inlineStr">
         <is>
-          <t>- 특정 변경이력 선택 후 롤백</t>
+          <t>- 좌측 기등록 메뉴목록·우측 권한별 체크 상태 확인</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
@@ -11852,7 +11820,7 @@
       </c>
       <c r="L52" s="1" t="inlineStr">
         <is>
-          <t>- 이전 가중치 설정으로 정상 복원</t>
+          <t>- 권한별 메뉴 권한 부여 현황이 정상 조회</t>
         </is>
       </c>
       <c r="M52" s="67" t="inlineStr">
@@ -11862,112 +11830,111 @@
       </c>
     </row>
     <row r="53" ht="78" customHeight="1" s="48">
-      <c r="A53" s="35" t="n">
+      <c r="A53" s="67" t="n">
         <v>48</v>
       </c>
       <c r="B53" s="68" t="n"/>
       <c r="C53" s="68" t="n"/>
       <c r="D53" s="68" t="n"/>
-      <c r="E53" s="35" t="inlineStr">
-        <is>
-          <t>TT-PAR-08-05</t>
-        </is>
-      </c>
-      <c r="F53" s="35" t="inlineStr">
-        <is>
-          <t>[화면] 설정_분석지표 가중치설정</t>
-        </is>
-      </c>
-      <c r="G53" s="36" t="inlineStr">
-        <is>
-          <t>PR-PAR-011-01~04</t>
-        </is>
-      </c>
-      <c r="H53" s="35" t="inlineStr">
-        <is>
-          <t>UI-PAR-006-03</t>
-        </is>
-      </c>
-      <c r="I53" s="37" t="inlineStr">
-        <is>
-          <t>분석지표 가중치를 지역 여건에 맞게 조정·이력 관리
-(화면설계 점검)</t>
-        </is>
-      </c>
-      <c r="J53" s="38" t="inlineStr">
-        <is>
-          <t>- 분석유형별 탭 가중치 조절
-- 가중치 변경 이력 표시
-- 설정 저장(변경 내용 이력 기록)
-- 기본값 초기화(롤백)</t>
-        </is>
-      </c>
-      <c r="K53" s="39" t="inlineStr">
+      <c r="E53" s="67" t="inlineStr">
+        <is>
+          <t>TT-PAR-08-07</t>
+        </is>
+      </c>
+      <c r="F53" s="67" t="inlineStr">
+        <is>
+          <t>메뉴별 권한 설정</t>
+        </is>
+      </c>
+      <c r="G53" s="22" t="inlineStr">
+        <is>
+          <t>PR-CMM-003-02</t>
+        </is>
+      </c>
+      <c r="H53" s="67" t="inlineStr">
+        <is>
+          <t>UI-PAR-006-02</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>권한 부여·회수</t>
+        </is>
+      </c>
+      <c r="J53" s="1" t="inlineStr">
+        <is>
+          <t>- 기등록 메뉴에 권한 체크(INSERT)/해제(DELETE) 후 저장</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
       </c>
-      <c r="L53" s="38" t="inlineStr">
-        <is>
-          <t>- 설정_분석지표 가중치설정 화면의 설계 기능이 모두 정상 표출·동작</t>
-        </is>
-      </c>
-      <c r="M53" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="L53" s="1" t="inlineStr">
+        <is>
+          <t>- 체크=부여, 해제=회수가 반영되고 재로그인 시 메뉴 구성에 적용</t>
+        </is>
+      </c>
+      <c r="M53" s="67" t="inlineStr">
+        <is>
+          <t>신규</t>
         </is>
       </c>
     </row>
     <row r="54" ht="78" customHeight="1" s="48">
-      <c r="A54" s="67" t="n">
+      <c r="A54" s="35" t="n">
         <v>49</v>
       </c>
       <c r="B54" s="68" t="n"/>
       <c r="C54" s="68" t="n"/>
       <c r="D54" s="68" t="n"/>
-      <c r="E54" s="67" t="inlineStr">
-        <is>
-          <t>TT-PAR-08-06</t>
-        </is>
-      </c>
-      <c r="F54" s="67" t="inlineStr">
-        <is>
-          <t>공통코드 관리</t>
-        </is>
-      </c>
-      <c r="G54" s="22" t="inlineStr">
-        <is>
-          <t>PR-CMM-002-01</t>
-        </is>
-      </c>
-      <c r="H54" s="67" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>지역·유형 코드 설정</t>
-        </is>
-      </c>
-      <c r="J54" s="1" t="inlineStr">
-        <is>
-          <t>- 대상 지역·민원 유형 등 공통코드 등록/수정</t>
-        </is>
-      </c>
-      <c r="K54" s="5" t="inlineStr">
+      <c r="E54" s="35" t="inlineStr">
+        <is>
+          <t>TT-PAR-08-08</t>
+        </is>
+      </c>
+      <c r="F54" s="35" t="inlineStr">
+        <is>
+          <t>[화면] 설정_메뉴 권한관리</t>
+        </is>
+      </c>
+      <c r="G54" s="36" t="inlineStr">
+        <is>
+          <t>PR-CMM-003-01~02</t>
+        </is>
+      </c>
+      <c r="H54" s="35" t="inlineStr">
+        <is>
+          <t>UI-PAR-006-02</t>
+        </is>
+      </c>
+      <c r="I54" s="37" t="inlineStr">
+        <is>
+          <t>메뉴별 사용 권한그룹 지정
+(화면설계 점검)</t>
+        </is>
+      </c>
+      <c r="J54" s="38" t="inlineStr">
+        <is>
+          <t>- 메뉴별 사용 가능 권한그룹 지정 탭
+- 메뉴 클릭→오른쪽에서 권한그룹 지정(체크 부여/해제)
+- 시스템·서비스관리자 전체권한 고정, 일반사용자 체크 부여·권한 저장</t>
+        </is>
+      </c>
+      <c r="K54" s="39" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
       </c>
-      <c r="L54" s="1" t="inlineStr">
-        <is>
-          <t>- 공통코드가 저장되고 분석·화면 전반에 반영</t>
-        </is>
-      </c>
-      <c r="M54" s="67" t="inlineStr">
-        <is>
-          <t>신규</t>
+      <c r="L54" s="38" t="inlineStr">
+        <is>
+          <t>- 설정_메뉴 권한관리 화면의 설계 기능이 모두 정상 표출·동작</t>
+        </is>
+      </c>
+      <c r="M54" s="35" t="inlineStr">
+        <is>
+          <t>화면설계</t>
         </is>
       </c>
     </row>
@@ -11980,32 +11947,34 @@
       <c r="D55" s="68" t="n"/>
       <c r="E55" s="67" t="inlineStr">
         <is>
-          <t>TT-PAR-08-07</t>
+          <t>TT-PAR-08-09</t>
         </is>
       </c>
       <c r="F55" s="67" t="inlineStr">
         <is>
-          <t>메뉴별 권한 조회</t>
+          <t>메뉴 권한 관리 조회</t>
         </is>
       </c>
       <c r="G55" s="22" t="inlineStr">
         <is>
-          <t>PR-CMM-003-01</t>
+          <t>미정의(메뉴 권한 관리)</t>
         </is>
       </c>
       <c r="H55" s="67" t="inlineStr">
         <is>
-          <t>UI-PAR-006-02</t>
+          <t>UI-PAR-006-01</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>권한별 메뉴 권한 조회</t>
+          <t>사용자 계정·권한그룹 현황 조회</t>
         </is>
       </c>
       <c r="J55" s="1" t="inlineStr">
         <is>
-          <t>- 좌측 기등록 메뉴목록·우측 권한별 체크 상태 확인</t>
+          <t>- 설정&gt;메뉴 권한 관리 탭 진입
+- 메뉴 선택 후 권한 그룹 지정 상태 확인
+- 메뉴 단위 저장</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
@@ -12015,7 +11984,7 @@
       </c>
       <c r="L55" s="1" t="inlineStr">
         <is>
-          <t>- 권한별 메뉴 권한 부여 현황이 정상 조회</t>
+          <t>- 사용자 계정 현황이 권한그룹별로 조회되고 검색·필터 정상 동작</t>
         </is>
       </c>
       <c r="M55" s="67" t="inlineStr">
@@ -12025,199 +11994,35 @@
       </c>
     </row>
     <row r="56" ht="78" customHeight="1" s="48">
-      <c r="A56" s="67" t="n">
+      <c r="A56" s="35" t="n">
         <v>51</v>
       </c>
       <c r="B56" s="68" t="n"/>
       <c r="C56" s="68" t="n"/>
       <c r="D56" s="68" t="n"/>
-      <c r="E56" s="67" t="inlineStr">
-        <is>
-          <t>TT-PAR-08-08</t>
-        </is>
-      </c>
-      <c r="F56" s="67" t="inlineStr">
-        <is>
-          <t>메뉴별 권한 설정</t>
-        </is>
-      </c>
-      <c r="G56" s="22" t="inlineStr">
-        <is>
-          <t>PR-CMM-003-02</t>
-        </is>
-      </c>
-      <c r="H56" s="67" t="inlineStr">
-        <is>
-          <t>UI-PAR-006-02</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t>권한 부여·회수</t>
-        </is>
-      </c>
-      <c r="J56" s="1" t="inlineStr">
-        <is>
-          <t>- 기등록 메뉴에 권한 체크(INSERT)/해제(DELETE) 후 저장</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="inlineStr">
-        <is>
-          <t>시스템관리자 권한 계정</t>
-        </is>
-      </c>
-      <c r="L56" s="1" t="inlineStr">
-        <is>
-          <t>- 체크=부여, 해제=회수가 반영되고 재로그인 시 메뉴 구성에 적용</t>
-        </is>
-      </c>
-      <c r="M56" s="67" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="78" customHeight="1" s="48">
-      <c r="A57" s="35" t="n">
-        <v>52</v>
-      </c>
-      <c r="B57" s="68" t="n"/>
-      <c r="C57" s="68" t="n"/>
-      <c r="D57" s="68" t="n"/>
-      <c r="E57" s="35" t="inlineStr">
-        <is>
-          <t>TT-PAR-08-09</t>
-        </is>
-      </c>
-      <c r="F57" s="35" t="inlineStr">
-        <is>
-          <t>[화면] 설정_메뉴 권한관리</t>
-        </is>
-      </c>
-      <c r="G57" s="36" t="inlineStr">
-        <is>
-          <t>PR-CMM-003-01~02</t>
-        </is>
-      </c>
-      <c r="H57" s="35" t="inlineStr">
-        <is>
-          <t>UI-PAR-006-02</t>
-        </is>
-      </c>
-      <c r="I57" s="37" t="inlineStr">
-        <is>
-          <t>메뉴별 사용 권한그룹 지정
-(화면설계 점검)</t>
-        </is>
-      </c>
-      <c r="J57" s="38" t="inlineStr">
-        <is>
-          <t>- 메뉴별 사용 가능 권한그룹 지정 탭
-- 메뉴 클릭→오른쪽에서 권한그룹 지정(체크 부여/해제)
-- 시스템·서비스관리자 전체권한 고정, 일반사용자 체크 부여·권한 저장</t>
-        </is>
-      </c>
-      <c r="K57" s="39" t="inlineStr">
-        <is>
-          <t>시스템관리자 권한 계정</t>
-        </is>
-      </c>
-      <c r="L57" s="38" t="inlineStr">
-        <is>
-          <t>- 설정_메뉴 권한관리 화면의 설계 기능이 모두 정상 표출·동작</t>
-        </is>
-      </c>
-      <c r="M57" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="78" customHeight="1" s="48">
-      <c r="A58" s="67" t="n">
-        <v>53</v>
-      </c>
-      <c r="B58" s="68" t="n"/>
-      <c r="C58" s="68" t="n"/>
-      <c r="D58" s="68" t="n"/>
-      <c r="E58" s="67" t="inlineStr">
+      <c r="E56" s="35" t="inlineStr">
         <is>
           <t>TT-PAR-08-10</t>
         </is>
       </c>
-      <c r="F58" s="67" t="inlineStr">
-        <is>
-          <t>메뉴 권한 관리 조회</t>
-        </is>
-      </c>
-      <c r="G58" s="22" t="inlineStr">
-        <is>
-          <t>미정의(메뉴 권한 관리)</t>
-        </is>
-      </c>
-      <c r="H58" s="67" t="inlineStr">
+      <c r="F56" s="35" t="inlineStr">
+        <is>
+          <t>[화면] 설정_메뉴 권한 관리</t>
+        </is>
+      </c>
+      <c r="G56" s="36" t="n"/>
+      <c r="H56" s="35" t="inlineStr">
         <is>
           <t>UI-PAR-006-01</t>
         </is>
       </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>사용자 계정·권한그룹 현황 조회</t>
-        </is>
-      </c>
-      <c r="J58" s="1" t="inlineStr">
-        <is>
-          <t>- 설정&gt;메뉴 권한 관리 탭 진입
-- 메뉴 선택 후 권한 그룹 지정 상태 확인
-- 메뉴 단위 저장</t>
-        </is>
-      </c>
-      <c r="K58" s="5" t="inlineStr">
-        <is>
-          <t>시스템관리자 권한 계정</t>
-        </is>
-      </c>
-      <c r="L58" s="1" t="inlineStr">
-        <is>
-          <t>- 사용자 계정 현황이 권한그룹별로 조회되고 검색·필터 정상 동작</t>
-        </is>
-      </c>
-      <c r="M58" s="67" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="78" customHeight="1" s="48">
-      <c r="A59" s="35" t="n">
-        <v>54</v>
-      </c>
-      <c r="B59" s="68" t="n"/>
-      <c r="C59" s="68" t="n"/>
-      <c r="D59" s="68" t="n"/>
-      <c r="E59" s="35" t="inlineStr">
-        <is>
-          <t>TT-PAR-08-11</t>
-        </is>
-      </c>
-      <c r="F59" s="35" t="inlineStr">
-        <is>
-          <t>[화면] 설정_메뉴 권한 관리</t>
-        </is>
-      </c>
-      <c r="G59" s="36" t="n"/>
-      <c r="H59" s="35" t="inlineStr">
-        <is>
-          <t>UI-PAR-006-01</t>
-        </is>
-      </c>
-      <c r="I59" s="37" t="inlineStr">
+      <c r="I56" s="37" t="inlineStr">
         <is>
           <t>사용자 계정 현황 조회·권한그룹별 관리
 (화면설계 점검)</t>
         </is>
       </c>
-      <c r="J59" s="38" t="inlineStr">
+      <c r="J56" s="38" t="inlineStr">
         <is>
           <t>- 메뉴 권한 관리/분석 지표 가중치 설정 2개 탭
 - 메뉴별 권한 그룹 지정(시스템 관리자 항상 허용, 일반 사용자 관리 메뉴 부여 불가)
@@ -12225,181 +12030,184 @@
 - 메뉴 단위 저장</t>
         </is>
       </c>
-      <c r="K59" s="39" t="inlineStr">
+      <c r="K56" s="39" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
       </c>
-      <c r="L59" s="38" t="inlineStr">
+      <c r="L56" s="38" t="inlineStr">
         <is>
           <t>- 설정_메뉴 권한 관리 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
-      <c r="M59" s="35" t="inlineStr">
+      <c r="M56" s="35" t="inlineStr">
         <is>
           <t>화면설계</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="78" customHeight="1" s="48">
-      <c r="A60" s="67" t="n">
-        <v>55</v>
-      </c>
-      <c r="B60" s="69" t="n"/>
-      <c r="C60" s="69" t="n"/>
-      <c r="D60" s="69" t="n"/>
-      <c r="E60" s="67" t="inlineStr">
-        <is>
-          <t>TT-PAR-08-12</t>
-        </is>
-      </c>
-      <c r="F60" s="67" t="inlineStr">
+    <row r="57" ht="78" customHeight="1" s="48">
+      <c r="A57" s="67" t="n">
+        <v>52</v>
+      </c>
+      <c r="B57" s="69" t="n"/>
+      <c r="C57" s="69" t="n"/>
+      <c r="D57" s="69" t="n"/>
+      <c r="E57" s="67" t="inlineStr">
+        <is>
+          <t>TT-PAR-08-11</t>
+        </is>
+      </c>
+      <c r="F57" s="67" t="inlineStr">
         <is>
           <t>설정 전환 후 기능 재검증</t>
         </is>
       </c>
-      <c r="G60" s="22" t="inlineStr">
+      <c r="G57" s="22" t="inlineStr">
         <is>
           <t>PR-PAR-003-01 외 주요 분석</t>
         </is>
       </c>
-      <c r="H60" s="67" t="inlineStr">
+      <c r="H57" s="67" t="inlineStr">
         <is>
           <t>UI-PAR-003</t>
         </is>
       </c>
-      <c r="I60" s="3" t="inlineStr">
+      <c r="I57" s="3" t="inlineStr">
         <is>
           <t>설정 전환 후 주요 분석 재실행</t>
         </is>
       </c>
-      <c r="J60" s="1" t="inlineStr">
+      <c r="J57" s="1" t="inlineStr">
         <is>
           <t>- 변경된 지역·가중치·권한 기준으로 집중구역/시뮬레이션/투자우선순위 재실행</t>
         </is>
       </c>
-      <c r="K60" s="5" t="inlineStr">
+      <c r="K57" s="5" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
       </c>
-      <c r="L60" s="1" t="inlineStr">
+      <c r="L57" s="1" t="inlineStr">
         <is>
           <t>- 변경 설정 기준으로 주요 분석 기능이 오류 없이 정상 동작</t>
         </is>
       </c>
-      <c r="M60" s="67" t="inlineStr">
+      <c r="M57" s="67" t="inlineStr">
         <is>
           <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="78" customHeight="1" s="48">
-      <c r="A61" s="67" t="n">
-        <v>56</v>
-      </c>
-      <c r="B61" s="67" t="inlineStr">
+    <row r="58" ht="78" customHeight="1" s="48">
+      <c r="A58" s="67" t="n">
+        <v>53</v>
+      </c>
+      <c r="B58" s="67" t="inlineStr">
         <is>
           <t>ITS-PAR-09</t>
         </is>
       </c>
-      <c r="C61" s="67" t="inlineStr">
+      <c r="C58" s="67" t="inlineStr">
         <is>
           <t>예외·비정상 흐름 검증(권한)</t>
         </is>
       </c>
-      <c r="D61" s="67" t="inlineStr">
+      <c r="D58" s="67" t="inlineStr">
         <is>
           <t>시스템관리자,
 서비스관리자,
 일반사용자</t>
         </is>
       </c>
-      <c r="E61" s="67" t="inlineStr">
+      <c r="E58" s="67" t="inlineStr">
         <is>
           <t>TT-PAR-09-01</t>
         </is>
       </c>
-      <c r="F61" s="67" t="inlineStr">
+      <c r="F58" s="67" t="inlineStr">
         <is>
           <t>권한 범위 초과 접근 차단</t>
         </is>
       </c>
-      <c r="G61" s="22" t="inlineStr">
+      <c r="G58" s="22" t="inlineStr">
         <is>
           <t>PR-CMM-003-03</t>
         </is>
       </c>
-      <c r="H61" s="67" t="inlineStr">
+      <c r="H58" s="67" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="I61" s="3" t="inlineStr">
+      <c r="I58" s="3" t="inlineStr">
         <is>
           <t>비인가 접근 차단</t>
         </is>
       </c>
-      <c r="J61" s="1" t="inlineStr">
+      <c r="J58" s="1" t="inlineStr">
         <is>
           <t>- 비인가·타 부서 권한 계정으로 관리 기능/데이터 접근 시도</t>
         </is>
       </c>
-      <c r="K61" s="5" t="inlineStr">
+      <c r="K58" s="5" t="inlineStr">
         <is>
           <t>일반사용자 권한 계정</t>
         </is>
       </c>
-      <c r="L61" s="1" t="inlineStr">
+      <c r="L58" s="1" t="inlineStr">
         <is>
           <t>- 권한 범위 초과 접근이 차단되고 안내 메시지 표출</t>
         </is>
       </c>
-      <c r="M61" s="67" t="inlineStr">
+      <c r="M58" s="67" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
     </row>
+    <row r="59" ht="78" customHeight="1" s="48"/>
+    <row r="60" ht="78" customHeight="1" s="48"/>
+    <row r="61" ht="78" customHeight="1" s="48"/>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="B49:B60"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="E4:E5"/>
-    <mergeCell ref="C42:C45"/>
     <mergeCell ref="B30:B32"/>
-    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="D40:D43"/>
+    <mergeCell ref="C47:C57"/>
     <mergeCell ref="D30:D32"/>
-    <mergeCell ref="C49:C60"/>
     <mergeCell ref="D25:D29"/>
     <mergeCell ref="D4:D5"/>
+    <mergeCell ref="D47:D57"/>
     <mergeCell ref="J4:J5"/>
+    <mergeCell ref="D44:D46"/>
     <mergeCell ref="L4:L5"/>
+    <mergeCell ref="B33:B39"/>
+    <mergeCell ref="D33:D39"/>
     <mergeCell ref="B6:B16"/>
-    <mergeCell ref="D33:D41"/>
-    <mergeCell ref="D49:D60"/>
+    <mergeCell ref="C40:C43"/>
     <mergeCell ref="B17:B24"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="D17:D24"/>
-    <mergeCell ref="B33:B41"/>
+    <mergeCell ref="B40:B43"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="B25:B29"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="K4:K5"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="C33:C39"/>
+    <mergeCell ref="C44:C46"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C33:C41"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="C17:C24"/>
+    <mergeCell ref="B47:B57"/>
+    <mergeCell ref="B44:B46"/>
     <mergeCell ref="H4:H5"/>
     <mergeCell ref="C25:C29"/>
-    <mergeCell ref="D42:D45"/>
     <mergeCell ref="C6:C16"/>
     <mergeCell ref="D6:D16"/>
-    <mergeCell ref="C46:C48"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12412,7 +12220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S44"/>
+  <dimension ref="A2:S39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="5.125" customWidth="1" style="2" min="1" max="1"/>
@@ -12433,7 +12241,6 @@
     <col width="9" customWidth="1" style="4" min="19" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="41.25" customFormat="1" customHeight="1" s="83">
       <c r="A2" s="72" t="inlineStr">
         <is>
@@ -12733,19 +12540,19 @@
       <c r="A9" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="76" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>TT-PAR-A01-02</t>
         </is>
       </c>
-      <c r="C9" s="76" t="inlineStr">
-        <is>
-          <t>민원 데이터 연계·수집</t>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>민원 데이터 수집 반영</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-04</t>
+          <t>PR-PAR-A01-07</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -12755,7 +12562,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>민원 원천 데이터 Open API 수집</t>
+          <t>수집 결과 대시보드 반영</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
@@ -12763,8 +12570,8 @@
       </c>
       <c r="H9" s="1" t="inlineStr">
         <is>
-          <t>- 120만덕콜센터·국민신문고·안전신문고 연계 배치 수행
-- 수집 로그 및 적재 건수 확인</t>
+          <t>- 배치 완료 후 대시보드 재진입
+- 최근 갱신 일시 및 KPI 수치 확인</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -12774,7 +12581,7 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>- 민원 3종 데이터가 오류 없이 수집·정제되어 적재</t>
+          <t>- 최근 갱신 일시이 갱신되고 KPI 수치가 수집 결과와 일치</t>
         </is>
       </c>
       <c r="K9" s="3" t="n"/>
@@ -12785,7 +12592,8 @@
       <c r="P9" s="31" t="n"/>
       <c r="Q9" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-005-02</t>
+          <t>REQ-SFR-003-07
+REQ-SFR-005-02</t>
         </is>
       </c>
     </row>
@@ -12793,11 +12601,19 @@
       <c r="A10" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="68" t="n"/>
-      <c r="C10" s="68" t="n"/>
+      <c r="B10" s="76" t="inlineStr">
+        <is>
+          <t>TT-PAR-A01-03</t>
+        </is>
+      </c>
+      <c r="C10" s="76" t="inlineStr">
+        <is>
+          <t>민원현황 GIS 조회</t>
+        </is>
+      </c>
       <c r="D10" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-05</t>
+          <t>PR-PAR-A01-08</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -12805,18 +12621,18 @@
           <t>UI-PAR-002</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>불법주정차 민원·단속 데이터 연계</t>
+      <c r="F10" s="73" t="inlineStr">
+        <is>
+          <t>자세히 보기 이동 및 조회조건 승계</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
-          <t>- 민원처리시스템 / 단속관리시스템 Open API 호출
-- 수집 건수 및 좌표 매핑 확인</t>
+          <t>- 대시보드 '불법주차 집중구역 순위' 영역의 [자세히 보기] 클릭
+- 민원현황 화면 진입 확인</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -12826,7 +12642,7 @@
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>- 민원·단속 데이터가 읍·면·동 및 좌표 기준으로 정상 매핑</t>
+          <t>- 민원현황 화면으로 이동하고 직전 조회 단위·기간 조건이 승계</t>
         </is>
       </c>
       <c r="K10" s="3" t="n"/>
@@ -12837,7 +12653,8 @@
       <c r="P10" s="31" t="n"/>
       <c r="Q10" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-005-02</t>
+          <t>REQ-SFR-003-03
+REQ-SFR-003-07</t>
         </is>
       </c>
     </row>
@@ -12849,7 +12666,7 @@
       <c r="C11" s="68" t="n"/>
       <c r="D11" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-06</t>
+          <t>PR-PAR-A01-09</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -12859,16 +12676,16 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>공영주차장 운영 데이터 연계</t>
+          <t>분석 레이어 전환</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
-          <t>- 주차관제시스템 Open API 호출
-- 공영주차장 시설물 현황 적재 확인</t>
+          <t>- 레이어 설정에서 민원 다발 지역 / 단속 집중 지역 / 수요 부족 지역을 순차 선택
+- 민원 다발·단속 집중 레이어에서 [히트맵] 전환</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -12878,7 +12695,7 @@
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>- 공영주차장 운영·시설물 데이터가 적재되고 지도에 P 마커로 표출</t>
+          <t>- 선택한 레이어 1개만 활성화되고, 히트맵 전환 시 밀도 히트맵·그라데이션 범례로 표시</t>
         </is>
       </c>
       <c r="K11" s="3" t="n"/>
@@ -12889,7 +12706,7 @@
       <c r="P11" s="31" t="n"/>
       <c r="Q11" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-005-02</t>
+          <t>REQ-SFR-003-09</t>
         </is>
       </c>
     </row>
@@ -12897,30 +12714,30 @@
       <c r="A12" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="69" t="n"/>
-      <c r="C12" s="69" t="n"/>
+      <c r="B12" s="68" t="n"/>
+      <c r="C12" s="68" t="n"/>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-07</t>
+          <t>PR-PAR-A01-10</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>UI-PAR-001</t>
+          <t>UI-PAR-002</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>수집 결과 대시보드 반영</t>
+          <t>공영주차장·행정동 경계 토글</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>- 배치 완료 후 대시보드 재진입
-- 최근 갱신 일시 및 KPI 수치 확인</t>
+          <t>- 공영주차장 토글 ON/OFF
+- 행정동 경계 토글 ON/OFF</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -12930,7 +12747,7 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>- 최근 갱신 일시이 갱신되고 KPI 수치가 수집 결과와 일치</t>
+          <t>- 공영주차장 P 마커와 행정동 경계가 각각 표시/숨김 전환</t>
         </is>
       </c>
       <c r="K12" s="3" t="n"/>
@@ -12941,8 +12758,7 @@
       <c r="P12" s="31" t="n"/>
       <c r="Q12" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-07
-REQ-SFR-005-02</t>
+          <t>REQ-SFR-003-09</t>
         </is>
       </c>
     </row>
@@ -12950,19 +12766,11 @@
       <c r="A13" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="76" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-03</t>
-        </is>
-      </c>
-      <c r="C13" s="76" t="inlineStr">
-        <is>
-          <t>민원현황 GIS 조회</t>
-        </is>
-      </c>
+      <c r="B13" s="69" t="n"/>
+      <c r="C13" s="69" t="n"/>
       <c r="D13" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-08</t>
+          <t>PR-PAR-A01-11</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -12970,18 +12778,18 @@
           <t>UI-PAR-002</t>
         </is>
       </c>
-      <c r="F13" s="73" t="inlineStr">
-        <is>
-          <t>자세히 보기 이동 및 조회조건 승계</t>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>지역별 민원현황·집중구역 순위 동기화</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H13" s="1" t="inlineStr">
         <is>
-          <t>- 대시보드 '불법주차 집중구역 순위' 영역의 [자세히 보기] 클릭
-- 민원현황 화면 진입 확인</t>
+          <t>- 조회 필터(행정구역/민원유형/위험단계) 변경
+- 우측 지역별 민원현황 및 불법주차 집중구역 순위 확인</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -12991,7 +12799,7 @@
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>- 민원현황 화면으로 이동하고 직전 조회 단위·기간 조건이 승계</t>
+          <t>- 지도·지역별 순위·집중구역 순위가 동일 조건 기준으로 동시 갱신</t>
         </is>
       </c>
       <c r="K13" s="3" t="n"/>
@@ -13002,8 +12810,7 @@
       <c r="P13" s="31" t="n"/>
       <c r="Q13" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-03
-REQ-SFR-003-07</t>
+          <t>REQ-SFR-003-03</t>
         </is>
       </c>
     </row>
@@ -13011,30 +12818,39 @@
       <c r="A14" s="32" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="68" t="n"/>
-      <c r="C14" s="68" t="n"/>
+      <c r="B14" s="76" t="inlineStr">
+        <is>
+          <t>TT-PAR-A01-04</t>
+        </is>
+      </c>
+      <c r="C14" s="76" t="inlineStr">
+        <is>
+          <t>불법주차 집중구역 분석</t>
+        </is>
+      </c>
       <c r="D14" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-09</t>
+          <t>PR-PAR-A01-12</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
         <is>
-          <t>UI-PAR-002</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>분석 레이어 전환</t>
+          <t>UI-PAR-003-01</t>
+        </is>
+      </c>
+      <c r="F14" s="73" t="inlineStr">
+        <is>
+          <t>집중구역 자동 도출 실행</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="1" t="inlineStr">
         <is>
-          <t>- 레이어 설정에서 민원 다발 지역 / 단속 집중 지역 / 수요 부족 지역을 순차 선택
-- 민원 다발·단속 집중 레이어에서 [히트맵] 전환</t>
+          <t>- 분석·시뮬레이션 &gt; 불법 주차 불법 주차 집중 구역 분석 진입
+- 분석 지역(제주시), 분석 기간(최근3개월) 설정
+- [분석 실행] 클릭</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -13044,7 +12860,7 @@
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>- 선택한 레이어 1개만 활성화되고, 히트맵 전환 시 밀도 히트맵·그라데이션 범례로 표시</t>
+          <t>- 종합점수 기준으로 집중구역이 자동 도출되어 지도·순위가 갱신</t>
         </is>
       </c>
       <c r="K14" s="3" t="n"/>
@@ -13055,7 +12871,7 @@
       <c r="P14" s="31" t="n"/>
       <c r="Q14" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-09</t>
+          <t>REQ-SFR-003-02</t>
         </is>
       </c>
     </row>
@@ -13067,26 +12883,25 @@
       <c r="C15" s="68" t="n"/>
       <c r="D15" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-10</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
-        <is>
-          <t>UI-PAR-002</t>
+          <t>PR-PAR-A01-13</t>
+        </is>
+      </c>
+      <c r="E15" s="67" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-01</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>공영주차장·행정동 경계 토글</t>
+          <t>지도 마커 상세 팝업</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="1" t="inlineStr">
         <is>
-          <t>- 공영주차장 토글 ON/OFF
-- 행정동 경계 토글 ON/OFF</t>
+          <t>- 지도상 집중구역 마커 클릭</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -13096,7 +12911,7 @@
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>- 공영주차장 P 마커와 행정동 경계가 각각 표시/숨김 전환</t>
+          <t>- 순위·구역명·민원 건수·단속 건수 팝업이 표출</t>
         </is>
       </c>
       <c r="K15" s="3" t="n"/>
@@ -13105,9 +12920,9 @@
       <c r="N15" s="3" t="n"/>
       <c r="O15" s="3" t="n"/>
       <c r="P15" s="31" t="n"/>
-      <c r="Q15" s="34" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-09</t>
+      <c r="Q15" s="67" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-02</t>
         </is>
       </c>
     </row>
@@ -13119,26 +12934,26 @@
       <c r="C16" s="69" t="n"/>
       <c r="D16" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-11</t>
-        </is>
-      </c>
-      <c r="E16" s="22" t="inlineStr">
-        <is>
-          <t>UI-PAR-002</t>
+          <t>PR-PAR-A01-14</t>
+        </is>
+      </c>
+      <c r="E16" s="67" t="inlineStr">
+        <is>
+          <t>UI-PAR-004-01</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>지역별 민원현황·집중구역 순위 동기화</t>
+          <t>분석 결과 보고서 내보내기</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
-          <t>- 조회 필터(행정구역/민원유형/위험단계) 변경
-- 우측 지역별 민원현황 및 불법주차 집중구역 순위 확인</t>
+          <t>- [내보내기] 클릭
+- 보고서·알림 &gt; 보고서 관리 진입</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -13148,7 +12963,7 @@
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>- 지도·지역별 순위·집중구역 순위가 동일 조건 기준으로 동시 갱신</t>
+          <t>- 직접 생성 보고서 목록에 보고서명·분석기간·생성일·생성자가 등록되고 PDF 다운로드 가능</t>
         </is>
       </c>
       <c r="K16" s="3" t="n"/>
@@ -13157,9 +12972,9 @@
       <c r="N16" s="3" t="n"/>
       <c r="O16" s="3" t="n"/>
       <c r="P16" s="31" t="n"/>
-      <c r="Q16" s="34" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-03</t>
+      <c r="Q16" s="67" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-10</t>
         </is>
       </c>
     </row>
@@ -13169,27 +12984,27 @@
       </c>
       <c r="B17" s="76" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-04</t>
+          <t>TT-PAR-A01-05</t>
         </is>
       </c>
       <c r="C17" s="76" t="inlineStr">
         <is>
-          <t>불법주차 집중구역 분석</t>
+          <t>정책 효과 시뮬레이션</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-12</t>
-        </is>
-      </c>
-      <c r="E17" s="22" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-01</t>
-        </is>
-      </c>
-      <c r="F17" s="73" t="inlineStr">
-        <is>
-          <t>집중구역 자동 도출 실행</t>
+          <t>PR-PAR-A01-15</t>
+        </is>
+      </c>
+      <c r="E17" s="67" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-02</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>주차장 확충 시뮬레이션 실행</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
@@ -13197,19 +13012,19 @@
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
-          <t>- 분석·시뮬레이션 &gt; 불법 주차 불법 주차 집중 구역 분석 진입
-- 분석 지역(제주시), 분석 기간(최근3개월) 설정
-- [분석 실행] 클릭</t>
+          <t>- 정책 유형 [주차장 확충] 선택
+- 대상 지역(제주 전체), 확충 방식(공한지 조성), 주차면 증설 수 입력
+- [시뮬레이션 실행] 클릭</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>교통행정과 담당자 권한 계정</t>
+          <t>차량관리과 담당자 권한 계정</t>
         </is>
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
-          <t>- 종합점수 기준으로 집중구역이 자동 도출되어 지도·순위가 갱신</t>
+          <t>- 효과 예측 차트와 민원 감소 예측·혼잡도 개선 수치가 표출</t>
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
@@ -13218,9 +13033,9 @@
       <c r="N17" s="3" t="n"/>
       <c r="O17" s="3" t="n"/>
       <c r="P17" s="31" t="n"/>
-      <c r="Q17" s="34" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-02</t>
+      <c r="Q17" s="67" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-05</t>
         </is>
       </c>
     </row>
@@ -13232,17 +13047,17 @@
       <c r="C18" s="68" t="n"/>
       <c r="D18" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-13</t>
+          <t>PR-PAR-A01-16</t>
         </is>
       </c>
       <c r="E18" s="67" t="inlineStr">
         <is>
-          <t>UI-PAR-003-01</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>지도 마커 상세 팝업</t>
+          <t>UI-PAR-003-02-1</t>
+        </is>
+      </c>
+      <c r="F18" s="73" t="inlineStr">
+        <is>
+          <t>정책 유형 전환 및 변수 입력</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
@@ -13250,17 +13065,18 @@
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>- 지도상 집중구역 마커 클릭</t>
+          <t>- 정책 유형을 [이면도로 정비] / [요금제 적용]으로 전환
+- 정비유형 및 요금 인상율 선택 후 실행</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>교통행정과 담당자 권한 계정</t>
+          <t>차량관리과 담당자 권한 계정</t>
         </is>
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>- 순위·구역명·민원 건수·단속 건수 팝업이 표출</t>
+          <t>- 정책 유형별 입력 항목이 전환되고 각 조건 기준의 예측 결과가 산출</t>
         </is>
       </c>
       <c r="K18" s="3" t="n"/>
@@ -13271,7 +13087,7 @@
       <c r="P18" s="31" t="n"/>
       <c r="Q18" s="67" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-02</t>
+          <t>REQ-SFR-003-05</t>
         </is>
       </c>
     </row>
@@ -13279,21 +13095,21 @@
       <c r="A19" s="32" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="69" t="n"/>
-      <c r="C19" s="69" t="n"/>
-      <c r="D19" s="22" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-14</t>
+      <c r="B19" s="68" t="n"/>
+      <c r="C19" s="68" t="n"/>
+      <c r="D19" s="67" t="inlineStr">
+        <is>
+          <t>PR-PAR-A01-17</t>
         </is>
       </c>
       <c r="E19" s="67" t="inlineStr">
         <is>
-          <t>UI-PAR-004-01</t>
+          <t>UI-PAR-003-02</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>분석 결과 보고서 내보내기</t>
+          <t>시나리오 비교</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
@@ -13301,18 +13117,17 @@
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>- [내보내기] 클릭
-- 보고서·알림 &gt; 보고서 관리 진입</t>
+          <t>- 하단 시나리오 비교 테이블 확인</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>교통행정과 담당자 권한 계정</t>
+          <t>차량관리과 담당자 권한 계정</t>
         </is>
       </c>
       <c r="J19" s="1" t="inlineStr">
         <is>
-          <t>- 직접 생성 보고서 목록에 보고서명·분석기간·생성일·생성자가 등록되고 PDF 다운로드 가능</t>
+          <t>- 시나리오별 민원 감소율·혼잡도 개선·비용 수준이 비교 표출되고 추천 배지가 부여</t>
         </is>
       </c>
       <c r="K19" s="3" t="n"/>
@@ -13323,7 +13138,8 @@
       <c r="P19" s="31" t="n"/>
       <c r="Q19" s="67" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-10</t>
+          <t>REQ-SFR-003-12
+REQ-SFR-003-13</t>
         </is>
       </c>
     </row>
@@ -13331,39 +13147,29 @@
       <c r="A20" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="76" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-05</t>
-        </is>
-      </c>
-      <c r="C20" s="76" t="inlineStr">
-        <is>
-          <t>정책 효과 시뮬레이션</t>
-        </is>
-      </c>
-      <c r="D20" s="22" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-15</t>
+      <c r="B20" s="69" t="n"/>
+      <c r="C20" s="69" t="n"/>
+      <c r="D20" s="67" t="inlineStr">
+        <is>
+          <t>PR-PAR-A01-18</t>
         </is>
       </c>
       <c r="E20" s="67" t="inlineStr">
         <is>
-          <t>UI-PAR-003-02</t>
+          <t>UI-PAR-004-01</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>주차장 확충 시뮬레이션 실행</t>
+          <t>시뮬레이션 결과 보고서 내보내기</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
-          <t>- 정책 유형 [주차장 확충] 선택
-- 대상 지역(제주 전체), 확충 방식(공한지 조성), 주차면 증설 수 입력
-- [시뮬레이션 실행] 클릭</t>
+          <t>- [내보내기] 클릭 후 보고서 관리 진입</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -13373,7 +13179,7 @@
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
-          <t>- 효과 예측 차트와 민원 감소 예측·혼잡도 개선 수치가 표출</t>
+          <t>- 직접 생성 보고서 목록에 시뮬레이션 보고서가 등록되고 미리보기·다운로드 동작</t>
         </is>
       </c>
       <c r="K20" s="3" t="n"/>
@@ -13384,7 +13190,8 @@
       <c r="P20" s="31" t="n"/>
       <c r="Q20" s="67" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-05</t>
+          <t>REQ-SFR-003-10
+REQ-SFR-003-12</t>
         </is>
       </c>
     </row>
@@ -13392,30 +13199,38 @@
       <c r="A21" s="32" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="68" t="n"/>
-      <c r="C21" s="68" t="n"/>
-      <c r="D21" s="22" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-16</t>
+      <c r="B21" s="76" t="inlineStr">
+        <is>
+          <t>TT-PAR-A01-06</t>
+        </is>
+      </c>
+      <c r="C21" s="76" t="inlineStr">
+        <is>
+          <t>생활권 시뮬레이션</t>
+        </is>
+      </c>
+      <c r="D21" s="67" t="inlineStr">
+        <is>
+          <t>PR-PAR-A01-19</t>
         </is>
       </c>
       <c r="E21" s="67" t="inlineStr">
         <is>
-          <t>UI-PAR-003-02-1</t>
-        </is>
-      </c>
-      <c r="F21" s="73" t="inlineStr">
-        <is>
-          <t>정책 유형 전환 및 변수 입력</t>
+          <t>UI-PAR-003-03</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>격자 기반 분석 실행</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21" s="1" t="inlineStr">
         <is>
-          <t>- 정책 유형을 [이면도로 정비] / [요금제 적용]으로 전환
-- 정비유형 및 요금 인상율 선택 후 실행</t>
+          <t>- 분석 내용(민원건수/수급/혼잡도), 분석 지역, 분석 기간, 격자 크기(500m) 설정
+- [생활권 분석 실행] 클릭</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -13425,7 +13240,7 @@
       </c>
       <c r="J21" s="1" t="inlineStr">
         <is>
-          <t>- 정책 유형별 입력 항목이 전환되고 각 조건 기준의 예측 결과가 산출</t>
+          <t>- 제주 전역 격자 기반 히트맵이 표출</t>
         </is>
       </c>
       <c r="K21" s="3" t="n"/>
@@ -13436,7 +13251,7 @@
       <c r="P21" s="31" t="n"/>
       <c r="Q21" s="67" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-05</t>
+          <t>REQ-SFR-003-04</t>
         </is>
       </c>
     </row>
@@ -13448,25 +13263,25 @@
       <c r="C22" s="68" t="n"/>
       <c r="D22" s="67" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-17</t>
+          <t>PR-PAR-A01-20</t>
         </is>
       </c>
       <c r="E22" s="67" t="inlineStr">
         <is>
-          <t>UI-PAR-003-02</t>
+          <t>UI-PAR-003-03</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>시나리오 비교</t>
+          <t>격자 클릭 상세 팝업</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" s="1" t="inlineStr">
         <is>
-          <t>- 하단 시나리오 비교 테이블 확인</t>
+          <t>- 히트맵상 격자 클릭</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -13476,7 +13291,7 @@
       </c>
       <c r="J22" s="1" t="inlineStr">
         <is>
-          <t>- 시나리오별 민원 감소율·혼잡도 개선·비용 수준이 비교 표출되고 추천 배지가 부여</t>
+          <t>- 위험단계·구역명·민원 건수·유형별 세부 건수 팝업이 표출</t>
         </is>
       </c>
       <c r="K22" s="3" t="n"/>
@@ -13487,8 +13302,7 @@
       <c r="P22" s="31" t="n"/>
       <c r="Q22" s="67" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-12
-REQ-SFR-003-13</t>
+          <t>REQ-SFR-003-04</t>
         </is>
       </c>
     </row>
@@ -13498,27 +13312,27 @@
       </c>
       <c r="B23" s="69" t="n"/>
       <c r="C23" s="69" t="n"/>
-      <c r="D23" s="67" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-18</t>
-        </is>
-      </c>
-      <c r="E23" s="67" t="inlineStr">
-        <is>
-          <t>UI-PAR-004-01</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>시뮬레이션 결과 보고서 내보내기</t>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>PR-PAR-A01-21</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-03</t>
+        </is>
+      </c>
+      <c r="F23" s="73" t="inlineStr">
+        <is>
+          <t>분석결과요약·민원집중구역 표출</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
-          <t>- [내보내기] 클릭 후 보고서 관리 진입</t>
+          <t>- 우측 분석 결과 요약 및 민원 집중 구역 목록 확인</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -13528,7 +13342,7 @@
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
-          <t>- 직접 생성 보고서 목록에 시뮬레이션 보고서가 등록되고 미리보기·다운로드 동작</t>
+          <t>- 전체/유형별 격자 수가 집계되고 집중구역이 '동 + 격자 중심 POI' 명칭으로 표출</t>
         </is>
       </c>
       <c r="K23" s="3" t="n"/>
@@ -13537,10 +13351,9 @@
       <c r="N23" s="3" t="n"/>
       <c r="O23" s="3" t="n"/>
       <c r="P23" s="31" t="n"/>
-      <c r="Q23" s="67" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-10
-REQ-SFR-003-12</t>
+      <c r="Q23" s="34" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-04</t>
         </is>
       </c>
     </row>
@@ -13548,29 +13361,29 @@
       <c r="A24" s="32" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="76" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-06</t>
-        </is>
-      </c>
-      <c r="C24" s="76" t="inlineStr">
-        <is>
-          <t>생활권 시뮬레이션</t>
+      <c r="B24" s="67" t="inlineStr">
+        <is>
+          <t>TT-PAR-A01-07</t>
+        </is>
+      </c>
+      <c r="C24" s="73" t="inlineStr">
+        <is>
+          <t>구역 추천</t>
         </is>
       </c>
       <c r="D24" s="67" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-19</t>
+          <t>PR-PAR-A01-22</t>
         </is>
       </c>
       <c r="E24" s="67" t="inlineStr">
         <is>
-          <t>UI-PAR-003-03</t>
+          <t>UI-PAR-003-04</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>격자 기반 분석 실행</t>
+          <t>구역 추천 실행</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
@@ -13578,8 +13391,8 @@
       </c>
       <c r="H24" s="1" t="inlineStr">
         <is>
-          <t>- 분석 내용(민원건수/수급/혼잡도), 분석 지역, 분석 기간, 격자 크기(500m) 설정
-- [생활권 분석 실행] 클릭</t>
+          <t>- 분석 내용(요금제 적용/공유주차제), 분석 지역, 분석 기간 설정
+- [구역 추천 실행] 클릭</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -13589,7 +13402,7 @@
       </c>
       <c r="J24" s="1" t="inlineStr">
         <is>
-          <t>- 제주 전역 격자 기반 히트맵이 표출</t>
+          <t>- 민원 증가 추세를 반영한 추천 구역이 자동 도출</t>
         </is>
       </c>
       <c r="K24" s="3" t="n"/>
@@ -13600,7 +13413,7 @@
       <c r="P24" s="31" t="n"/>
       <c r="Q24" s="67" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-04</t>
+          <t>REQ-SFR-003-06</t>
         </is>
       </c>
     </row>
@@ -13609,20 +13422,20 @@
         <v>20</v>
       </c>
       <c r="B25" s="68" t="n"/>
-      <c r="C25" s="68" t="n"/>
-      <c r="D25" s="67" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-20</t>
-        </is>
-      </c>
-      <c r="E25" s="67" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-03</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>격자 클릭 상세 팝업</t>
+      <c r="C25" s="74" t="n"/>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>PR-PAR-A01-23</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-04</t>
+        </is>
+      </c>
+      <c r="F25" s="67" t="inlineStr">
+        <is>
+          <t>추천 구역 마커 표출</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
@@ -13630,7 +13443,7 @@
       </c>
       <c r="H25" s="1" t="inlineStr">
         <is>
-          <t>- 히트맵상 격자 클릭</t>
+          <t>- 지도상 추천 구역 핀 마커 확인 후 클릭</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -13640,7 +13453,7 @@
       </c>
       <c r="J25" s="1" t="inlineStr">
         <is>
-          <t>- 위험단계·구역명·민원 건수·유형별 세부 건수 팝업이 표출</t>
+          <t>- 요금제/공유주차제 유형별 마커가 구분 표시되고 구역명·민원 증가율·최근 건수 팝업이 표출</t>
         </is>
       </c>
       <c r="K25" s="3" t="n"/>
@@ -13649,9 +13462,9 @@
       <c r="N25" s="3" t="n"/>
       <c r="O25" s="3" t="n"/>
       <c r="P25" s="31" t="n"/>
-      <c r="Q25" s="67" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-04</t>
+      <c r="Q25" s="34" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-06</t>
         </is>
       </c>
     </row>
@@ -13660,20 +13473,20 @@
         <v>21</v>
       </c>
       <c r="B26" s="69" t="n"/>
-      <c r="C26" s="69" t="n"/>
+      <c r="C26" s="71" t="n"/>
       <c r="D26" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-21</t>
+          <t>PR-PAR-A01-24</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
         <is>
-          <t>UI-PAR-003-03</t>
-        </is>
-      </c>
-      <c r="F26" s="73" t="inlineStr">
-        <is>
-          <t>분석결과요약·민원집중구역 표출</t>
+          <t>UI-PAR-003-04</t>
+        </is>
+      </c>
+      <c r="F26" s="67" t="inlineStr">
+        <is>
+          <t>추천 구역 순위 산정</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
@@ -13681,7 +13494,7 @@
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
-          <t>- 우측 분석 결과 요약 및 민원 집중 구역 목록 확인</t>
+          <t>- 우측 추천 구역 순위 목록 확인</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -13691,7 +13504,7 @@
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
-          <t>- 전체/유형별 격자 수가 집계되고 집중구역이 '동 + 격자 중심 POI' 명칭으로 표출</t>
+          <t>- 민원 증가 추세를 반영한 순위 기준으로 상위 구역이 표출</t>
         </is>
       </c>
       <c r="K26" s="3" t="n"/>
@@ -13702,7 +13515,7 @@
       <c r="P26" s="31" t="n"/>
       <c r="Q26" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-04</t>
+          <t>REQ-SFR-003-06</t>
         </is>
       </c>
     </row>
@@ -13710,29 +13523,29 @@
       <c r="A27" s="32" t="n">
         <v>22</v>
       </c>
-      <c r="B27" s="67" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-07</t>
-        </is>
-      </c>
-      <c r="C27" s="73" t="inlineStr">
-        <is>
-          <t>구역 추천</t>
-        </is>
-      </c>
-      <c r="D27" s="67" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-22</t>
-        </is>
-      </c>
-      <c r="E27" s="67" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-04</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>구역 추천 실행</t>
+      <c r="B27" s="76" t="inlineStr">
+        <is>
+          <t>TT-PAR-A01-08</t>
+        </is>
+      </c>
+      <c r="C27" s="76" t="inlineStr">
+        <is>
+          <t>투자우선순위 산정</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>PR-PAR-A01-25</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-05</t>
+        </is>
+      </c>
+      <c r="F27" s="67" t="inlineStr">
+        <is>
+          <t>종합 지표 기반 우선순위 자동 산정</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
@@ -13740,8 +13553,7 @@
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
-          <t>- 분석 내용(요금제 적용/공유주차제), 분석 지역, 분석 기간 설정
-- [구역 추천 실행] 클릭</t>
+          <t>- 분석·시뮬레이션 &gt; 투자우선순위 보드 진입</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -13751,7 +13563,7 @@
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
-          <t>- 민원 증가 추세를 반영한 추천 구역이 자동 도출</t>
+          <t>- 설정된 가중치(안전위험도·민원빈도·이용패턴·사고이력)로 종합점수가 자동 산정</t>
         </is>
       </c>
       <c r="K27" s="3" t="n"/>
@@ -13760,9 +13572,9 @@
       <c r="N27" s="3" t="n"/>
       <c r="O27" s="3" t="n"/>
       <c r="P27" s="31" t="n"/>
-      <c r="Q27" s="67" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-06</t>
+      <c r="Q27" s="34" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-04</t>
         </is>
       </c>
     </row>
@@ -13771,20 +13583,20 @@
         <v>23</v>
       </c>
       <c r="B28" s="68" t="n"/>
-      <c r="C28" s="74" t="n"/>
+      <c r="C28" s="68" t="n"/>
       <c r="D28" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-23</t>
+          <t>PR-PAR-A01-26</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
         <is>
-          <t>UI-PAR-003-04</t>
-        </is>
-      </c>
-      <c r="F28" s="67" t="inlineStr">
-        <is>
-          <t>추천 구역 마커 표출</t>
+          <t>UI-PAR-003-05</t>
+        </is>
+      </c>
+      <c r="F28" s="73" t="inlineStr">
+        <is>
+          <t>지도 마커 표출 및 상세 팝업</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
@@ -13792,7 +13604,7 @@
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
-          <t>- 지도상 추천 구역 핀 마커 확인 후 클릭</t>
+          <t>- 공영주차장 P 핀 마커 확인 후 클릭</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -13802,7 +13614,7 @@
       </c>
       <c r="J28" s="1" t="inlineStr">
         <is>
-          <t>- 요금제/공유주차제 유형별 마커가 구분 표시되고 구역명·민원 증가율·최근 건수 팝업이 표출</t>
+          <t>- 우선순위(높음·중간·낮음)가 컬러로 구분되고 주차장명·종합점수·4개 지표 점수 팝업이 표출</t>
         </is>
       </c>
       <c r="K28" s="3" t="n"/>
@@ -13813,7 +13625,7 @@
       <c r="P28" s="31" t="n"/>
       <c r="Q28" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-06</t>
+          <t>REQ-SFR-005-04</t>
         </is>
       </c>
     </row>
@@ -13822,20 +13634,20 @@
         <v>24</v>
       </c>
       <c r="B29" s="69" t="n"/>
-      <c r="C29" s="71" t="n"/>
+      <c r="C29" s="69" t="n"/>
       <c r="D29" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-24</t>
+          <t>PR-PAR-A01-27</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
         <is>
-          <t>UI-PAR-003-04</t>
+          <t>UI-PAR-003-05</t>
         </is>
       </c>
       <c r="F29" s="67" t="inlineStr">
         <is>
-          <t>추천 구역 순위 산정</t>
+          <t>요약 카드·순위 리스트 정합성</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
@@ -13843,7 +13655,7 @@
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
-          <t>- 우측 추천 구역 순위 목록 확인</t>
+          <t>- 상단 요약 카드와 우측 우선순위 리스트 대조</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -13853,7 +13665,7 @@
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
-          <t>- 민원 증가 추세를 반영한 순위 기준으로 상위 구역이 표출</t>
+          <t>- 분석 대상 주차장 수·높음 우선순위 개소·최근 3개월 사고 건수가 리스트 집계와 일치</t>
         </is>
       </c>
       <c r="K29" s="3" t="n"/>
@@ -13864,7 +13676,7 @@
       <c r="P29" s="31" t="n"/>
       <c r="Q29" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-06</t>
+          <t>REQ-SFR-005-04</t>
         </is>
       </c>
     </row>
@@ -13874,27 +13686,27 @@
       </c>
       <c r="B30" s="76" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-08</t>
+          <t>TT-PAR-A01-09</t>
         </is>
       </c>
       <c r="C30" s="76" t="inlineStr">
         <is>
-          <t>투자우선순위 산정</t>
+          <t>위험단계 알림 관리</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-25</t>
+          <t>PR-PAR-A01-28</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
         <is>
-          <t>UI-PAR-003-05</t>
+          <t>UI-PAR-004-03</t>
         </is>
       </c>
       <c r="F30" s="67" t="inlineStr">
         <is>
-          <t>종합 지표 기반 우선순위 자동 산정</t>
+          <t>알림 기준 설정 저장</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
@@ -13902,17 +13714,18 @@
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
-          <t>- 분석·시뮬레이션 &gt; 투자우선순위 보드 진입</t>
+          <t>- 보고서·알림 &gt; 위험단계 알림 관리 진입
+- 심각/경고/주의 기준 건수 입력 후 [저장] 클릭</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>차량관리과 담당자 권한 계정</t>
+          <t>시스템관리자 권한 계정</t>
         </is>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
-          <t>- 설정된 가중치(안전위험도·민원빈도·이용패턴·사고이력)로 종합점수가 자동 산정</t>
+          <t>- 설정한 위험단계 기준이 저장되고 재진입 시 유지</t>
         </is>
       </c>
       <c r="K30" s="3" t="n"/>
@@ -13923,7 +13736,7 @@
       <c r="P30" s="31" t="n"/>
       <c r="Q30" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-005-04</t>
+          <t>REQ-SFR-003-08</t>
         </is>
       </c>
     </row>
@@ -13935,17 +13748,17 @@
       <c r="C31" s="68" t="n"/>
       <c r="D31" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-26</t>
+          <t>PR-PAR-A01-29</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
         <is>
-          <t>UI-PAR-003-05</t>
-        </is>
-      </c>
-      <c r="F31" s="73" t="inlineStr">
-        <is>
-          <t>지도 마커 표출 및 상세 팝업</t>
+          <t>UI-PAR-004-03</t>
+        </is>
+      </c>
+      <c r="F31" s="67" t="inlineStr">
+        <is>
+          <t>수신자 등록 및 활성화 관리</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
@@ -13953,17 +13766,18 @@
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
-          <t>- 공영주차장 P 핀 마커 확인 후 클릭</t>
+          <t>- [수신자 추가] 클릭 후 소속·이름·이메일·단계 그룹 입력
+- 활성화 토글 전환</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>차량관리과 담당자 권한 계정</t>
+          <t>시스템관리자 권한 계정</t>
         </is>
       </c>
       <c r="J31" s="1" t="inlineStr">
         <is>
-          <t>- 우선순위(높음·중간·낮음)가 컬러로 구분되고 주차장명·종합점수·4개 지표 점수 팝업이 표출</t>
+          <t>- 수신자가 등록되고 활성화 여부에 따라 알림 발송 대상이 결정</t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
@@ -13974,7 +13788,7 @@
       <c r="P31" s="31" t="n"/>
       <c r="Q31" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-005-04</t>
+          <t>REQ-SFR-003-08</t>
         </is>
       </c>
     </row>
@@ -13982,21 +13796,21 @@
       <c r="A32" s="32" t="n">
         <v>27</v>
       </c>
-      <c r="B32" s="69" t="n"/>
-      <c r="C32" s="69" t="n"/>
+      <c r="B32" s="68" t="n"/>
+      <c r="C32" s="68" t="n"/>
       <c r="D32" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-27</t>
+          <t>PR-PAR-A01-30</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
         <is>
-          <t>UI-PAR-003-05</t>
+          <t>UI-PAR-004-02</t>
         </is>
       </c>
       <c r="F32" s="67" t="inlineStr">
         <is>
-          <t>요약 카드·순위 리스트 정합성</t>
+          <t>기준 충족 시 알림 자동 발생</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
@@ -14004,17 +13818,18 @@
       </c>
       <c r="H32" s="1" t="inlineStr">
         <is>
-          <t>- 상단 요약 카드와 우측 우선순위 리스트 대조</t>
+          <t>- 기준 초과 민원 데이터 수집
+- 알림 발생 및 수신자 메일 통보 확인</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>차량관리과 담당자 권한 계정</t>
+          <t>시스템관리자 권한 계정</t>
         </is>
       </c>
       <c r="J32" s="1" t="inlineStr">
         <is>
-          <t>- 분석 대상 주차장 수·높음 우선순위 개소·최근 3개월 사고 건수가 리스트 집계와 일치</t>
+          <t>- 위험 단계별 알림이 자동 발생하고 활성화된 수신자에게 통보</t>
         </is>
       </c>
       <c r="K32" s="3" t="n"/>
@@ -14025,7 +13840,7 @@
       <c r="P32" s="31" t="n"/>
       <c r="Q32" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-005-04</t>
+          <t>REQ-SFR-003-08</t>
         </is>
       </c>
     </row>
@@ -14033,38 +13848,30 @@
       <c r="A33" s="32" t="n">
         <v>28</v>
       </c>
-      <c r="B33" s="76" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-09</t>
-        </is>
-      </c>
-      <c r="C33" s="76" t="inlineStr">
-        <is>
-          <t>위험단계 알림 관리</t>
-        </is>
-      </c>
+      <c r="B33" s="69" t="n"/>
+      <c r="C33" s="69" t="n"/>
       <c r="D33" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-28</t>
+          <t>PR-PAR-A01-31</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
         <is>
-          <t>UI-PAR-004-03</t>
+          <t>UI-PAR-004-02</t>
         </is>
       </c>
       <c r="F33" s="67" t="inlineStr">
         <is>
-          <t>알림 기준 설정 저장</t>
+          <t>알림 이력 조회</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H33" s="1" t="inlineStr">
         <is>
-          <t>- 보고서·알림 &gt; 위험단계 알림 관리 진입
-- 심각/경고/주의 기준 건수 입력 후 [저장] 클릭</t>
+          <t>- 보고서·알림 &gt; 위험단계 알림 조회 진입
+- 단계/지역/기간 필터 적용</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -14074,7 +13881,7 @@
       </c>
       <c r="J33" s="1" t="inlineStr">
         <is>
-          <t>- 설정한 위험단계 기준이 저장되고 재진입 시 유지</t>
+          <t>- 필터 조건에 맞는 알림 이력이 단계 뱃지와 함께 목록으로 표출</t>
         </is>
       </c>
       <c r="K33" s="3" t="n"/>
@@ -14093,30 +13900,38 @@
       <c r="A34" s="32" t="n">
         <v>29</v>
       </c>
-      <c r="B34" s="68" t="n"/>
-      <c r="C34" s="68" t="n"/>
+      <c r="B34" s="76" t="inlineStr">
+        <is>
+          <t>TT-PAR-A01-10</t>
+        </is>
+      </c>
+      <c r="C34" s="76" t="inlineStr">
+        <is>
+          <t>보고서 자동 생성</t>
+        </is>
+      </c>
       <c r="D34" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-29</t>
+          <t>PR-PAR-A01-32</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
         <is>
-          <t>UI-PAR-004-03</t>
+          <t>UI-PAR-004-01</t>
         </is>
       </c>
       <c r="F34" s="67" t="inlineStr">
         <is>
-          <t>수신자 등록 및 활성화 관리</t>
+          <t>배포주기·배포일자 설정</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
-          <t>- [수신자 추가] 클릭 후 소속·이름·이메일·단계 그룹 입력
-- 활성화 토글 전환</t>
+          <t>- 보고서·알림 &gt; 보고서 관리 진입
+- 배포 주기, 배포 일자 선택 후 [보고서 자동 생성] 클릭</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -14126,7 +13941,7 @@
       </c>
       <c r="J34" s="1" t="inlineStr">
         <is>
-          <t>- 수신자가 등록되고 활성화 여부에 따라 알림 발송 대상이 결정</t>
+          <t>- 자동 생성 설정이 저장되고 자동 생성 보고서 목록에 항목이 추가</t>
         </is>
       </c>
       <c r="K34" s="3" t="n"/>
@@ -14137,7 +13952,9 @@
       <c r="P34" s="31" t="n"/>
       <c r="Q34" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-08</t>
+          <t>REQ-SFR-003-11
+REQ-SFR-005-05
+REQ-SFR-005-06</t>
         </is>
       </c>
     </row>
@@ -14149,26 +13966,25 @@
       <c r="C35" s="68" t="n"/>
       <c r="D35" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-30</t>
+          <t>PR-PAR-A01-33</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
         <is>
-          <t>UI-PAR-004-02</t>
+          <t>UI-PAR-004-01</t>
         </is>
       </c>
       <c r="F35" s="67" t="inlineStr">
         <is>
-          <t>기준 충족 시 알림 자동 발생</t>
+          <t>배포일자 도래 시 자동 생성</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H35" s="1" t="inlineStr">
         <is>
-          <t>- 기준 초과 민원 데이터 수집
-- 알림 발생 및 수신자 메일 통보 확인</t>
+          <t>- 배포 일자 도래 후 목록 상태 확인</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -14178,7 +13994,7 @@
       </c>
       <c r="J35" s="1" t="inlineStr">
         <is>
-          <t>- 위험 단계별 알림이 자동 발생하고 활성화된 수신자에게 통보</t>
+          <t>- 보고서명(당해년도+배포주기+민원보고서)으로 생성되고 상태가 '대기'에서 '완료'로 전환</t>
         </is>
       </c>
       <c r="K35" s="3" t="n"/>
@@ -14189,7 +14005,7 @@
       <c r="P35" s="31" t="n"/>
       <c r="Q35" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-08</t>
+          <t>REQ-SFR-005-05</t>
         </is>
       </c>
     </row>
@@ -14201,26 +14017,25 @@
       <c r="C36" s="69" t="n"/>
       <c r="D36" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-31</t>
+          <t>PR-PAR-A01-34</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
         <is>
-          <t>UI-PAR-004-02</t>
-        </is>
-      </c>
-      <c r="F36" s="67" t="inlineStr">
-        <is>
-          <t>알림 이력 조회</t>
+          <t>UI-PAR-004-01</t>
+        </is>
+      </c>
+      <c r="F36" s="73" t="inlineStr">
+        <is>
+          <t>미리보기 및 다운로드</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
-          <t>- 보고서·알림 &gt; 위험단계 알림 조회 진입
-- 단계/지역/기간 필터 적용</t>
+          <t>- [미리보기] 클릭 후 [PDF] 클릭</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -14230,7 +14045,7 @@
       </c>
       <c r="J36" s="1" t="inlineStr">
         <is>
-          <t>- 필터 조건에 맞는 알림 이력이 단계 뱃지와 함께 목록으로 표출</t>
+          <t>- 보고서 미리보기 팝업이 표출되고 PDF 형식으로 다운로드</t>
         </is>
       </c>
       <c r="K36" s="3" t="n"/>
@@ -14241,7 +14056,8 @@
       <c r="P36" s="31" t="n"/>
       <c r="Q36" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-08</t>
+          <t>REQ-SFR-003-11
+REQ-SFR-005-05</t>
         </is>
       </c>
     </row>
@@ -14249,29 +14065,29 @@
       <c r="A37" s="32" t="n">
         <v>32</v>
       </c>
-      <c r="B37" s="76" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-10</t>
-        </is>
-      </c>
-      <c r="C37" s="76" t="inlineStr">
-        <is>
-          <t>보고서 자동 생성</t>
+      <c r="B37" s="67" t="inlineStr">
+        <is>
+          <t>TT-PAR-A01-11</t>
+        </is>
+      </c>
+      <c r="C37" s="67" t="inlineStr">
+        <is>
+          <t>AI 어시스턴트</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-32</t>
-        </is>
-      </c>
-      <c r="E37" s="22" t="inlineStr">
-        <is>
-          <t>UI-PAR-004-01</t>
-        </is>
-      </c>
-      <c r="F37" s="67" t="inlineStr">
-        <is>
-          <t>배포주기·배포일자 설정</t>
+          <t>PR-PAR-A01-35</t>
+        </is>
+      </c>
+      <c r="E37" s="67" t="inlineStr">
+        <is>
+          <t>UI-PAR-005</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>AI 어시스턴트 행정 지원(자연어 검색·조례 인용·민원 요약)</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
@@ -14279,18 +14095,18 @@
       </c>
       <c r="H37" s="1" t="inlineStr">
         <is>
-          <t>- 보고서·알림 &gt; 보고서 관리 진입
-- 배포 주기, 배포 일자 선택 후 [보고서 자동 생성] 클릭</t>
+          <t>- 자연어 질의로 sLLM 응답 및 RAG 조례 인용 카드 확인
+- 대량 민원 내용 보고용 요약 실행</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>시스템관리자 권한 계정</t>
+          <t>교통행정과 담당자 권한 계정</t>
         </is>
       </c>
       <c r="J37" s="1" t="inlineStr">
         <is>
-          <t>- 자동 생성 설정이 저장되고 자동 생성 보고서 목록에 항목이 추가</t>
+          <t>- sLLM 자연어 응답·조례명·관련 조문 발췌 인용·민원 보고용 요약이 정상 표출</t>
         </is>
       </c>
       <c r="K37" s="3" t="n"/>
@@ -14299,11 +14115,11 @@
       <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="n"/>
       <c r="P37" s="31" t="n"/>
-      <c r="Q37" s="34" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-11
-REQ-SFR-005-05
-REQ-SFR-005-06</t>
+      <c r="Q37" s="67" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-07
+REQ-SFR-005-08
+REQ-SFR-005-09</t>
         </is>
       </c>
     </row>
@@ -14311,29 +14127,37 @@
       <c r="A38" s="32" t="n">
         <v>33</v>
       </c>
-      <c r="B38" s="68" t="n"/>
-      <c r="C38" s="68" t="n"/>
+      <c r="B38" s="67" t="inlineStr">
+        <is>
+          <t>TT-PAR-A01-12</t>
+        </is>
+      </c>
+      <c r="C38" s="67" t="inlineStr">
+        <is>
+          <t>데이터 융합 통합분석</t>
+        </is>
+      </c>
       <c r="D38" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-33</t>
-        </is>
-      </c>
-      <c r="E38" s="22" t="inlineStr">
-        <is>
-          <t>UI-PAR-004-01</t>
-        </is>
-      </c>
-      <c r="F38" s="67" t="inlineStr">
-        <is>
-          <t>배포일자 도래 시 자동 생성</t>
+          <t>PR-PAR-A01-37</t>
+        </is>
+      </c>
+      <c r="E38" s="67" t="inlineStr">
+        <is>
+          <t>UI-PAR-005</t>
+        </is>
+      </c>
+      <c r="F38" s="33" t="inlineStr">
+        <is>
+          <t>데이터 융합 통합분석</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" s="1" t="inlineStr">
         <is>
-          <t>- 배포 일자 도래 후 목록 상태 확인</t>
+          <t>- 상관관계 분석 및 종합 인사이트 도출·보고서 반영 확인</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
@@ -14343,7 +14167,7 @@
       </c>
       <c r="J38" s="1" t="inlineStr">
         <is>
-          <t>- 보고서명(당해년도+배포주기+민원보고서)으로 생성되고 상태가 '대기'에서 '완료'로 전환</t>
+          <t>- 두 솔루션 데이터가 결합되어 상관관계·종합 인사이트가 시각화·보고서에 반영</t>
         </is>
       </c>
       <c r="K38" s="3" t="n"/>
@@ -14352,9 +14176,9 @@
       <c r="N38" s="3" t="n"/>
       <c r="O38" s="3" t="n"/>
       <c r="P38" s="31" t="n"/>
-      <c r="Q38" s="34" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-05</t>
+      <c r="Q38" s="67" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-01</t>
         </is>
       </c>
     </row>
@@ -14362,29 +14186,38 @@
       <c r="A39" s="32" t="n">
         <v>34</v>
       </c>
-      <c r="B39" s="69" t="n"/>
-      <c r="C39" s="69" t="n"/>
+      <c r="B39" s="67" t="inlineStr">
+        <is>
+          <t>TT-PAR-A01-13</t>
+        </is>
+      </c>
+      <c r="C39" s="67" t="inlineStr">
+        <is>
+          <t>타 지자체 확산 적용 구조</t>
+        </is>
+      </c>
       <c r="D39" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-34</t>
-        </is>
-      </c>
-      <c r="E39" s="22" t="inlineStr">
-        <is>
-          <t>UI-PAR-004-01</t>
-        </is>
-      </c>
-      <c r="F39" s="73" t="inlineStr">
-        <is>
-          <t>미리보기 및 다운로드</t>
+          <t>PR-PAR-A01-39</t>
+        </is>
+      </c>
+      <c r="E39" s="67" t="inlineStr">
+        <is>
+          <t>공통(설정)</t>
+        </is>
+      </c>
+      <c r="F39" s="33" t="inlineStr">
+        <is>
+          <t>타 지자체 확산 적용 구조 검증</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H39" s="1" t="inlineStr">
         <is>
-          <t>- [미리보기] 클릭 후 [PDF] 클릭</t>
+          <t>- 대상 지역·데이터 구조·분석 지표(가중치)를 타 지자체 기준으로 설정 변경
+- 변경 설정으로 주요 분석 기능 동작 확인</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
@@ -14394,7 +14227,7 @@
       </c>
       <c r="J39" s="1" t="inlineStr">
         <is>
-          <t>- 보고서 미리보기 팝업이 표출되고 PDF 형식으로 다운로드</t>
+          <t>- 지역 여건에 맞게 설정·조정되어 기능이 오류 없이 정상 동작</t>
         </is>
       </c>
       <c r="K39" s="3" t="n"/>
@@ -14403,351 +14236,51 @@
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="n"/>
       <c r="P39" s="31" t="n"/>
-      <c r="Q39" s="34" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-11
-REQ-SFR-005-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="48" customHeight="1" s="48">
-      <c r="A40" s="32" t="n">
-        <v>35</v>
-      </c>
-      <c r="B40" s="67" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-11</t>
-        </is>
-      </c>
-      <c r="C40" s="67" t="inlineStr">
-        <is>
-          <t>AI 어시스턴트</t>
-        </is>
-      </c>
-      <c r="D40" s="22" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-35</t>
-        </is>
-      </c>
-      <c r="E40" s="67" t="inlineStr">
-        <is>
-          <t>UI-PAR-005</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>AI 어시스턴트 행정 지원(자연어 검색·조례 인용·민원 요약)</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="1" t="inlineStr">
-        <is>
-          <t>- 자연어 질의로 sLLM 응답 및 RAG 조례 인용 카드 확인
-- 대량 민원 내용 보고용 요약 실행</t>
-        </is>
-      </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>교통행정과 담당자 권한 계정</t>
-        </is>
-      </c>
-      <c r="J40" s="1" t="inlineStr">
-        <is>
-          <t>- sLLM 자연어 응답·조례명·관련 조문 발췌 인용·민원 보고용 요약이 정상 표출</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="n"/>
-      <c r="L40" s="3" t="n"/>
-      <c r="M40" s="21" t="n"/>
-      <c r="N40" s="3" t="n"/>
-      <c r="O40" s="3" t="n"/>
-      <c r="P40" s="31" t="n"/>
-      <c r="Q40" s="67" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-07
-REQ-SFR-005-08
-REQ-SFR-005-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="48" customHeight="1" s="48">
-      <c r="A41" s="32" t="n">
-        <v>36</v>
-      </c>
-      <c r="B41" s="67" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-12</t>
-        </is>
-      </c>
-      <c r="C41" s="67" t="inlineStr">
-        <is>
-          <t>비정형 행정문서 자동 수집·정형화</t>
-        </is>
-      </c>
-      <c r="D41" s="22" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-36</t>
-        </is>
-      </c>
-      <c r="E41" s="67" t="inlineStr">
-        <is>
-          <t>UI-PAR-005</t>
-        </is>
-      </c>
-      <c r="F41" s="33" t="inlineStr">
-        <is>
-          <t>비정형 행정문서 자동 수집·정형화(AI RPA/OCR)</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="1" t="inlineStr">
-        <is>
-          <t>- AI RPA/OCR로 비정형·스캔 문서 자동 수집·텍스트 추출
-- 정형화·구조화 적재 후 RAG 검색 연계 확인</t>
-        </is>
-      </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>시스템관리자 권한 계정</t>
-        </is>
-      </c>
-      <c r="J41" s="1" t="inlineStr">
-        <is>
-          <t>- 비정형 문서가 정형화 적재되고 RAG 검색 대상에 포함됨</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="n"/>
-      <c r="L41" s="3" t="n"/>
-      <c r="M41" s="21" t="n"/>
-      <c r="N41" s="3" t="n"/>
-      <c r="O41" s="3" t="n"/>
-      <c r="P41" s="31" t="n"/>
-      <c r="Q41" s="67" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-03
-REQ-SFR-005-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="32.1" customHeight="1" s="48">
-      <c r="A42" s="32" t="n">
-        <v>37</v>
-      </c>
-      <c r="B42" s="67" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-13</t>
-        </is>
-      </c>
-      <c r="C42" s="67" t="inlineStr">
-        <is>
-          <t>데이터 융합 통합분석</t>
-        </is>
-      </c>
-      <c r="D42" s="22" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-37</t>
-        </is>
-      </c>
-      <c r="E42" s="67" t="inlineStr">
-        <is>
-          <t>UI-PAR-005</t>
-        </is>
-      </c>
-      <c r="F42" s="33" t="inlineStr">
-        <is>
-          <t>데이터 융합 통합분석</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" s="1" t="inlineStr">
-        <is>
-          <t>- 상관관계 분석 및 종합 인사이트 도출·보고서 반영 확인</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>시스템관리자 권한 계정</t>
-        </is>
-      </c>
-      <c r="J42" s="1" t="inlineStr">
-        <is>
-          <t>- 두 솔루션 데이터가 결합되어 상관관계·종합 인사이트가 시각화·보고서에 반영</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="n"/>
-      <c r="L42" s="3" t="n"/>
-      <c r="M42" s="21" t="n"/>
-      <c r="N42" s="3" t="n"/>
-      <c r="O42" s="3" t="n"/>
-      <c r="P42" s="31" t="n"/>
-      <c r="Q42" s="67" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="32.1" customHeight="1" s="48">
-      <c r="A43" s="32" t="n">
-        <v>38</v>
-      </c>
-      <c r="B43" s="67" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-14</t>
-        </is>
-      </c>
-      <c r="C43" s="67" t="inlineStr">
-        <is>
-          <t>분석 모델 고도화·재학습</t>
-        </is>
-      </c>
-      <c r="D43" s="22" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-38</t>
-        </is>
-      </c>
-      <c r="E43" s="67" t="inlineStr">
-        <is>
-          <t>공통(배치)</t>
-        </is>
-      </c>
-      <c r="F43" s="33" t="inlineStr">
-        <is>
-          <t>분석 모델 재학습 및 고도화</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="1" t="inlineStr">
-        <is>
-          <t>- 신규 민원 유형·정책 변화 데이터 반영 후 재학습 배치 실행
-- 재학습 전후 성능 지표 및 개선 이력 확인</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>시스템관리자 권한 계정</t>
-        </is>
-      </c>
-      <c r="J43" s="1" t="inlineStr">
-        <is>
-          <t>- 재학습이 정상 완료되고 신규 유형이 분석에 반영되며 개선 이력이 관리됨</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="n"/>
-      <c r="L43" s="3" t="n"/>
-      <c r="M43" s="21" t="n"/>
-      <c r="N43" s="3" t="n"/>
-      <c r="O43" s="3" t="n"/>
-      <c r="P43" s="31" t="n"/>
-      <c r="Q43" s="67" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="32.1" customHeight="1" s="48">
-      <c r="A44" s="32" t="n">
-        <v>39</v>
-      </c>
-      <c r="B44" s="67" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-15</t>
-        </is>
-      </c>
-      <c r="C44" s="67" t="inlineStr">
-        <is>
-          <t>타 지자체 확산 적용 구조</t>
-        </is>
-      </c>
-      <c r="D44" s="22" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-39</t>
-        </is>
-      </c>
-      <c r="E44" s="67" t="inlineStr">
-        <is>
-          <t>공통(설정)</t>
-        </is>
-      </c>
-      <c r="F44" s="33" t="inlineStr">
-        <is>
-          <t>타 지자체 확산 적용 구조 검증</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="1" t="inlineStr">
-        <is>
-          <t>- 대상 지역·데이터 구조·분석 지표(가중치)를 타 지자체 기준으로 설정 변경
-- 변경 설정으로 주요 분석 기능 동작 확인</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>시스템관리자 권한 계정</t>
-        </is>
-      </c>
-      <c r="J44" s="1" t="inlineStr">
-        <is>
-          <t>- 지역 여건에 맞게 설정·조정되어 기능이 오류 없이 정상 동작</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="n"/>
-      <c r="L44" s="3" t="n"/>
-      <c r="M44" s="21" t="n"/>
-      <c r="N44" s="3" t="n"/>
-      <c r="O44" s="3" t="n"/>
-      <c r="P44" s="31" t="n"/>
-      <c r="Q44" s="67" t="inlineStr">
+      <c r="Q39" s="67" t="inlineStr">
         <is>
           <t>REQ-SFR-005-10</t>
         </is>
       </c>
     </row>
+    <row r="40" ht="48" customHeight="1" s="48"/>
+    <row r="41" ht="48" customHeight="1" s="48"/>
+    <row r="42" ht="32.1" customHeight="1" s="48"/>
+    <row r="43" ht="32.1" customHeight="1" s="48"/>
+    <row r="44" ht="32.1" customHeight="1" s="48"/>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="32">
     <mergeCell ref="C27:C29"/>
+    <mergeCell ref="C21:C23"/>
     <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C33:C36"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="A4:A5"/>
     <mergeCell ref="E4:E5"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="C20:C23"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="A2:Q2"/>
     <mergeCell ref="B24:B26"/>
-    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="C30:C33"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="B17:B20"/>
     <mergeCell ref="Q4:Q5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="F4:F5"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="J4:J5"/>
-    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="B14:B16"/>
     <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="B33:B36"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="C13:C16"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B10:B13"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.5905511811023623" bottom="0.5905511811023623" header="0.3149606299212598" footer="0.3149606299212598"/>
@@ -14769,7 +14302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O897"/>
+  <dimension ref="A1:O782"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="17.1"/>
   <cols>
     <col width="10" customWidth="1" style="48" min="1" max="3"/>
@@ -15421,7 +14954,7 @@
       <c r="C72" s="42" t="n"/>
       <c r="D72" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-04</t>
+          <t>PR-PAR-A01-07</t>
         </is>
       </c>
       <c r="E72" s="41" t="n"/>
@@ -15471,7 +15004,7 @@
       <c r="C74" s="42" t="n"/>
       <c r="D74" s="40" t="inlineStr">
         <is>
-          <t>민원 원천 데이터 Open API 수집</t>
+          <t>수집 결과 대시보드 반영</t>
         </is>
       </c>
       <c r="E74" s="41" t="n"/>
@@ -15599,7 +15132,7 @@
       <c r="C94" s="42" t="n"/>
       <c r="D94" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-02</t>
+          <t>TT-PAR-A01-03</t>
         </is>
       </c>
       <c r="E94" s="41" t="n"/>
@@ -15624,7 +15157,7 @@
       <c r="C95" s="42" t="n"/>
       <c r="D95" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-05</t>
+          <t>PR-PAR-A01-08</t>
         </is>
       </c>
       <c r="E95" s="41" t="n"/>
@@ -15674,7 +15207,7 @@
       <c r="C97" s="42" t="n"/>
       <c r="D97" s="40" t="inlineStr">
         <is>
-          <t>불법주정차 민원·단속 데이터 연계</t>
+          <t>자세히 보기 이동 및 조회조건 승계</t>
         </is>
       </c>
       <c r="E97" s="41" t="n"/>
@@ -15802,7 +15335,7 @@
       <c r="C117" s="42" t="n"/>
       <c r="D117" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-02</t>
+          <t>TT-PAR-A01-03</t>
         </is>
       </c>
       <c r="E117" s="41" t="n"/>
@@ -15827,7 +15360,7 @@
       <c r="C118" s="42" t="n"/>
       <c r="D118" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-06</t>
+          <t>PR-PAR-A01-09</t>
         </is>
       </c>
       <c r="E118" s="41" t="n"/>
@@ -15877,7 +15410,7 @@
       <c r="C120" s="42" t="n"/>
       <c r="D120" s="40" t="inlineStr">
         <is>
-          <t>공영주차장 운영 데이터 연계</t>
+          <t>분석 레이어 전환</t>
         </is>
       </c>
       <c r="E120" s="41" t="n"/>
@@ -16005,7 +15538,7 @@
       <c r="C140" s="42" t="n"/>
       <c r="D140" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-02</t>
+          <t>TT-PAR-A01-03</t>
         </is>
       </c>
       <c r="E140" s="41" t="n"/>
@@ -16030,7 +15563,7 @@
       <c r="C141" s="42" t="n"/>
       <c r="D141" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-07</t>
+          <t>PR-PAR-A01-10</t>
         </is>
       </c>
       <c r="E141" s="41" t="n"/>
@@ -16055,7 +15588,7 @@
       <c r="C142" s="42" t="n"/>
       <c r="D142" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-001</t>
+          <t>UI-PAR-002</t>
         </is>
       </c>
       <c r="E142" s="41" t="n"/>
@@ -16080,7 +15613,7 @@
       <c r="C143" s="42" t="n"/>
       <c r="D143" s="40" t="inlineStr">
         <is>
-          <t>수집 결과 대시보드 반영</t>
+          <t>공영주차장·행정동 경계 토글</t>
         </is>
       </c>
       <c r="E143" s="41" t="n"/>
@@ -16233,7 +15766,7 @@
       <c r="C164" s="42" t="n"/>
       <c r="D164" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-08</t>
+          <t>PR-PAR-A01-11</t>
         </is>
       </c>
       <c r="E164" s="41" t="n"/>
@@ -16283,7 +15816,7 @@
       <c r="C166" s="42" t="n"/>
       <c r="D166" s="40" t="inlineStr">
         <is>
-          <t>자세히 보기 이동 및 조회조건 승계</t>
+          <t>지역별 민원현황·집중구역 순위 동기화</t>
         </is>
       </c>
       <c r="E166" s="41" t="n"/>
@@ -16411,7 +15944,7 @@
       <c r="C186" s="42" t="n"/>
       <c r="D186" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-03</t>
+          <t>TT-PAR-A01-04</t>
         </is>
       </c>
       <c r="E186" s="41" t="n"/>
@@ -16436,7 +15969,7 @@
       <c r="C187" s="42" t="n"/>
       <c r="D187" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-09</t>
+          <t>PR-PAR-A01-12</t>
         </is>
       </c>
       <c r="E187" s="41" t="n"/>
@@ -16461,7 +15994,7 @@
       <c r="C188" s="42" t="n"/>
       <c r="D188" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-002</t>
+          <t>UI-PAR-003-01</t>
         </is>
       </c>
       <c r="E188" s="41" t="n"/>
@@ -16486,7 +16019,7 @@
       <c r="C189" s="42" t="n"/>
       <c r="D189" s="40" t="inlineStr">
         <is>
-          <t>분석 레이어 전환</t>
+          <t>집중구역 자동 도출 실행</t>
         </is>
       </c>
       <c r="E189" s="41" t="n"/>
@@ -16614,7 +16147,7 @@
       <c r="C209" s="42" t="n"/>
       <c r="D209" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-03</t>
+          <t>TT-PAR-A01-04</t>
         </is>
       </c>
       <c r="E209" s="41" t="n"/>
@@ -16639,7 +16172,7 @@
       <c r="C210" s="42" t="n"/>
       <c r="D210" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-10</t>
+          <t>PR-PAR-A01-13</t>
         </is>
       </c>
       <c r="E210" s="41" t="n"/>
@@ -16664,7 +16197,7 @@
       <c r="C211" s="42" t="n"/>
       <c r="D211" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-002</t>
+          <t>UI-PAR-003-01</t>
         </is>
       </c>
       <c r="E211" s="41" t="n"/>
@@ -16689,7 +16222,7 @@
       <c r="C212" s="42" t="n"/>
       <c r="D212" s="40" t="inlineStr">
         <is>
-          <t>공영주차장·행정동 경계 토글</t>
+          <t>지도 마커 상세 팝업</t>
         </is>
       </c>
       <c r="E212" s="41" t="n"/>
@@ -16817,7 +16350,7 @@
       <c r="C232" s="42" t="n"/>
       <c r="D232" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-03</t>
+          <t>TT-PAR-A01-04</t>
         </is>
       </c>
       <c r="E232" s="41" t="n"/>
@@ -16842,7 +16375,7 @@
       <c r="C233" s="42" t="n"/>
       <c r="D233" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-11</t>
+          <t>PR-PAR-A01-14</t>
         </is>
       </c>
       <c r="E233" s="41" t="n"/>
@@ -16867,7 +16400,7 @@
       <c r="C234" s="42" t="n"/>
       <c r="D234" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-002</t>
+          <t>UI-PAR-004-01</t>
         </is>
       </c>
       <c r="E234" s="41" t="n"/>
@@ -16892,7 +16425,7 @@
       <c r="C235" s="42" t="n"/>
       <c r="D235" s="40" t="inlineStr">
         <is>
-          <t>지역별 민원현황·집중구역 순위 동기화</t>
+          <t>분석 결과 보고서 내보내기</t>
         </is>
       </c>
       <c r="E235" s="41" t="n"/>
@@ -17020,7 +16553,7 @@
       <c r="C255" s="42" t="n"/>
       <c r="D255" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-04</t>
+          <t>TT-PAR-A01-05</t>
         </is>
       </c>
       <c r="E255" s="41" t="n"/>
@@ -17045,7 +16578,7 @@
       <c r="C256" s="42" t="n"/>
       <c r="D256" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-12</t>
+          <t>PR-PAR-A01-15</t>
         </is>
       </c>
       <c r="E256" s="41" t="n"/>
@@ -17070,7 +16603,7 @@
       <c r="C257" s="42" t="n"/>
       <c r="D257" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-01</t>
+          <t>UI-PAR-003-02</t>
         </is>
       </c>
       <c r="E257" s="41" t="n"/>
@@ -17095,7 +16628,7 @@
       <c r="C258" s="42" t="n"/>
       <c r="D258" s="40" t="inlineStr">
         <is>
-          <t>집중구역 자동 도출 실행</t>
+          <t>주차장 확충 시뮬레이션 실행</t>
         </is>
       </c>
       <c r="E258" s="41" t="n"/>
@@ -17223,7 +16756,7 @@
       <c r="C278" s="42" t="n"/>
       <c r="D278" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-04</t>
+          <t>TT-PAR-A01-05</t>
         </is>
       </c>
       <c r="E278" s="41" t="n"/>
@@ -17248,7 +16781,7 @@
       <c r="C279" s="42" t="n"/>
       <c r="D279" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-13</t>
+          <t>PR-PAR-A01-16</t>
         </is>
       </c>
       <c r="E279" s="41" t="n"/>
@@ -17273,7 +16806,7 @@
       <c r="C280" s="42" t="n"/>
       <c r="D280" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-01</t>
+          <t>UI-PAR-003-02-1</t>
         </is>
       </c>
       <c r="E280" s="41" t="n"/>
@@ -17298,7 +16831,7 @@
       <c r="C281" s="42" t="n"/>
       <c r="D281" s="40" t="inlineStr">
         <is>
-          <t>지도 마커 상세 팝업</t>
+          <t>정책 유형 전환 및 변수 입력</t>
         </is>
       </c>
       <c r="E281" s="41" t="n"/>
@@ -17426,7 +16959,7 @@
       <c r="C301" s="42" t="n"/>
       <c r="D301" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-04</t>
+          <t>TT-PAR-A01-05</t>
         </is>
       </c>
       <c r="E301" s="41" t="n"/>
@@ -17451,7 +16984,7 @@
       <c r="C302" s="42" t="n"/>
       <c r="D302" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-14</t>
+          <t>PR-PAR-A01-17</t>
         </is>
       </c>
       <c r="E302" s="41" t="n"/>
@@ -17476,7 +17009,7 @@
       <c r="C303" s="42" t="n"/>
       <c r="D303" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-004-01</t>
+          <t>UI-PAR-003-02</t>
         </is>
       </c>
       <c r="E303" s="41" t="n"/>
@@ -17501,7 +17034,7 @@
       <c r="C304" s="42" t="n"/>
       <c r="D304" s="40" t="inlineStr">
         <is>
-          <t>분석 결과 보고서 내보내기</t>
+          <t>시나리오 비교</t>
         </is>
       </c>
       <c r="E304" s="41" t="n"/>
@@ -17654,7 +17187,7 @@
       <c r="C325" s="42" t="n"/>
       <c r="D325" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-15</t>
+          <t>PR-PAR-A01-18</t>
         </is>
       </c>
       <c r="E325" s="41" t="n"/>
@@ -17679,7 +17212,7 @@
       <c r="C326" s="42" t="n"/>
       <c r="D326" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-02</t>
+          <t>UI-PAR-004-01</t>
         </is>
       </c>
       <c r="E326" s="41" t="n"/>
@@ -17704,7 +17237,7 @@
       <c r="C327" s="42" t="n"/>
       <c r="D327" s="40" t="inlineStr">
         <is>
-          <t>주차장 확충 시뮬레이션 실행</t>
+          <t>시뮬레이션 결과 보고서 내보내기</t>
         </is>
       </c>
       <c r="E327" s="41" t="n"/>
@@ -17832,7 +17365,7 @@
       <c r="C347" s="42" t="n"/>
       <c r="D347" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-05</t>
+          <t>TT-PAR-A01-06</t>
         </is>
       </c>
       <c r="E347" s="41" t="n"/>
@@ -17857,7 +17390,7 @@
       <c r="C348" s="42" t="n"/>
       <c r="D348" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-16</t>
+          <t>PR-PAR-A01-19</t>
         </is>
       </c>
       <c r="E348" s="41" t="n"/>
@@ -17882,7 +17415,7 @@
       <c r="C349" s="42" t="n"/>
       <c r="D349" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-02-1</t>
+          <t>UI-PAR-003-03</t>
         </is>
       </c>
       <c r="E349" s="41" t="n"/>
@@ -17907,7 +17440,7 @@
       <c r="C350" s="42" t="n"/>
       <c r="D350" s="40" t="inlineStr">
         <is>
-          <t>정책 유형 전환 및 변수 입력</t>
+          <t>격자 기반 분석 실행</t>
         </is>
       </c>
       <c r="E350" s="41" t="n"/>
@@ -18035,7 +17568,7 @@
       <c r="C370" s="42" t="n"/>
       <c r="D370" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-05</t>
+          <t>TT-PAR-A01-06</t>
         </is>
       </c>
       <c r="E370" s="41" t="n"/>
@@ -18060,7 +17593,7 @@
       <c r="C371" s="42" t="n"/>
       <c r="D371" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-17</t>
+          <t>PR-PAR-A01-20</t>
         </is>
       </c>
       <c r="E371" s="41" t="n"/>
@@ -18085,7 +17618,7 @@
       <c r="C372" s="42" t="n"/>
       <c r="D372" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-02</t>
+          <t>UI-PAR-003-03</t>
         </is>
       </c>
       <c r="E372" s="41" t="n"/>
@@ -18110,7 +17643,7 @@
       <c r="C373" s="42" t="n"/>
       <c r="D373" s="40" t="inlineStr">
         <is>
-          <t>시나리오 비교</t>
+          <t>격자 클릭 상세 팝업</t>
         </is>
       </c>
       <c r="E373" s="41" t="n"/>
@@ -18238,7 +17771,7 @@
       <c r="C393" s="42" t="n"/>
       <c r="D393" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-05</t>
+          <t>TT-PAR-A01-06</t>
         </is>
       </c>
       <c r="E393" s="41" t="n"/>
@@ -18263,7 +17796,7 @@
       <c r="C394" s="42" t="n"/>
       <c r="D394" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-18</t>
+          <t>PR-PAR-A01-21</t>
         </is>
       </c>
       <c r="E394" s="41" t="n"/>
@@ -18288,7 +17821,7 @@
       <c r="C395" s="42" t="n"/>
       <c r="D395" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-004-01</t>
+          <t>UI-PAR-003-03</t>
         </is>
       </c>
       <c r="E395" s="41" t="n"/>
@@ -18313,7 +17846,7 @@
       <c r="C396" s="42" t="n"/>
       <c r="D396" s="40" t="inlineStr">
         <is>
-          <t>시뮬레이션 결과 보고서 내보내기</t>
+          <t>분석결과요약·민원집중구역 표출</t>
         </is>
       </c>
       <c r="E396" s="41" t="n"/>
@@ -18441,7 +17974,7 @@
       <c r="C416" s="42" t="n"/>
       <c r="D416" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-06</t>
+          <t>TT-PAR-A01-07</t>
         </is>
       </c>
       <c r="E416" s="41" t="n"/>
@@ -18466,7 +17999,7 @@
       <c r="C417" s="42" t="n"/>
       <c r="D417" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-19</t>
+          <t>PR-PAR-A01-22</t>
         </is>
       </c>
       <c r="E417" s="41" t="n"/>
@@ -18491,7 +18024,7 @@
       <c r="C418" s="42" t="n"/>
       <c r="D418" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-03</t>
+          <t>UI-PAR-003-04</t>
         </is>
       </c>
       <c r="E418" s="41" t="n"/>
@@ -18516,7 +18049,7 @@
       <c r="C419" s="42" t="n"/>
       <c r="D419" s="40" t="inlineStr">
         <is>
-          <t>격자 기반 분석 실행</t>
+          <t>구역 추천 실행</t>
         </is>
       </c>
       <c r="E419" s="41" t="n"/>
@@ -18644,7 +18177,7 @@
       <c r="C439" s="42" t="n"/>
       <c r="D439" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-06</t>
+          <t>TT-PAR-A01-07</t>
         </is>
       </c>
       <c r="E439" s="41" t="n"/>
@@ -18669,7 +18202,7 @@
       <c r="C440" s="42" t="n"/>
       <c r="D440" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-20</t>
+          <t>PR-PAR-A01-23</t>
         </is>
       </c>
       <c r="E440" s="41" t="n"/>
@@ -18694,7 +18227,7 @@
       <c r="C441" s="42" t="n"/>
       <c r="D441" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-03</t>
+          <t>UI-PAR-003-04</t>
         </is>
       </c>
       <c r="E441" s="41" t="n"/>
@@ -18719,7 +18252,7 @@
       <c r="C442" s="42" t="n"/>
       <c r="D442" s="40" t="inlineStr">
         <is>
-          <t>격자 클릭 상세 팝업</t>
+          <t>추천 구역 마커 표출</t>
         </is>
       </c>
       <c r="E442" s="41" t="n"/>
@@ -18847,7 +18380,7 @@
       <c r="C462" s="42" t="n"/>
       <c r="D462" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-06</t>
+          <t>TT-PAR-A01-07</t>
         </is>
       </c>
       <c r="E462" s="41" t="n"/>
@@ -18872,7 +18405,7 @@
       <c r="C463" s="42" t="n"/>
       <c r="D463" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-21</t>
+          <t>PR-PAR-A01-24</t>
         </is>
       </c>
       <c r="E463" s="41" t="n"/>
@@ -18897,7 +18430,7 @@
       <c r="C464" s="42" t="n"/>
       <c r="D464" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-03</t>
+          <t>UI-PAR-003-04</t>
         </is>
       </c>
       <c r="E464" s="41" t="n"/>
@@ -18922,7 +18455,7 @@
       <c r="C465" s="42" t="n"/>
       <c r="D465" s="40" t="inlineStr">
         <is>
-          <t>분석결과요약·민원집중구역 표출</t>
+          <t>추천 구역 순위 산정</t>
         </is>
       </c>
       <c r="E465" s="41" t="n"/>
@@ -19050,7 +18583,7 @@
       <c r="C485" s="42" t="n"/>
       <c r="D485" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-07</t>
+          <t>TT-PAR-A01-08</t>
         </is>
       </c>
       <c r="E485" s="41" t="n"/>
@@ -19075,7 +18608,7 @@
       <c r="C486" s="42" t="n"/>
       <c r="D486" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-22</t>
+          <t>PR-PAR-A01-25</t>
         </is>
       </c>
       <c r="E486" s="41" t="n"/>
@@ -19100,7 +18633,7 @@
       <c r="C487" s="42" t="n"/>
       <c r="D487" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-04</t>
+          <t>UI-PAR-003-05</t>
         </is>
       </c>
       <c r="E487" s="41" t="n"/>
@@ -19125,7 +18658,7 @@
       <c r="C488" s="42" t="n"/>
       <c r="D488" s="40" t="inlineStr">
         <is>
-          <t>구역 추천 실행</t>
+          <t>종합 지표 기반 우선순위 자동 산정</t>
         </is>
       </c>
       <c r="E488" s="41" t="n"/>
@@ -19253,7 +18786,7 @@
       <c r="C508" s="42" t="n"/>
       <c r="D508" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-07</t>
+          <t>TT-PAR-A01-08</t>
         </is>
       </c>
       <c r="E508" s="41" t="n"/>
@@ -19278,7 +18811,7 @@
       <c r="C509" s="42" t="n"/>
       <c r="D509" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-23</t>
+          <t>PR-PAR-A01-26</t>
         </is>
       </c>
       <c r="E509" s="41" t="n"/>
@@ -19303,7 +18836,7 @@
       <c r="C510" s="42" t="n"/>
       <c r="D510" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-04</t>
+          <t>UI-PAR-003-05</t>
         </is>
       </c>
       <c r="E510" s="41" t="n"/>
@@ -19328,7 +18861,7 @@
       <c r="C511" s="42" t="n"/>
       <c r="D511" s="40" t="inlineStr">
         <is>
-          <t>추천 구역 마커 표출</t>
+          <t>지도 마커 표출 및 상세 팝업</t>
         </is>
       </c>
       <c r="E511" s="41" t="n"/>
@@ -19456,7 +18989,7 @@
       <c r="C531" s="42" t="n"/>
       <c r="D531" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-07</t>
+          <t>TT-PAR-A01-08</t>
         </is>
       </c>
       <c r="E531" s="41" t="n"/>
@@ -19481,7 +19014,7 @@
       <c r="C532" s="42" t="n"/>
       <c r="D532" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-24</t>
+          <t>PR-PAR-A01-27</t>
         </is>
       </c>
       <c r="E532" s="41" t="n"/>
@@ -19506,7 +19039,7 @@
       <c r="C533" s="42" t="n"/>
       <c r="D533" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-04</t>
+          <t>UI-PAR-003-05</t>
         </is>
       </c>
       <c r="E533" s="41" t="n"/>
@@ -19531,7 +19064,7 @@
       <c r="C534" s="42" t="n"/>
       <c r="D534" s="40" t="inlineStr">
         <is>
-          <t>추천 구역 순위 산정</t>
+          <t>요약 카드·순위 리스트 정합성</t>
         </is>
       </c>
       <c r="E534" s="41" t="n"/>
@@ -19659,7 +19192,7 @@
       <c r="C554" s="42" t="n"/>
       <c r="D554" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-08</t>
+          <t>TT-PAR-A01-09</t>
         </is>
       </c>
       <c r="E554" s="41" t="n"/>
@@ -19684,7 +19217,7 @@
       <c r="C555" s="42" t="n"/>
       <c r="D555" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-25</t>
+          <t>PR-PAR-A01-28</t>
         </is>
       </c>
       <c r="E555" s="41" t="n"/>
@@ -19709,7 +19242,7 @@
       <c r="C556" s="42" t="n"/>
       <c r="D556" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-05</t>
+          <t>UI-PAR-004-03</t>
         </is>
       </c>
       <c r="E556" s="41" t="n"/>
@@ -19734,7 +19267,7 @@
       <c r="C557" s="42" t="n"/>
       <c r="D557" s="40" t="inlineStr">
         <is>
-          <t>종합 지표 기반 우선순위 자동 산정</t>
+          <t>알림 기준 설정 저장</t>
         </is>
       </c>
       <c r="E557" s="41" t="n"/>
@@ -19862,7 +19395,7 @@
       <c r="C577" s="42" t="n"/>
       <c r="D577" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-08</t>
+          <t>TT-PAR-A01-09</t>
         </is>
       </c>
       <c r="E577" s="41" t="n"/>
@@ -19887,7 +19420,7 @@
       <c r="C578" s="42" t="n"/>
       <c r="D578" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-26</t>
+          <t>PR-PAR-A01-29</t>
         </is>
       </c>
       <c r="E578" s="41" t="n"/>
@@ -19912,7 +19445,7 @@
       <c r="C579" s="42" t="n"/>
       <c r="D579" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-05</t>
+          <t>UI-PAR-004-03</t>
         </is>
       </c>
       <c r="E579" s="41" t="n"/>
@@ -19937,7 +19470,7 @@
       <c r="C580" s="42" t="n"/>
       <c r="D580" s="40" t="inlineStr">
         <is>
-          <t>지도 마커 표출 및 상세 팝업</t>
+          <t>수신자 등록 및 활성화 관리</t>
         </is>
       </c>
       <c r="E580" s="41" t="n"/>
@@ -20065,7 +19598,7 @@
       <c r="C600" s="42" t="n"/>
       <c r="D600" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-08</t>
+          <t>TT-PAR-A01-09</t>
         </is>
       </c>
       <c r="E600" s="41" t="n"/>
@@ -20090,7 +19623,7 @@
       <c r="C601" s="42" t="n"/>
       <c r="D601" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-27</t>
+          <t>PR-PAR-A01-30</t>
         </is>
       </c>
       <c r="E601" s="41" t="n"/>
@@ -20115,7 +19648,7 @@
       <c r="C602" s="42" t="n"/>
       <c r="D602" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-05</t>
+          <t>UI-PAR-004-02</t>
         </is>
       </c>
       <c r="E602" s="41" t="n"/>
@@ -20140,7 +19673,7 @@
       <c r="C603" s="42" t="n"/>
       <c r="D603" s="40" t="inlineStr">
         <is>
-          <t>요약 카드·순위 리스트 정합성</t>
+          <t>기준 충족 시 알림 자동 발생</t>
         </is>
       </c>
       <c r="E603" s="41" t="n"/>
@@ -20293,7 +19826,7 @@
       <c r="C624" s="42" t="n"/>
       <c r="D624" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-28</t>
+          <t>PR-PAR-A01-31</t>
         </is>
       </c>
       <c r="E624" s="41" t="n"/>
@@ -20318,7 +19851,7 @@
       <c r="C625" s="42" t="n"/>
       <c r="D625" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-004-03</t>
+          <t>UI-PAR-004-02</t>
         </is>
       </c>
       <c r="E625" s="41" t="n"/>
@@ -20343,7 +19876,7 @@
       <c r="C626" s="42" t="n"/>
       <c r="D626" s="40" t="inlineStr">
         <is>
-          <t>알림 기준 설정 저장</t>
+          <t>알림 이력 조회</t>
         </is>
       </c>
       <c r="E626" s="41" t="n"/>
@@ -20471,7 +20004,7 @@
       <c r="C646" s="42" t="n"/>
       <c r="D646" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-09</t>
+          <t>TT-PAR-A01-10</t>
         </is>
       </c>
       <c r="E646" s="41" t="n"/>
@@ -20496,7 +20029,7 @@
       <c r="C647" s="42" t="n"/>
       <c r="D647" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-29</t>
+          <t>PR-PAR-A01-32</t>
         </is>
       </c>
       <c r="E647" s="41" t="n"/>
@@ -20521,7 +20054,7 @@
       <c r="C648" s="42" t="n"/>
       <c r="D648" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-004-03</t>
+          <t>UI-PAR-004-01</t>
         </is>
       </c>
       <c r="E648" s="41" t="n"/>
@@ -20546,7 +20079,7 @@
       <c r="C649" s="42" t="n"/>
       <c r="D649" s="40" t="inlineStr">
         <is>
-          <t>수신자 등록 및 활성화 관리</t>
+          <t>배포주기·배포일자 설정</t>
         </is>
       </c>
       <c r="E649" s="41" t="n"/>
@@ -20674,7 +20207,7 @@
       <c r="C669" s="42" t="n"/>
       <c r="D669" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-09</t>
+          <t>TT-PAR-A01-10</t>
         </is>
       </c>
       <c r="E669" s="41" t="n"/>
@@ -20699,7 +20232,7 @@
       <c r="C670" s="42" t="n"/>
       <c r="D670" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-30</t>
+          <t>PR-PAR-A01-33</t>
         </is>
       </c>
       <c r="E670" s="41" t="n"/>
@@ -20724,7 +20257,7 @@
       <c r="C671" s="42" t="n"/>
       <c r="D671" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-004-02</t>
+          <t>UI-PAR-004-01</t>
         </is>
       </c>
       <c r="E671" s="41" t="n"/>
@@ -20749,7 +20282,7 @@
       <c r="C672" s="42" t="n"/>
       <c r="D672" s="40" t="inlineStr">
         <is>
-          <t>기준 충족 시 알림 자동 발생</t>
+          <t>배포일자 도래 시 자동 생성</t>
         </is>
       </c>
       <c r="E672" s="41" t="n"/>
@@ -20877,7 +20410,7 @@
       <c r="C692" s="42" t="n"/>
       <c r="D692" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-09</t>
+          <t>TT-PAR-A01-10</t>
         </is>
       </c>
       <c r="E692" s="41" t="n"/>
@@ -20902,7 +20435,7 @@
       <c r="C693" s="42" t="n"/>
       <c r="D693" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-31</t>
+          <t>PR-PAR-A01-34</t>
         </is>
       </c>
       <c r="E693" s="41" t="n"/>
@@ -20927,7 +20460,7 @@
       <c r="C694" s="42" t="n"/>
       <c r="D694" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-004-02</t>
+          <t>UI-PAR-004-01</t>
         </is>
       </c>
       <c r="E694" s="41" t="n"/>
@@ -20952,7 +20485,7 @@
       <c r="C695" s="42" t="n"/>
       <c r="D695" s="40" t="inlineStr">
         <is>
-          <t>알림 이력 조회</t>
+          <t>미리보기 및 다운로드</t>
         </is>
       </c>
       <c r="E695" s="41" t="n"/>
@@ -21080,7 +20613,7 @@
       <c r="C715" s="42" t="n"/>
       <c r="D715" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-10</t>
+          <t>TT-PAR-A01-11</t>
         </is>
       </c>
       <c r="E715" s="41" t="n"/>
@@ -21105,7 +20638,7 @@
       <c r="C716" s="42" t="n"/>
       <c r="D716" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-32</t>
+          <t>PR-PAR-A01-35</t>
         </is>
       </c>
       <c r="E716" s="41" t="n"/>
@@ -21130,7 +20663,7 @@
       <c r="C717" s="42" t="n"/>
       <c r="D717" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-004-01</t>
+          <t>UI-PAR-005</t>
         </is>
       </c>
       <c r="E717" s="41" t="n"/>
@@ -21155,7 +20688,7 @@
       <c r="C718" s="42" t="n"/>
       <c r="D718" s="40" t="inlineStr">
         <is>
-          <t>배포주기·배포일자 설정</t>
+          <t>AI 어시스턴트 행정 지원(자연어 검색·조례 인용·민원 요약)</t>
         </is>
       </c>
       <c r="E718" s="41" t="n"/>
@@ -21283,7 +20816,7 @@
       <c r="C738" s="42" t="n"/>
       <c r="D738" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-10</t>
+          <t>TT-PAR-A01-12</t>
         </is>
       </c>
       <c r="E738" s="41" t="n"/>
@@ -21308,7 +20841,7 @@
       <c r="C739" s="42" t="n"/>
       <c r="D739" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-33</t>
+          <t>PR-PAR-A01-37</t>
         </is>
       </c>
       <c r="E739" s="41" t="n"/>
@@ -21333,7 +20866,7 @@
       <c r="C740" s="42" t="n"/>
       <c r="D740" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-004-01</t>
+          <t>UI-PAR-005</t>
         </is>
       </c>
       <c r="E740" s="41" t="n"/>
@@ -21358,7 +20891,7 @@
       <c r="C741" s="42" t="n"/>
       <c r="D741" s="40" t="inlineStr">
         <is>
-          <t>배포일자 도래 시 자동 생성</t>
+          <t>데이터 융합 통합분석</t>
         </is>
       </c>
       <c r="E741" s="41" t="n"/>
@@ -21486,7 +21019,7 @@
       <c r="C761" s="42" t="n"/>
       <c r="D761" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-10</t>
+          <t>TT-PAR-A01-13</t>
         </is>
       </c>
       <c r="E761" s="41" t="n"/>
@@ -21511,7 +21044,7 @@
       <c r="C762" s="42" t="n"/>
       <c r="D762" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-34</t>
+          <t>PR-PAR-A01-39</t>
         </is>
       </c>
       <c r="E762" s="41" t="n"/>
@@ -21536,7 +21069,7 @@
       <c r="C763" s="42" t="n"/>
       <c r="D763" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-004-01</t>
+          <t>공통(설정)</t>
         </is>
       </c>
       <c r="E763" s="41" t="n"/>
@@ -21561,7 +21094,7 @@
       <c r="C764" s="42" t="n"/>
       <c r="D764" s="40" t="inlineStr">
         <is>
-          <t>미리보기 및 다운로드</t>
+          <t>타 지자체 확산 적용 구조 검증</t>
         </is>
       </c>
       <c r="E764" s="41" t="n"/>
@@ -21678,1039 +21211,40 @@
       <c r="N782" s="51" t="n"/>
       <c r="O782" s="52" t="n"/>
     </row>
-    <row r="783"/>
-    <row r="784" ht="24" customHeight="1" s="48">
-      <c r="A784" s="43" t="inlineStr">
-        <is>
-          <t>통합테스트 아이디</t>
-        </is>
-      </c>
-      <c r="B784" s="41" t="n"/>
-      <c r="C784" s="42" t="n"/>
-      <c r="D784" s="40" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-11</t>
-        </is>
-      </c>
-      <c r="E784" s="41" t="n"/>
-      <c r="F784" s="41" t="n"/>
-      <c r="G784" s="41" t="n"/>
-      <c r="H784" s="41" t="n"/>
-      <c r="I784" s="41" t="n"/>
-      <c r="J784" s="41" t="n"/>
-      <c r="K784" s="41" t="n"/>
-      <c r="L784" s="41" t="n"/>
-      <c r="M784" s="41" t="n"/>
-      <c r="N784" s="41" t="n"/>
-      <c r="O784" s="42" t="n"/>
-    </row>
-    <row r="785" ht="24" customHeight="1" s="48">
-      <c r="A785" s="43" t="inlineStr">
-        <is>
-          <t>프로그램 ID</t>
-        </is>
-      </c>
-      <c r="B785" s="41" t="n"/>
-      <c r="C785" s="42" t="n"/>
-      <c r="D785" s="40" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-35</t>
-        </is>
-      </c>
-      <c r="E785" s="41" t="n"/>
-      <c r="F785" s="41" t="n"/>
-      <c r="G785" s="41" t="n"/>
-      <c r="H785" s="41" t="n"/>
-      <c r="I785" s="41" t="n"/>
-      <c r="J785" s="41" t="n"/>
-      <c r="K785" s="41" t="n"/>
-      <c r="L785" s="41" t="n"/>
-      <c r="M785" s="41" t="n"/>
-      <c r="N785" s="41" t="n"/>
-      <c r="O785" s="42" t="n"/>
-    </row>
-    <row r="786" ht="24" customHeight="1" s="48">
-      <c r="A786" s="43" t="inlineStr">
-        <is>
-          <t>화면 ID</t>
-        </is>
-      </c>
-      <c r="B786" s="41" t="n"/>
-      <c r="C786" s="42" t="n"/>
-      <c r="D786" s="40" t="inlineStr">
-        <is>
-          <t>UI-PAR-005</t>
-        </is>
-      </c>
-      <c r="E786" s="41" t="n"/>
-      <c r="F786" s="41" t="n"/>
-      <c r="G786" s="41" t="n"/>
-      <c r="H786" s="41" t="n"/>
-      <c r="I786" s="41" t="n"/>
-      <c r="J786" s="41" t="n"/>
-      <c r="K786" s="41" t="n"/>
-      <c r="L786" s="41" t="n"/>
-      <c r="M786" s="41" t="n"/>
-      <c r="N786" s="41" t="n"/>
-      <c r="O786" s="42" t="n"/>
-    </row>
-    <row r="787" ht="24" customHeight="1" s="48">
-      <c r="A787" s="43" t="inlineStr">
-        <is>
-          <t>시나리오명</t>
-        </is>
-      </c>
-      <c r="B787" s="41" t="n"/>
-      <c r="C787" s="42" t="n"/>
-      <c r="D787" s="40" t="inlineStr">
-        <is>
-          <t>AI 어시스턴트 행정 지원(자연어 검색·조례 인용·민원 요약)</t>
-        </is>
-      </c>
-      <c r="E787" s="41" t="n"/>
-      <c r="F787" s="41" t="n"/>
-      <c r="G787" s="41" t="n"/>
-      <c r="H787" s="41" t="n"/>
-      <c r="I787" s="41" t="n"/>
-      <c r="J787" s="41" t="n"/>
-      <c r="K787" s="41" t="n"/>
-      <c r="L787" s="41" t="n"/>
-      <c r="M787" s="41" t="n"/>
-      <c r="N787" s="41" t="n"/>
-      <c r="O787" s="42" t="n"/>
-    </row>
-    <row r="788">
-      <c r="A788" s="44" t="inlineStr">
-        <is>
-          <t>[ 테스트 결과 화면 캡쳐 ]</t>
-        </is>
-      </c>
-      <c r="B788" s="45" t="n"/>
-      <c r="C788" s="45" t="n"/>
-      <c r="D788" s="45" t="n"/>
-      <c r="E788" s="45" t="n"/>
-      <c r="F788" s="45" t="n"/>
-      <c r="G788" s="45" t="n"/>
-      <c r="H788" s="45" t="n"/>
-      <c r="I788" s="45" t="n"/>
-      <c r="J788" s="45" t="n"/>
-      <c r="K788" s="45" t="n"/>
-      <c r="L788" s="45" t="n"/>
-      <c r="M788" s="45" t="n"/>
-      <c r="N788" s="45" t="n"/>
-      <c r="O788" s="46" t="n"/>
-    </row>
-    <row r="789">
-      <c r="A789" s="47" t="n"/>
-      <c r="O789" s="49" t="n"/>
-    </row>
-    <row r="790">
-      <c r="A790" s="47" t="n"/>
-      <c r="O790" s="49" t="n"/>
-    </row>
-    <row r="791">
-      <c r="A791" s="47" t="n"/>
-      <c r="O791" s="49" t="n"/>
-    </row>
-    <row r="792">
-      <c r="A792" s="47" t="n"/>
-      <c r="O792" s="49" t="n"/>
-    </row>
-    <row r="793">
-      <c r="A793" s="47" t="n"/>
-      <c r="O793" s="49" t="n"/>
-    </row>
-    <row r="794">
-      <c r="A794" s="47" t="n"/>
-      <c r="O794" s="49" t="n"/>
-    </row>
-    <row r="795">
-      <c r="A795" s="47" t="n"/>
-      <c r="O795" s="49" t="n"/>
-    </row>
-    <row r="796">
-      <c r="A796" s="47" t="n"/>
-      <c r="O796" s="49" t="n"/>
-    </row>
-    <row r="797">
-      <c r="A797" s="47" t="n"/>
-      <c r="O797" s="49" t="n"/>
-    </row>
-    <row r="798">
-      <c r="A798" s="47" t="n"/>
-      <c r="O798" s="49" t="n"/>
-    </row>
-    <row r="799">
-      <c r="A799" s="47" t="n"/>
-      <c r="O799" s="49" t="n"/>
-    </row>
-    <row r="800">
-      <c r="A800" s="47" t="n"/>
-      <c r="O800" s="49" t="n"/>
-    </row>
-    <row r="801">
-      <c r="A801" s="47" t="n"/>
-      <c r="O801" s="49" t="n"/>
-    </row>
-    <row r="802">
-      <c r="A802" s="47" t="n"/>
-      <c r="O802" s="49" t="n"/>
-    </row>
-    <row r="803">
-      <c r="A803" s="47" t="n"/>
-      <c r="O803" s="49" t="n"/>
-    </row>
-    <row r="804">
-      <c r="A804" s="47" t="n"/>
-      <c r="O804" s="49" t="n"/>
-    </row>
-    <row r="805">
-      <c r="A805" s="50" t="n"/>
-      <c r="B805" s="51" t="n"/>
-      <c r="C805" s="51" t="n"/>
-      <c r="D805" s="51" t="n"/>
-      <c r="E805" s="51" t="n"/>
-      <c r="F805" s="51" t="n"/>
-      <c r="G805" s="51" t="n"/>
-      <c r="H805" s="51" t="n"/>
-      <c r="I805" s="51" t="n"/>
-      <c r="J805" s="51" t="n"/>
-      <c r="K805" s="51" t="n"/>
-      <c r="L805" s="51" t="n"/>
-      <c r="M805" s="51" t="n"/>
-      <c r="N805" s="51" t="n"/>
-      <c r="O805" s="52" t="n"/>
-    </row>
-    <row r="806"/>
-    <row r="807" ht="24" customHeight="1" s="48">
-      <c r="A807" s="43" t="inlineStr">
-        <is>
-          <t>통합테스트 아이디</t>
-        </is>
-      </c>
-      <c r="B807" s="41" t="n"/>
-      <c r="C807" s="42" t="n"/>
-      <c r="D807" s="40" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-12</t>
-        </is>
-      </c>
-      <c r="E807" s="41" t="n"/>
-      <c r="F807" s="41" t="n"/>
-      <c r="G807" s="41" t="n"/>
-      <c r="H807" s="41" t="n"/>
-      <c r="I807" s="41" t="n"/>
-      <c r="J807" s="41" t="n"/>
-      <c r="K807" s="41" t="n"/>
-      <c r="L807" s="41" t="n"/>
-      <c r="M807" s="41" t="n"/>
-      <c r="N807" s="41" t="n"/>
-      <c r="O807" s="42" t="n"/>
-    </row>
-    <row r="808" ht="24" customHeight="1" s="48">
-      <c r="A808" s="43" t="inlineStr">
-        <is>
-          <t>프로그램 ID</t>
-        </is>
-      </c>
-      <c r="B808" s="41" t="n"/>
-      <c r="C808" s="42" t="n"/>
-      <c r="D808" s="40" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-36</t>
-        </is>
-      </c>
-      <c r="E808" s="41" t="n"/>
-      <c r="F808" s="41" t="n"/>
-      <c r="G808" s="41" t="n"/>
-      <c r="H808" s="41" t="n"/>
-      <c r="I808" s="41" t="n"/>
-      <c r="J808" s="41" t="n"/>
-      <c r="K808" s="41" t="n"/>
-      <c r="L808" s="41" t="n"/>
-      <c r="M808" s="41" t="n"/>
-      <c r="N808" s="41" t="n"/>
-      <c r="O808" s="42" t="n"/>
-    </row>
-    <row r="809" ht="24" customHeight="1" s="48">
-      <c r="A809" s="43" t="inlineStr">
-        <is>
-          <t>화면 ID</t>
-        </is>
-      </c>
-      <c r="B809" s="41" t="n"/>
-      <c r="C809" s="42" t="n"/>
-      <c r="D809" s="40" t="inlineStr">
-        <is>
-          <t>UI-PAR-005</t>
-        </is>
-      </c>
-      <c r="E809" s="41" t="n"/>
-      <c r="F809" s="41" t="n"/>
-      <c r="G809" s="41" t="n"/>
-      <c r="H809" s="41" t="n"/>
-      <c r="I809" s="41" t="n"/>
-      <c r="J809" s="41" t="n"/>
-      <c r="K809" s="41" t="n"/>
-      <c r="L809" s="41" t="n"/>
-      <c r="M809" s="41" t="n"/>
-      <c r="N809" s="41" t="n"/>
-      <c r="O809" s="42" t="n"/>
-    </row>
-    <row r="810" ht="24" customHeight="1" s="48">
-      <c r="A810" s="43" t="inlineStr">
-        <is>
-          <t>시나리오명</t>
-        </is>
-      </c>
-      <c r="B810" s="41" t="n"/>
-      <c r="C810" s="42" t="n"/>
-      <c r="D810" s="40" t="inlineStr">
-        <is>
-          <t>비정형 행정문서 자동 수집·정형화(AI RPA/OCR)</t>
-        </is>
-      </c>
-      <c r="E810" s="41" t="n"/>
-      <c r="F810" s="41" t="n"/>
-      <c r="G810" s="41" t="n"/>
-      <c r="H810" s="41" t="n"/>
-      <c r="I810" s="41" t="n"/>
-      <c r="J810" s="41" t="n"/>
-      <c r="K810" s="41" t="n"/>
-      <c r="L810" s="41" t="n"/>
-      <c r="M810" s="41" t="n"/>
-      <c r="N810" s="41" t="n"/>
-      <c r="O810" s="42" t="n"/>
-    </row>
-    <row r="811">
-      <c r="A811" s="44" t="inlineStr">
-        <is>
-          <t>[ 테스트 결과 화면 캡쳐 ]</t>
-        </is>
-      </c>
-      <c r="B811" s="45" t="n"/>
-      <c r="C811" s="45" t="n"/>
-      <c r="D811" s="45" t="n"/>
-      <c r="E811" s="45" t="n"/>
-      <c r="F811" s="45" t="n"/>
-      <c r="G811" s="45" t="n"/>
-      <c r="H811" s="45" t="n"/>
-      <c r="I811" s="45" t="n"/>
-      <c r="J811" s="45" t="n"/>
-      <c r="K811" s="45" t="n"/>
-      <c r="L811" s="45" t="n"/>
-      <c r="M811" s="45" t="n"/>
-      <c r="N811" s="45" t="n"/>
-      <c r="O811" s="46" t="n"/>
-    </row>
-    <row r="812">
-      <c r="A812" s="47" t="n"/>
-      <c r="O812" s="49" t="n"/>
-    </row>
-    <row r="813">
-      <c r="A813" s="47" t="n"/>
-      <c r="O813" s="49" t="n"/>
-    </row>
-    <row r="814">
-      <c r="A814" s="47" t="n"/>
-      <c r="O814" s="49" t="n"/>
-    </row>
-    <row r="815">
-      <c r="A815" s="47" t="n"/>
-      <c r="O815" s="49" t="n"/>
-    </row>
-    <row r="816">
-      <c r="A816" s="47" t="n"/>
-      <c r="O816" s="49" t="n"/>
-    </row>
-    <row r="817">
-      <c r="A817" s="47" t="n"/>
-      <c r="O817" s="49" t="n"/>
-    </row>
-    <row r="818">
-      <c r="A818" s="47" t="n"/>
-      <c r="O818" s="49" t="n"/>
-    </row>
-    <row r="819">
-      <c r="A819" s="47" t="n"/>
-      <c r="O819" s="49" t="n"/>
-    </row>
-    <row r="820">
-      <c r="A820" s="47" t="n"/>
-      <c r="O820" s="49" t="n"/>
-    </row>
-    <row r="821">
-      <c r="A821" s="47" t="n"/>
-      <c r="O821" s="49" t="n"/>
-    </row>
-    <row r="822">
-      <c r="A822" s="47" t="n"/>
-      <c r="O822" s="49" t="n"/>
-    </row>
-    <row r="823">
-      <c r="A823" s="47" t="n"/>
-      <c r="O823" s="49" t="n"/>
-    </row>
-    <row r="824">
-      <c r="A824" s="47" t="n"/>
-      <c r="O824" s="49" t="n"/>
-    </row>
-    <row r="825">
-      <c r="A825" s="47" t="n"/>
-      <c r="O825" s="49" t="n"/>
-    </row>
-    <row r="826">
-      <c r="A826" s="47" t="n"/>
-      <c r="O826" s="49" t="n"/>
-    </row>
-    <row r="827">
-      <c r="A827" s="47" t="n"/>
-      <c r="O827" s="49" t="n"/>
-    </row>
-    <row r="828">
-      <c r="A828" s="50" t="n"/>
-      <c r="B828" s="51" t="n"/>
-      <c r="C828" s="51" t="n"/>
-      <c r="D828" s="51" t="n"/>
-      <c r="E828" s="51" t="n"/>
-      <c r="F828" s="51" t="n"/>
-      <c r="G828" s="51" t="n"/>
-      <c r="H828" s="51" t="n"/>
-      <c r="I828" s="51" t="n"/>
-      <c r="J828" s="51" t="n"/>
-      <c r="K828" s="51" t="n"/>
-      <c r="L828" s="51" t="n"/>
-      <c r="M828" s="51" t="n"/>
-      <c r="N828" s="51" t="n"/>
-      <c r="O828" s="52" t="n"/>
-    </row>
-    <row r="829"/>
-    <row r="830" ht="24" customHeight="1" s="48">
-      <c r="A830" s="43" t="inlineStr">
-        <is>
-          <t>통합테스트 아이디</t>
-        </is>
-      </c>
-      <c r="B830" s="41" t="n"/>
-      <c r="C830" s="42" t="n"/>
-      <c r="D830" s="40" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-13</t>
-        </is>
-      </c>
-      <c r="E830" s="41" t="n"/>
-      <c r="F830" s="41" t="n"/>
-      <c r="G830" s="41" t="n"/>
-      <c r="H830" s="41" t="n"/>
-      <c r="I830" s="41" t="n"/>
-      <c r="J830" s="41" t="n"/>
-      <c r="K830" s="41" t="n"/>
-      <c r="L830" s="41" t="n"/>
-      <c r="M830" s="41" t="n"/>
-      <c r="N830" s="41" t="n"/>
-      <c r="O830" s="42" t="n"/>
-    </row>
-    <row r="831" ht="24" customHeight="1" s="48">
-      <c r="A831" s="43" t="inlineStr">
-        <is>
-          <t>프로그램 ID</t>
-        </is>
-      </c>
-      <c r="B831" s="41" t="n"/>
-      <c r="C831" s="42" t="n"/>
-      <c r="D831" s="40" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-37</t>
-        </is>
-      </c>
-      <c r="E831" s="41" t="n"/>
-      <c r="F831" s="41" t="n"/>
-      <c r="G831" s="41" t="n"/>
-      <c r="H831" s="41" t="n"/>
-      <c r="I831" s="41" t="n"/>
-      <c r="J831" s="41" t="n"/>
-      <c r="K831" s="41" t="n"/>
-      <c r="L831" s="41" t="n"/>
-      <c r="M831" s="41" t="n"/>
-      <c r="N831" s="41" t="n"/>
-      <c r="O831" s="42" t="n"/>
-    </row>
-    <row r="832" ht="24" customHeight="1" s="48">
-      <c r="A832" s="43" t="inlineStr">
-        <is>
-          <t>화면 ID</t>
-        </is>
-      </c>
-      <c r="B832" s="41" t="n"/>
-      <c r="C832" s="42" t="n"/>
-      <c r="D832" s="40" t="inlineStr">
-        <is>
-          <t>UI-PAR-005</t>
-        </is>
-      </c>
-      <c r="E832" s="41" t="n"/>
-      <c r="F832" s="41" t="n"/>
-      <c r="G832" s="41" t="n"/>
-      <c r="H832" s="41" t="n"/>
-      <c r="I832" s="41" t="n"/>
-      <c r="J832" s="41" t="n"/>
-      <c r="K832" s="41" t="n"/>
-      <c r="L832" s="41" t="n"/>
-      <c r="M832" s="41" t="n"/>
-      <c r="N832" s="41" t="n"/>
-      <c r="O832" s="42" t="n"/>
-    </row>
-    <row r="833" ht="24" customHeight="1" s="48">
-      <c r="A833" s="43" t="inlineStr">
-        <is>
-          <t>시나리오명</t>
-        </is>
-      </c>
-      <c r="B833" s="41" t="n"/>
-      <c r="C833" s="42" t="n"/>
-      <c r="D833" s="40" t="inlineStr">
-        <is>
-          <t>데이터 융합 통합분석</t>
-        </is>
-      </c>
-      <c r="E833" s="41" t="n"/>
-      <c r="F833" s="41" t="n"/>
-      <c r="G833" s="41" t="n"/>
-      <c r="H833" s="41" t="n"/>
-      <c r="I833" s="41" t="n"/>
-      <c r="J833" s="41" t="n"/>
-      <c r="K833" s="41" t="n"/>
-      <c r="L833" s="41" t="n"/>
-      <c r="M833" s="41" t="n"/>
-      <c r="N833" s="41" t="n"/>
-      <c r="O833" s="42" t="n"/>
-    </row>
-    <row r="834">
-      <c r="A834" s="44" t="inlineStr">
-        <is>
-          <t>[ 테스트 결과 화면 캡쳐 ]</t>
-        </is>
-      </c>
-      <c r="B834" s="45" t="n"/>
-      <c r="C834" s="45" t="n"/>
-      <c r="D834" s="45" t="n"/>
-      <c r="E834" s="45" t="n"/>
-      <c r="F834" s="45" t="n"/>
-      <c r="G834" s="45" t="n"/>
-      <c r="H834" s="45" t="n"/>
-      <c r="I834" s="45" t="n"/>
-      <c r="J834" s="45" t="n"/>
-      <c r="K834" s="45" t="n"/>
-      <c r="L834" s="45" t="n"/>
-      <c r="M834" s="45" t="n"/>
-      <c r="N834" s="45" t="n"/>
-      <c r="O834" s="46" t="n"/>
-    </row>
-    <row r="835">
-      <c r="A835" s="47" t="n"/>
-      <c r="O835" s="49" t="n"/>
-    </row>
-    <row r="836">
-      <c r="A836" s="47" t="n"/>
-      <c r="O836" s="49" t="n"/>
-    </row>
-    <row r="837">
-      <c r="A837" s="47" t="n"/>
-      <c r="O837" s="49" t="n"/>
-    </row>
-    <row r="838">
-      <c r="A838" s="47" t="n"/>
-      <c r="O838" s="49" t="n"/>
-    </row>
-    <row r="839">
-      <c r="A839" s="47" t="n"/>
-      <c r="O839" s="49" t="n"/>
-    </row>
-    <row r="840">
-      <c r="A840" s="47" t="n"/>
-      <c r="O840" s="49" t="n"/>
-    </row>
-    <row r="841">
-      <c r="A841" s="47" t="n"/>
-      <c r="O841" s="49" t="n"/>
-    </row>
-    <row r="842">
-      <c r="A842" s="47" t="n"/>
-      <c r="O842" s="49" t="n"/>
-    </row>
-    <row r="843">
-      <c r="A843" s="47" t="n"/>
-      <c r="O843" s="49" t="n"/>
-    </row>
-    <row r="844">
-      <c r="A844" s="47" t="n"/>
-      <c r="O844" s="49" t="n"/>
-    </row>
-    <row r="845">
-      <c r="A845" s="47" t="n"/>
-      <c r="O845" s="49" t="n"/>
-    </row>
-    <row r="846">
-      <c r="A846" s="47" t="n"/>
-      <c r="O846" s="49" t="n"/>
-    </row>
-    <row r="847">
-      <c r="A847" s="47" t="n"/>
-      <c r="O847" s="49" t="n"/>
-    </row>
-    <row r="848">
-      <c r="A848" s="47" t="n"/>
-      <c r="O848" s="49" t="n"/>
-    </row>
-    <row r="849">
-      <c r="A849" s="47" t="n"/>
-      <c r="O849" s="49" t="n"/>
-    </row>
-    <row r="850">
-      <c r="A850" s="47" t="n"/>
-      <c r="O850" s="49" t="n"/>
-    </row>
-    <row r="851">
-      <c r="A851" s="50" t="n"/>
-      <c r="B851" s="51" t="n"/>
-      <c r="C851" s="51" t="n"/>
-      <c r="D851" s="51" t="n"/>
-      <c r="E851" s="51" t="n"/>
-      <c r="F851" s="51" t="n"/>
-      <c r="G851" s="51" t="n"/>
-      <c r="H851" s="51" t="n"/>
-      <c r="I851" s="51" t="n"/>
-      <c r="J851" s="51" t="n"/>
-      <c r="K851" s="51" t="n"/>
-      <c r="L851" s="51" t="n"/>
-      <c r="M851" s="51" t="n"/>
-      <c r="N851" s="51" t="n"/>
-      <c r="O851" s="52" t="n"/>
-    </row>
-    <row r="852"/>
-    <row r="853" ht="24" customHeight="1" s="48">
-      <c r="A853" s="43" t="inlineStr">
-        <is>
-          <t>통합테스트 아이디</t>
-        </is>
-      </c>
-      <c r="B853" s="41" t="n"/>
-      <c r="C853" s="42" t="n"/>
-      <c r="D853" s="40" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-14</t>
-        </is>
-      </c>
-      <c r="E853" s="41" t="n"/>
-      <c r="F853" s="41" t="n"/>
-      <c r="G853" s="41" t="n"/>
-      <c r="H853" s="41" t="n"/>
-      <c r="I853" s="41" t="n"/>
-      <c r="J853" s="41" t="n"/>
-      <c r="K853" s="41" t="n"/>
-      <c r="L853" s="41" t="n"/>
-      <c r="M853" s="41" t="n"/>
-      <c r="N853" s="41" t="n"/>
-      <c r="O853" s="42" t="n"/>
-    </row>
-    <row r="854" ht="24" customHeight="1" s="48">
-      <c r="A854" s="43" t="inlineStr">
-        <is>
-          <t>프로그램 ID</t>
-        </is>
-      </c>
-      <c r="B854" s="41" t="n"/>
-      <c r="C854" s="42" t="n"/>
-      <c r="D854" s="40" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-38</t>
-        </is>
-      </c>
-      <c r="E854" s="41" t="n"/>
-      <c r="F854" s="41" t="n"/>
-      <c r="G854" s="41" t="n"/>
-      <c r="H854" s="41" t="n"/>
-      <c r="I854" s="41" t="n"/>
-      <c r="J854" s="41" t="n"/>
-      <c r="K854" s="41" t="n"/>
-      <c r="L854" s="41" t="n"/>
-      <c r="M854" s="41" t="n"/>
-      <c r="N854" s="41" t="n"/>
-      <c r="O854" s="42" t="n"/>
-    </row>
-    <row r="855" ht="24" customHeight="1" s="48">
-      <c r="A855" s="43" t="inlineStr">
-        <is>
-          <t>화면 ID</t>
-        </is>
-      </c>
-      <c r="B855" s="41" t="n"/>
-      <c r="C855" s="42" t="n"/>
-      <c r="D855" s="40" t="inlineStr">
-        <is>
-          <t>공통(배치)</t>
-        </is>
-      </c>
-      <c r="E855" s="41" t="n"/>
-      <c r="F855" s="41" t="n"/>
-      <c r="G855" s="41" t="n"/>
-      <c r="H855" s="41" t="n"/>
-      <c r="I855" s="41" t="n"/>
-      <c r="J855" s="41" t="n"/>
-      <c r="K855" s="41" t="n"/>
-      <c r="L855" s="41" t="n"/>
-      <c r="M855" s="41" t="n"/>
-      <c r="N855" s="41" t="n"/>
-      <c r="O855" s="42" t="n"/>
-    </row>
-    <row r="856" ht="24" customHeight="1" s="48">
-      <c r="A856" s="43" t="inlineStr">
-        <is>
-          <t>시나리오명</t>
-        </is>
-      </c>
-      <c r="B856" s="41" t="n"/>
-      <c r="C856" s="42" t="n"/>
-      <c r="D856" s="40" t="inlineStr">
-        <is>
-          <t>분석 모델 재학습 및 고도화</t>
-        </is>
-      </c>
-      <c r="E856" s="41" t="n"/>
-      <c r="F856" s="41" t="n"/>
-      <c r="G856" s="41" t="n"/>
-      <c r="H856" s="41" t="n"/>
-      <c r="I856" s="41" t="n"/>
-      <c r="J856" s="41" t="n"/>
-      <c r="K856" s="41" t="n"/>
-      <c r="L856" s="41" t="n"/>
-      <c r="M856" s="41" t="n"/>
-      <c r="N856" s="41" t="n"/>
-      <c r="O856" s="42" t="n"/>
-    </row>
-    <row r="857">
-      <c r="A857" s="44" t="inlineStr">
-        <is>
-          <t>[ 테스트 결과 화면 캡쳐 ]</t>
-        </is>
-      </c>
-      <c r="B857" s="45" t="n"/>
-      <c r="C857" s="45" t="n"/>
-      <c r="D857" s="45" t="n"/>
-      <c r="E857" s="45" t="n"/>
-      <c r="F857" s="45" t="n"/>
-      <c r="G857" s="45" t="n"/>
-      <c r="H857" s="45" t="n"/>
-      <c r="I857" s="45" t="n"/>
-      <c r="J857" s="45" t="n"/>
-      <c r="K857" s="45" t="n"/>
-      <c r="L857" s="45" t="n"/>
-      <c r="M857" s="45" t="n"/>
-      <c r="N857" s="45" t="n"/>
-      <c r="O857" s="46" t="n"/>
-    </row>
-    <row r="858">
-      <c r="A858" s="47" t="n"/>
-      <c r="O858" s="49" t="n"/>
-    </row>
-    <row r="859">
-      <c r="A859" s="47" t="n"/>
-      <c r="O859" s="49" t="n"/>
-    </row>
-    <row r="860">
-      <c r="A860" s="47" t="n"/>
-      <c r="O860" s="49" t="n"/>
-    </row>
-    <row r="861">
-      <c r="A861" s="47" t="n"/>
-      <c r="O861" s="49" t="n"/>
-    </row>
-    <row r="862">
-      <c r="A862" s="47" t="n"/>
-      <c r="O862" s="49" t="n"/>
-    </row>
-    <row r="863">
-      <c r="A863" s="47" t="n"/>
-      <c r="O863" s="49" t="n"/>
-    </row>
-    <row r="864">
-      <c r="A864" s="47" t="n"/>
-      <c r="O864" s="49" t="n"/>
-    </row>
-    <row r="865">
-      <c r="A865" s="47" t="n"/>
-      <c r="O865" s="49" t="n"/>
-    </row>
-    <row r="866">
-      <c r="A866" s="47" t="n"/>
-      <c r="O866" s="49" t="n"/>
-    </row>
-    <row r="867">
-      <c r="A867" s="47" t="n"/>
-      <c r="O867" s="49" t="n"/>
-    </row>
-    <row r="868">
-      <c r="A868" s="47" t="n"/>
-      <c r="O868" s="49" t="n"/>
-    </row>
-    <row r="869">
-      <c r="A869" s="47" t="n"/>
-      <c r="O869" s="49" t="n"/>
-    </row>
-    <row r="870">
-      <c r="A870" s="47" t="n"/>
-      <c r="O870" s="49" t="n"/>
-    </row>
-    <row r="871">
-      <c r="A871" s="47" t="n"/>
-      <c r="O871" s="49" t="n"/>
-    </row>
-    <row r="872">
-      <c r="A872" s="47" t="n"/>
-      <c r="O872" s="49" t="n"/>
-    </row>
-    <row r="873">
-      <c r="A873" s="47" t="n"/>
-      <c r="O873" s="49" t="n"/>
-    </row>
-    <row r="874">
-      <c r="A874" s="50" t="n"/>
-      <c r="B874" s="51" t="n"/>
-      <c r="C874" s="51" t="n"/>
-      <c r="D874" s="51" t="n"/>
-      <c r="E874" s="51" t="n"/>
-      <c r="F874" s="51" t="n"/>
-      <c r="G874" s="51" t="n"/>
-      <c r="H874" s="51" t="n"/>
-      <c r="I874" s="51" t="n"/>
-      <c r="J874" s="51" t="n"/>
-      <c r="K874" s="51" t="n"/>
-      <c r="L874" s="51" t="n"/>
-      <c r="M874" s="51" t="n"/>
-      <c r="N874" s="51" t="n"/>
-      <c r="O874" s="52" t="n"/>
-    </row>
-    <row r="875"/>
-    <row r="876" ht="24" customHeight="1" s="48">
-      <c r="A876" s="43" t="inlineStr">
-        <is>
-          <t>통합테스트 아이디</t>
-        </is>
-      </c>
-      <c r="B876" s="41" t="n"/>
-      <c r="C876" s="42" t="n"/>
-      <c r="D876" s="40" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-15</t>
-        </is>
-      </c>
-      <c r="E876" s="41" t="n"/>
-      <c r="F876" s="41" t="n"/>
-      <c r="G876" s="41" t="n"/>
-      <c r="H876" s="41" t="n"/>
-      <c r="I876" s="41" t="n"/>
-      <c r="J876" s="41" t="n"/>
-      <c r="K876" s="41" t="n"/>
-      <c r="L876" s="41" t="n"/>
-      <c r="M876" s="41" t="n"/>
-      <c r="N876" s="41" t="n"/>
-      <c r="O876" s="42" t="n"/>
-    </row>
-    <row r="877" ht="24" customHeight="1" s="48">
-      <c r="A877" s="43" t="inlineStr">
-        <is>
-          <t>프로그램 ID</t>
-        </is>
-      </c>
-      <c r="B877" s="41" t="n"/>
-      <c r="C877" s="42" t="n"/>
-      <c r="D877" s="40" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-39</t>
-        </is>
-      </c>
-      <c r="E877" s="41" t="n"/>
-      <c r="F877" s="41" t="n"/>
-      <c r="G877" s="41" t="n"/>
-      <c r="H877" s="41" t="n"/>
-      <c r="I877" s="41" t="n"/>
-      <c r="J877" s="41" t="n"/>
-      <c r="K877" s="41" t="n"/>
-      <c r="L877" s="41" t="n"/>
-      <c r="M877" s="41" t="n"/>
-      <c r="N877" s="41" t="n"/>
-      <c r="O877" s="42" t="n"/>
-    </row>
-    <row r="878" ht="24" customHeight="1" s="48">
-      <c r="A878" s="43" t="inlineStr">
-        <is>
-          <t>화면 ID</t>
-        </is>
-      </c>
-      <c r="B878" s="41" t="n"/>
-      <c r="C878" s="42" t="n"/>
-      <c r="D878" s="40" t="inlineStr">
-        <is>
-          <t>공통(설정)</t>
-        </is>
-      </c>
-      <c r="E878" s="41" t="n"/>
-      <c r="F878" s="41" t="n"/>
-      <c r="G878" s="41" t="n"/>
-      <c r="H878" s="41" t="n"/>
-      <c r="I878" s="41" t="n"/>
-      <c r="J878" s="41" t="n"/>
-      <c r="K878" s="41" t="n"/>
-      <c r="L878" s="41" t="n"/>
-      <c r="M878" s="41" t="n"/>
-      <c r="N878" s="41" t="n"/>
-      <c r="O878" s="42" t="n"/>
-    </row>
-    <row r="879" ht="24" customHeight="1" s="48">
-      <c r="A879" s="43" t="inlineStr">
-        <is>
-          <t>시나리오명</t>
-        </is>
-      </c>
-      <c r="B879" s="41" t="n"/>
-      <c r="C879" s="42" t="n"/>
-      <c r="D879" s="40" t="inlineStr">
-        <is>
-          <t>타 지자체 확산 적용 구조 검증</t>
-        </is>
-      </c>
-      <c r="E879" s="41" t="n"/>
-      <c r="F879" s="41" t="n"/>
-      <c r="G879" s="41" t="n"/>
-      <c r="H879" s="41" t="n"/>
-      <c r="I879" s="41" t="n"/>
-      <c r="J879" s="41" t="n"/>
-      <c r="K879" s="41" t="n"/>
-      <c r="L879" s="41" t="n"/>
-      <c r="M879" s="41" t="n"/>
-      <c r="N879" s="41" t="n"/>
-      <c r="O879" s="42" t="n"/>
-    </row>
-    <row r="880">
-      <c r="A880" s="44" t="inlineStr">
-        <is>
-          <t>[ 테스트 결과 화면 캡쳐 ]</t>
-        </is>
-      </c>
-      <c r="B880" s="45" t="n"/>
-      <c r="C880" s="45" t="n"/>
-      <c r="D880" s="45" t="n"/>
-      <c r="E880" s="45" t="n"/>
-      <c r="F880" s="45" t="n"/>
-      <c r="G880" s="45" t="n"/>
-      <c r="H880" s="45" t="n"/>
-      <c r="I880" s="45" t="n"/>
-      <c r="J880" s="45" t="n"/>
-      <c r="K880" s="45" t="n"/>
-      <c r="L880" s="45" t="n"/>
-      <c r="M880" s="45" t="n"/>
-      <c r="N880" s="45" t="n"/>
-      <c r="O880" s="46" t="n"/>
-    </row>
-    <row r="881">
-      <c r="A881" s="47" t="n"/>
-      <c r="O881" s="49" t="n"/>
-    </row>
-    <row r="882">
-      <c r="A882" s="47" t="n"/>
-      <c r="O882" s="49" t="n"/>
-    </row>
-    <row r="883">
-      <c r="A883" s="47" t="n"/>
-      <c r="O883" s="49" t="n"/>
-    </row>
-    <row r="884">
-      <c r="A884" s="47" t="n"/>
-      <c r="O884" s="49" t="n"/>
-    </row>
-    <row r="885">
-      <c r="A885" s="47" t="n"/>
-      <c r="O885" s="49" t="n"/>
-    </row>
-    <row r="886">
-      <c r="A886" s="47" t="n"/>
-      <c r="O886" s="49" t="n"/>
-    </row>
-    <row r="887">
-      <c r="A887" s="47" t="n"/>
-      <c r="O887" s="49" t="n"/>
-    </row>
-    <row r="888">
-      <c r="A888" s="47" t="n"/>
-      <c r="O888" s="49" t="n"/>
-    </row>
-    <row r="889">
-      <c r="A889" s="47" t="n"/>
-      <c r="O889" s="49" t="n"/>
-    </row>
-    <row r="890">
-      <c r="A890" s="47" t="n"/>
-      <c r="O890" s="49" t="n"/>
-    </row>
-    <row r="891">
-      <c r="A891" s="47" t="n"/>
-      <c r="O891" s="49" t="n"/>
-    </row>
-    <row r="892">
-      <c r="A892" s="47" t="n"/>
-      <c r="O892" s="49" t="n"/>
-    </row>
-    <row r="893">
-      <c r="A893" s="47" t="n"/>
-      <c r="O893" s="49" t="n"/>
-    </row>
-    <row r="894">
-      <c r="A894" s="47" t="n"/>
-      <c r="O894" s="49" t="n"/>
-    </row>
-    <row r="895">
-      <c r="A895" s="47" t="n"/>
-      <c r="O895" s="49" t="n"/>
-    </row>
-    <row r="896">
-      <c r="A896" s="47" t="n"/>
-      <c r="O896" s="49" t="n"/>
-    </row>
-    <row r="897">
-      <c r="A897" s="50" t="n"/>
-      <c r="B897" s="51" t="n"/>
-      <c r="C897" s="51" t="n"/>
-      <c r="D897" s="51" t="n"/>
-      <c r="E897" s="51" t="n"/>
-      <c r="F897" s="51" t="n"/>
-      <c r="G897" s="51" t="n"/>
-      <c r="H897" s="51" t="n"/>
-      <c r="I897" s="51" t="n"/>
-      <c r="J897" s="51" t="n"/>
-      <c r="K897" s="51" t="n"/>
-      <c r="L897" s="51" t="n"/>
-      <c r="M897" s="51" t="n"/>
-      <c r="N897" s="51" t="n"/>
-      <c r="O897" s="52" t="n"/>
-    </row>
+    <row r="784" ht="24" customHeight="1" s="48"/>
+    <row r="785" ht="24" customHeight="1" s="48"/>
+    <row r="786" ht="24" customHeight="1" s="48"/>
+    <row r="787" ht="24" customHeight="1" s="48"/>
+    <row r="807" ht="24" customHeight="1" s="48"/>
+    <row r="808" ht="24" customHeight="1" s="48"/>
+    <row r="809" ht="24" customHeight="1" s="48"/>
+    <row r="810" ht="24" customHeight="1" s="48"/>
+    <row r="830" ht="24" customHeight="1" s="48"/>
+    <row r="831" ht="24" customHeight="1" s="48"/>
+    <row r="832" ht="24" customHeight="1" s="48"/>
+    <row r="833" ht="24" customHeight="1" s="48"/>
+    <row r="853" ht="24" customHeight="1" s="48"/>
+    <row r="854" ht="24" customHeight="1" s="48"/>
+    <row r="855" ht="24" customHeight="1" s="48"/>
+    <row r="856" ht="24" customHeight="1" s="48"/>
+    <row r="876" ht="24" customHeight="1" s="48"/>
+    <row r="877" ht="24" customHeight="1" s="48"/>
+    <row r="878" ht="24" customHeight="1" s="48"/>
+    <row r="879" ht="24" customHeight="1" s="48"/>
   </sheetData>
-  <mergeCells count="351">
+  <mergeCells count="306">
     <mergeCell ref="D2:O2"/>
     <mergeCell ref="A255:C255"/>
     <mergeCell ref="A326:C326"/>
     <mergeCell ref="D189:O189"/>
     <mergeCell ref="A557:C557"/>
-    <mergeCell ref="D877:O877"/>
-    <mergeCell ref="A855:C855"/>
     <mergeCell ref="D716:O716"/>
     <mergeCell ref="D416:O416"/>
-    <mergeCell ref="A784:C784"/>
     <mergeCell ref="A715:C715"/>
     <mergeCell ref="A351:O368"/>
     <mergeCell ref="A761:C761"/>
     <mergeCell ref="D142:O142"/>
     <mergeCell ref="A510:C510"/>
-    <mergeCell ref="D807:O807"/>
     <mergeCell ref="D442:O442"/>
     <mergeCell ref="A49:C49"/>
     <mergeCell ref="D119:O119"/>
@@ -22723,59 +21257,47 @@
     <mergeCell ref="D3:O3"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D74:O74"/>
+    <mergeCell ref="D117:O117"/>
     <mergeCell ref="D372:O372"/>
+    <mergeCell ref="D188:O188"/>
     <mergeCell ref="A512:O529"/>
-    <mergeCell ref="D117:O117"/>
-    <mergeCell ref="D188:O188"/>
-    <mergeCell ref="A786:C786"/>
     <mergeCell ref="D5:O5"/>
     <mergeCell ref="A258:C258"/>
     <mergeCell ref="D303:O303"/>
     <mergeCell ref="D417:O417"/>
-    <mergeCell ref="A785:C785"/>
-    <mergeCell ref="D830:O830"/>
     <mergeCell ref="A73:C73"/>
     <mergeCell ref="D603:O603"/>
-    <mergeCell ref="A787:C787"/>
     <mergeCell ref="A466:O483"/>
     <mergeCell ref="A167:O184"/>
     <mergeCell ref="A98:O115"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="D210:O210"/>
     <mergeCell ref="A578:C578"/>
-    <mergeCell ref="D210:O210"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A876:C876"/>
     <mergeCell ref="D209:O209"/>
     <mergeCell ref="A188:C188"/>
     <mergeCell ref="D301:O301"/>
-    <mergeCell ref="A878:C878"/>
-    <mergeCell ref="A853:C853"/>
     <mergeCell ref="D211:O211"/>
     <mergeCell ref="D511:O511"/>
     <mergeCell ref="A558:O575"/>
     <mergeCell ref="A259:O276"/>
-    <mergeCell ref="A856:C856"/>
     <mergeCell ref="D140:O140"/>
     <mergeCell ref="D740:O740"/>
     <mergeCell ref="A328:O345"/>
-    <mergeCell ref="D832:O832"/>
     <mergeCell ref="D440:O440"/>
-    <mergeCell ref="A808:C808"/>
     <mergeCell ref="D738:O738"/>
     <mergeCell ref="A74:C74"/>
     <mergeCell ref="D141:O141"/>
     <mergeCell ref="D72:O72"/>
     <mergeCell ref="D235:O235"/>
     <mergeCell ref="A140:C140"/>
-    <mergeCell ref="A788:O805"/>
     <mergeCell ref="D393:O393"/>
     <mergeCell ref="D624:O624"/>
+    <mergeCell ref="D26:O26"/>
+    <mergeCell ref="D324:O324"/>
+    <mergeCell ref="A350:C350"/>
+    <mergeCell ref="A692:C692"/>
+    <mergeCell ref="A279:C279"/>
     <mergeCell ref="A719:O736"/>
-    <mergeCell ref="A279:C279"/>
-    <mergeCell ref="D26:O26"/>
-    <mergeCell ref="A692:C692"/>
-    <mergeCell ref="A350:C350"/>
-    <mergeCell ref="D324:O324"/>
-    <mergeCell ref="A879:C879"/>
     <mergeCell ref="A420:O437"/>
     <mergeCell ref="A94:C94"/>
     <mergeCell ref="A281:C281"/>
@@ -22788,19 +21310,20 @@
     <mergeCell ref="A234:C234"/>
     <mergeCell ref="D764:O764"/>
     <mergeCell ref="D143:O143"/>
+    <mergeCell ref="D441:O441"/>
     <mergeCell ref="D118:O118"/>
+    <mergeCell ref="D256:O256"/>
     <mergeCell ref="A371:C371"/>
-    <mergeCell ref="D441:O441"/>
+    <mergeCell ref="D232:O232"/>
     <mergeCell ref="A165:C165"/>
-    <mergeCell ref="D232:O232"/>
     <mergeCell ref="D741:O741"/>
     <mergeCell ref="D532:O532"/>
     <mergeCell ref="A489:O506"/>
     <mergeCell ref="A669:C669"/>
     <mergeCell ref="D96:O96"/>
     <mergeCell ref="D27:O27"/>
+    <mergeCell ref="D396:O396"/>
     <mergeCell ref="D325:O325"/>
-    <mergeCell ref="D396:O396"/>
     <mergeCell ref="A120:C120"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A301:C301"/>
@@ -22808,42 +21331,39 @@
     <mergeCell ref="A393:C393"/>
     <mergeCell ref="A464:C464"/>
     <mergeCell ref="D327:O327"/>
-    <mergeCell ref="A695:C695"/>
     <mergeCell ref="D625:O625"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D556:O556"/>
     <mergeCell ref="A303:C303"/>
+    <mergeCell ref="A97:C97"/>
     <mergeCell ref="A601:C601"/>
-    <mergeCell ref="A97:C97"/>
     <mergeCell ref="A395:C395"/>
     <mergeCell ref="A693:C693"/>
     <mergeCell ref="A96:C96"/>
     <mergeCell ref="D487:O487"/>
     <mergeCell ref="D280:O280"/>
     <mergeCell ref="D488:O488"/>
-    <mergeCell ref="D233:O233"/>
     <mergeCell ref="D580:O580"/>
     <mergeCell ref="D350:O350"/>
     <mergeCell ref="A212:C212"/>
     <mergeCell ref="A187:C187"/>
+    <mergeCell ref="A485:C485"/>
     <mergeCell ref="D257:O257"/>
-    <mergeCell ref="A485:C485"/>
     <mergeCell ref="D533:O533"/>
     <mergeCell ref="A189:C189"/>
+    <mergeCell ref="D557:O557"/>
     <mergeCell ref="A487:C487"/>
-    <mergeCell ref="D557:O557"/>
     <mergeCell ref="A278:C278"/>
     <mergeCell ref="D371:O371"/>
     <mergeCell ref="D485:O485"/>
     <mergeCell ref="A581:O598"/>
-    <mergeCell ref="A857:O874"/>
+    <mergeCell ref="A695:C695"/>
     <mergeCell ref="D164:O164"/>
     <mergeCell ref="D462:O462"/>
-    <mergeCell ref="A830:C830"/>
     <mergeCell ref="A603:C603"/>
     <mergeCell ref="A650:O667"/>
-    <mergeCell ref="A832:C832"/>
+    <mergeCell ref="D762:O762"/>
     <mergeCell ref="A304:C304"/>
-    <mergeCell ref="D762:O762"/>
     <mergeCell ref="A396:C396"/>
     <mergeCell ref="D463:O463"/>
     <mergeCell ref="D555:O555"/>
@@ -22852,9 +21372,9 @@
     <mergeCell ref="D48:O48"/>
     <mergeCell ref="D554:O554"/>
     <mergeCell ref="D348:O348"/>
-    <mergeCell ref="A716:C716"/>
     <mergeCell ref="D646:O646"/>
     <mergeCell ref="D717:O717"/>
+    <mergeCell ref="A716:C716"/>
     <mergeCell ref="A324:C324"/>
     <mergeCell ref="D347:O347"/>
     <mergeCell ref="A416:C416"/>
@@ -22864,8 +21384,8 @@
     <mergeCell ref="D349:O349"/>
     <mergeCell ref="D647:O647"/>
     <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A604:O621"/>
     <mergeCell ref="A142:C142"/>
-    <mergeCell ref="A604:O621"/>
     <mergeCell ref="A696:O713"/>
     <mergeCell ref="D672:O672"/>
     <mergeCell ref="A442:C442"/>
@@ -22877,22 +21397,19 @@
     <mergeCell ref="A531:C531"/>
     <mergeCell ref="D465:O465"/>
     <mergeCell ref="D763:O763"/>
-    <mergeCell ref="A235:C235"/>
     <mergeCell ref="A210:C210"/>
     <mergeCell ref="A533:C533"/>
     <mergeCell ref="D578:O578"/>
-    <mergeCell ref="A831:C831"/>
-    <mergeCell ref="D876:O876"/>
+    <mergeCell ref="A235:C235"/>
     <mergeCell ref="A75:O92"/>
-    <mergeCell ref="A833:C833"/>
     <mergeCell ref="D418:O418"/>
     <mergeCell ref="A144:O161"/>
     <mergeCell ref="D718:O718"/>
     <mergeCell ref="A325:C325"/>
     <mergeCell ref="A119:C119"/>
     <mergeCell ref="A417:C417"/>
+    <mergeCell ref="A488:C488"/>
     <mergeCell ref="D186:O186"/>
-    <mergeCell ref="A488:C488"/>
     <mergeCell ref="D649:O649"/>
     <mergeCell ref="A256:C256"/>
     <mergeCell ref="A625:C625"/>
@@ -22901,38 +21418,32 @@
     <mergeCell ref="A418:C418"/>
     <mergeCell ref="D715:O715"/>
     <mergeCell ref="A305:O322"/>
-    <mergeCell ref="D809:O809"/>
+    <mergeCell ref="A397:O414"/>
     <mergeCell ref="D212:O212"/>
-    <mergeCell ref="A397:O414"/>
     <mergeCell ref="D510:O510"/>
     <mergeCell ref="D304:O304"/>
+    <mergeCell ref="A236:O253"/>
     <mergeCell ref="D602:O602"/>
-    <mergeCell ref="A236:O253"/>
     <mergeCell ref="A209:C209"/>
     <mergeCell ref="A280:C280"/>
     <mergeCell ref="A372:C372"/>
-    <mergeCell ref="D810:O810"/>
     <mergeCell ref="A211:C211"/>
-    <mergeCell ref="D256:O256"/>
     <mergeCell ref="A509:C509"/>
     <mergeCell ref="A534:C534"/>
     <mergeCell ref="D579:O579"/>
     <mergeCell ref="A186:C186"/>
     <mergeCell ref="A257:C257"/>
     <mergeCell ref="D370:O370"/>
+    <mergeCell ref="A555:C555"/>
+    <mergeCell ref="A349:C349"/>
+    <mergeCell ref="A51:C51"/>
     <mergeCell ref="A672:C672"/>
-    <mergeCell ref="A555:C555"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A349:C349"/>
     <mergeCell ref="A511:C511"/>
-    <mergeCell ref="A809:C809"/>
-    <mergeCell ref="D879:O879"/>
     <mergeCell ref="A486:C486"/>
     <mergeCell ref="A649:C649"/>
     <mergeCell ref="D693:O693"/>
     <mergeCell ref="D670:O670"/>
     <mergeCell ref="D486:O486"/>
-    <mergeCell ref="D784:O784"/>
     <mergeCell ref="A440:C440"/>
     <mergeCell ref="A738:C738"/>
     <mergeCell ref="D534:O534"/>
@@ -22941,111 +21452,93 @@
     <mergeCell ref="A439:C439"/>
     <mergeCell ref="D373:O373"/>
     <mergeCell ref="A72:C72"/>
-    <mergeCell ref="D785:O785"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="D73:O73"/>
-    <mergeCell ref="D787:O787"/>
-    <mergeCell ref="A834:O851"/>
     <mergeCell ref="A580:C580"/>
     <mergeCell ref="A765:O782"/>
     <mergeCell ref="D739:O739"/>
     <mergeCell ref="A52:O69"/>
-    <mergeCell ref="D854:O854"/>
     <mergeCell ref="A27:C27"/>
+    <mergeCell ref="D258:O258"/>
     <mergeCell ref="A577:C577"/>
     <mergeCell ref="D671:O671"/>
     <mergeCell ref="D4:O4"/>
     <mergeCell ref="D531:O531"/>
     <mergeCell ref="A764:C764"/>
     <mergeCell ref="A143:C143"/>
-    <mergeCell ref="D831:O831"/>
     <mergeCell ref="A441:C441"/>
+    <mergeCell ref="D508:O508"/>
     <mergeCell ref="A739:C739"/>
-    <mergeCell ref="D508:O508"/>
-    <mergeCell ref="A810:C810"/>
     <mergeCell ref="A232:C232"/>
     <mergeCell ref="D302:O302"/>
     <mergeCell ref="D600:O600"/>
     <mergeCell ref="A741:C741"/>
-    <mergeCell ref="D808:O808"/>
     <mergeCell ref="A532:C532"/>
-    <mergeCell ref="A807:C807"/>
     <mergeCell ref="D626:O626"/>
     <mergeCell ref="A302:C302"/>
     <mergeCell ref="D28:O28"/>
     <mergeCell ref="D326:O326"/>
     <mergeCell ref="D165:O165"/>
     <mergeCell ref="A327:C327"/>
-    <mergeCell ref="D394:O394"/>
     <mergeCell ref="D279:O279"/>
     <mergeCell ref="D692:O692"/>
+    <mergeCell ref="D394:O394"/>
     <mergeCell ref="D94:O94"/>
     <mergeCell ref="D623:O623"/>
     <mergeCell ref="D694:O694"/>
     <mergeCell ref="A29:O46"/>
-    <mergeCell ref="D833:O833"/>
+    <mergeCell ref="A718:C718"/>
     <mergeCell ref="A627:O644"/>
     <mergeCell ref="D577:O577"/>
     <mergeCell ref="D49:O49"/>
     <mergeCell ref="D120:O120"/>
     <mergeCell ref="D163:O163"/>
+    <mergeCell ref="D234:O234"/>
     <mergeCell ref="A602:C602"/>
-    <mergeCell ref="D234:O234"/>
     <mergeCell ref="A508:C508"/>
     <mergeCell ref="A579:C579"/>
-    <mergeCell ref="A877:C877"/>
     <mergeCell ref="A373:C373"/>
     <mergeCell ref="A671:C671"/>
     <mergeCell ref="D25:O25"/>
     <mergeCell ref="A213:O230"/>
     <mergeCell ref="D669:O669"/>
-    <mergeCell ref="D855:O855"/>
     <mergeCell ref="A462:C462"/>
-    <mergeCell ref="A880:O897"/>
     <mergeCell ref="A190:O207"/>
     <mergeCell ref="A762:C762"/>
-    <mergeCell ref="D856:O856"/>
-    <mergeCell ref="A25:C25"/>
     <mergeCell ref="D95:O95"/>
     <mergeCell ref="A463:C463"/>
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="D695:O695"/>
     <mergeCell ref="A626:C626"/>
     <mergeCell ref="A742:O759"/>
     <mergeCell ref="A163:C163"/>
     <mergeCell ref="A394:C394"/>
-    <mergeCell ref="D97:O97"/>
     <mergeCell ref="A465:C465"/>
     <mergeCell ref="D395:O395"/>
     <mergeCell ref="A763:C763"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D97:O97"/>
     <mergeCell ref="D255:O255"/>
     <mergeCell ref="A740:C740"/>
-    <mergeCell ref="D853:O853"/>
     <mergeCell ref="A443:O460"/>
     <mergeCell ref="A554:C554"/>
     <mergeCell ref="A348:C348"/>
     <mergeCell ref="A282:O299"/>
     <mergeCell ref="A646:C646"/>
-    <mergeCell ref="D786:O786"/>
     <mergeCell ref="A374:O391"/>
-    <mergeCell ref="D878:O878"/>
     <mergeCell ref="A347:C347"/>
     <mergeCell ref="D50:O50"/>
-    <mergeCell ref="A854:C854"/>
     <mergeCell ref="A648:C648"/>
     <mergeCell ref="D187:O187"/>
     <mergeCell ref="A623:C623"/>
     <mergeCell ref="A647:C647"/>
     <mergeCell ref="D281:O281"/>
     <mergeCell ref="A624:C624"/>
-    <mergeCell ref="A811:O828"/>
+    <mergeCell ref="D233:O233"/>
     <mergeCell ref="A6:O23"/>
     <mergeCell ref="A600:C600"/>
     <mergeCell ref="D761:O761"/>
     <mergeCell ref="A166:C166"/>
-    <mergeCell ref="D258:O258"/>
-    <mergeCell ref="D556:O556"/>
-    <mergeCell ref="A718:C718"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23057,7 +21550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="17.1"/>
   <cols>
     <col width="6" customWidth="1" style="48" min="1" max="1"/>
@@ -23076,7 +21569,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="28" t="inlineStr">
         <is>
@@ -23151,7 +21643,7 @@
     </row>
     <row r="5" ht="60" customHeight="1" s="48">
       <c r="A5" s="29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" s="29" t="inlineStr">
         <is>
@@ -23160,17 +21652,17 @@
       </c>
       <c r="C5" s="40" t="inlineStr">
         <is>
-          <t>AI RPA·OCR 기반 비정형 문서 자동 수집·정형화 배치에 대응하는 화면이 화면설계서(JJ_PD_IP_D04)에 없어 화면 ID를 공란 처리함</t>
+          <t>단위테스트(M04)의 설정 화면(UT-SET-01~06)에 대응하는 화면이 화면설계서에 없어 화면 ID를 공란 처리함</t>
         </is>
       </c>
       <c r="D5" s="29" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E5" s="40" t="inlineStr">
         <is>
-          <t>배치 모니터링 화면 신설 여부 검토 후 화면설계서 반영</t>
+          <t>화면설계서에 설정 화면 추가 또는 테스트 항목 조정</t>
         </is>
       </c>
       <c r="F5" s="29" t="inlineStr">
@@ -23186,31 +21678,31 @@
     </row>
     <row r="6" ht="60" customHeight="1" s="48">
       <c r="A6" s="29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" s="29" t="inlineStr">
         <is>
-          <t>설계 미반영</t>
+          <t>테스트 환경</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>단위테스트(M04)의 설정 화면(UT-SET-01~06)에 대응하는 화면이 화면설계서에 없어 화면 ID를 공란 처리함</t>
+          <t>테스트데이터를 권한 유형으로만 기재함. 실증 환경에서 권한별 계정 발급 후 테스트 수행 필요</t>
         </is>
       </c>
       <c r="D6" s="29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="E6" s="40" t="inlineStr">
         <is>
-          <t>화면설계서에 설정 화면 추가 또는 테스트 항목 조정</t>
+          <t>실증 착수 시 권한별 계정 발급 후 테스트 수행</t>
         </is>
       </c>
       <c r="F6" s="29" t="inlineStr">
         <is>
-          <t>검토중</t>
+          <t>대기</t>
         </is>
       </c>
       <c r="G6" s="29" t="inlineStr">
@@ -23221,16 +21713,16 @@
     </row>
     <row r="7" ht="60" customHeight="1" s="48">
       <c r="A7" s="29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" s="29" t="inlineStr">
         <is>
-          <t>테스트 환경</t>
+          <t>미수행</t>
         </is>
       </c>
       <c r="C7" s="40" t="inlineStr">
         <is>
-          <t>테스트데이터를 권한 유형으로만 기재함. 실증 환경에서 권한별 계정 발급 후 테스트 수행 필요</t>
+          <t>통합테스트 미수행 상태로 결과서의 1차·2차 상태·점검자·점검일이 공란임</t>
         </is>
       </c>
       <c r="D7" s="29" t="inlineStr">
@@ -23240,7 +21732,7 @@
       </c>
       <c r="E7" s="40" t="inlineStr">
         <is>
-          <t>실증 착수 시 권한별 계정 발급 후 테스트 수행</t>
+          <t>통합테스트 수행 후 결과 기입</t>
         </is>
       </c>
       <c r="F7" s="29" t="inlineStr">
@@ -23254,41 +21746,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1" s="48">
-      <c r="A8" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="29" t="inlineStr">
-        <is>
-          <t>미수행</t>
-        </is>
-      </c>
-      <c r="C8" s="40" t="inlineStr">
-        <is>
-          <t>통합테스트 미수행 상태로 결과서의 1차·2차 상태·점검자·점검일이 공란임</t>
-        </is>
-      </c>
-      <c r="D8" s="29" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="E8" s="40" t="inlineStr">
-        <is>
-          <t>통합테스트 수행 후 결과 기입</t>
-        </is>
-      </c>
-      <c r="F8" s="29" t="inlineStr">
-        <is>
-          <t>대기</t>
-        </is>
-      </c>
-      <c r="G8" s="29" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-    </row>
+    <row r="8" ht="60" customHeight="1" s="48"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
